--- a/ΕΥΑΓΓΕΛΙΖΟΜΕΝΟΙ.xlsx
+++ b/ΕΥΑΓΓΕΛΙΖΟΜΕΝΟΙ.xlsx
@@ -5,20 +5,18 @@
   <sheets>
     <sheet state="visible" name="Sheet" sheetId="1" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Sheet!$A$1:$G$49</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="BKPcT1dsre7QMsN/qutCJLkbmxHZ3KXobLbcMDg+ugc="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="TatrjW3kLCmVr1a+WBmaXxpZdL+hLfrS13V+GIzWn04="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
   <si>
     <t>publisher</t>
   </si>
@@ -41,10 +39,10 @@
     <t>Email</t>
   </si>
   <si>
-    <t>Αντωνατου Έλλη</t>
+    <t>Σμυρνόπουλος Στέφανος</t>
   </si>
   <si>
-    <t>Γυναίκα</t>
+    <t>Άνδρας</t>
   </si>
   <si>
     <t>ΜΟΣΧΑΤΟ</t>
@@ -53,475 +51,10 @@
     <t/>
   </si>
   <si>
-    <t>6973045948</t>
-  </si>
-  <si>
-    <t>elli.antonatou@gmail.com</t>
-  </si>
-  <si>
-    <t>Βασιλάκη Ειρήνη</t>
-  </si>
-  <si>
-    <t>6949972059</t>
-  </si>
-  <si>
-    <t>eirhnaki943@gmail.com</t>
-  </si>
-  <si>
-    <t>Βέττος Γιώργος</t>
-  </si>
-  <si>
-    <t>Άνδρας</t>
-  </si>
-  <si>
-    <t>6937112735</t>
-  </si>
-  <si>
-    <t>vettosg@gmail.com</t>
-  </si>
-  <si>
-    <t>Γεωργιάδου Νάντια</t>
-  </si>
-  <si>
-    <t>6908449601</t>
-  </si>
-  <si>
-    <t>egeorgiadi21@gmail.com</t>
-  </si>
-  <si>
-    <t>Γεωργιάδου Σωσώ</t>
-  </si>
-  <si>
-    <t>6938038865</t>
-  </si>
-  <si>
-    <t>Soso194921@gmail.com</t>
-  </si>
-  <si>
-    <t>Γεωργιλάς Γιώργος</t>
-  </si>
-  <si>
-    <t>6906464913</t>
-  </si>
-  <si>
-    <t>georgilasgeorge8@gmail.com</t>
-  </si>
-  <si>
-    <t>Δημητρίου Ασημίνα</t>
-  </si>
-  <si>
-    <t>6984447598</t>
-  </si>
-  <si>
-    <t>asiminad36@gmail.com</t>
-  </si>
-  <si>
-    <t>Διαμαντοπούλου Βάσω</t>
-  </si>
-  <si>
-    <t>2111843186</t>
-  </si>
-  <si>
-    <t>6978169637</t>
-  </si>
-  <si>
-    <t>vasdiamant44@gmail.com</t>
-  </si>
-  <si>
-    <t>Ζαχαριάδου Ρούλα</t>
-  </si>
-  <si>
-    <t>2104813046</t>
-  </si>
-  <si>
-    <t>6940986878</t>
-  </si>
-  <si>
-    <t>roulazah@gmail.com</t>
-  </si>
-  <si>
-    <t>Θεοδωράκης Γιώργος</t>
-  </si>
-  <si>
-    <t>2109417058</t>
-  </si>
-  <si>
-    <t>6937040491</t>
-  </si>
-  <si>
-    <t>naimur21@hotmail.gr</t>
-  </si>
-  <si>
-    <t>Ιακώβου Αναστασία</t>
-  </si>
-  <si>
-    <t>6988149199</t>
-  </si>
-  <si>
-    <t>Xaidemenakianast@gmail.com</t>
-  </si>
-  <si>
-    <t>Καραγιαννίδη Ελένη</t>
-  </si>
-  <si>
-    <t>2109414421</t>
-  </si>
-  <si>
-    <t>6947775544</t>
-  </si>
-  <si>
-    <t>Καραγιαννίδης Στέλιος</t>
-  </si>
-  <si>
-    <t>diamantopoulou.helen@gmail.com</t>
-  </si>
-  <si>
-    <t>6972555309</t>
-  </si>
-  <si>
-    <t>steliosks64@gmail.com</t>
-  </si>
-  <si>
-    <t>Κιλκικσή Μουκαντές.</t>
-  </si>
-  <si>
-    <t>6906059843</t>
-  </si>
-  <si>
-    <t>mkilkiksis@gmail.com</t>
-  </si>
-  <si>
-    <t>Κιλκικσής Δανιήλ</t>
-  </si>
-  <si>
-    <t>2130233087</t>
-  </si>
-  <si>
-    <t>6948824001</t>
-  </si>
-  <si>
-    <t>Κιλκικσή Μουκαντές</t>
-  </si>
-  <si>
-    <t>dkilkiksis@gmail.com</t>
-  </si>
-  <si>
-    <t>Κιοραί Μιγκένα</t>
-  </si>
-  <si>
-    <t>6907006621</t>
-  </si>
-  <si>
-    <t>Migenakr@hotmail.com</t>
-  </si>
-  <si>
-    <t>Κιούση Χριστίνα</t>
-  </si>
-  <si>
-    <t>6909520184</t>
-  </si>
-  <si>
-    <t>christkiousi@gmail.com</t>
-  </si>
-  <si>
-    <t>Κοστέλνα Μαίρη</t>
-  </si>
-  <si>
-    <t>6937844255</t>
-  </si>
-  <si>
-    <t>mairikostelna@gmail.com</t>
-  </si>
-  <si>
-    <t>Κουλούρη Τόνια</t>
-  </si>
-  <si>
-    <t>6938940315</t>
-  </si>
-  <si>
-    <t>toniazaha@gmail.com</t>
-  </si>
-  <si>
-    <t>Κουλούρης Πέτρος</t>
-  </si>
-  <si>
-    <t>2104823321</t>
-  </si>
-  <si>
-    <t>6945938555</t>
-  </si>
-  <si>
-    <t>petrosioanniskoulouris@gmail.com</t>
-  </si>
-  <si>
-    <t>Κυριακού Όλγα</t>
-  </si>
-  <si>
-    <t>6908737403</t>
-  </si>
-  <si>
-    <t>kyriakou.olga@gmail.com</t>
-  </si>
-  <si>
-    <t>Λεβεντάκη Αθηνά</t>
-  </si>
-  <si>
-    <t>2104626847</t>
-  </si>
-  <si>
-    <t>6972300565</t>
-  </si>
-  <si>
-    <t>a.tzortziou@gmail.com</t>
-  </si>
-  <si>
-    <t>Μαλισσόβας Κώστας</t>
-  </si>
-  <si>
-    <t>6985555115</t>
-  </si>
-  <si>
-    <t>malissovas@gmail.com</t>
-  </si>
-  <si>
-    <t>Μανετάκη Ζωή</t>
-  </si>
-  <si>
-    <t>6948044185</t>
-  </si>
-  <si>
-    <t>zmourtsinoudi@gmail.com</t>
-  </si>
-  <si>
-    <t>Μαργαντίνη Γεωργία</t>
-  </si>
-  <si>
-    <t>2109427951</t>
-  </si>
-  <si>
-    <t>6948752180</t>
-  </si>
-  <si>
-    <t>gorgina.ntini@gmail.com</t>
-  </si>
-  <si>
-    <t>Μαργαντίνη Μαριαννέτα</t>
-  </si>
-  <si>
-    <t>6908349127</t>
-  </si>
-  <si>
-    <t>mariannetamargantini@gmail.com</t>
-  </si>
-  <si>
-    <t>Μαργαντίνης Γιώργος</t>
-  </si>
-  <si>
-    <t>6934193129</t>
-  </si>
-  <si>
-    <t>g.margantinis@gmail.com</t>
-  </si>
-  <si>
-    <t>Μαργαντίνης Χρήστος.</t>
-  </si>
-  <si>
-    <t>6939069540</t>
-  </si>
-  <si>
-    <t>margantineschrestos@gmail.com</t>
-  </si>
-  <si>
-    <t>Μαυραειδή Λένα</t>
-  </si>
-  <si>
-    <t>6978252569</t>
-  </si>
-  <si>
-    <t>ntounilena@gmail.com</t>
-  </si>
-  <si>
-    <t>Μαυραειδής Αλέξανδρος</t>
-  </si>
-  <si>
-    <t>6980853483</t>
-  </si>
-  <si>
-    <t>amavraidis@gmail.com</t>
-  </si>
-  <si>
-    <t>Μπάϊλα Καίτη</t>
-  </si>
-  <si>
-    <t>6977883760</t>
-  </si>
-  <si>
-    <t>rebelg.kait@gmail.com</t>
-  </si>
-  <si>
-    <t>Ροδίτου Γεωργία</t>
-  </si>
-  <si>
-    <t>2104829406</t>
-  </si>
-  <si>
-    <t>6983090253</t>
-  </si>
-  <si>
-    <t>ginaroditou@gmail.com</t>
-  </si>
-  <si>
-    <t>Σαλλάτα Ολυμπία</t>
-  </si>
-  <si>
-    <t>6946435565</t>
-  </si>
-  <si>
-    <t>olimpiasallata@gmail.com</t>
-  </si>
-  <si>
-    <t>Σαφιανίδη Βαλέρια</t>
-  </si>
-  <si>
-    <t>6906168255</t>
-  </si>
-  <si>
-    <t>val.koval1636@gmail.com</t>
-  </si>
-  <si>
-    <t>Σαφιανίδης Κωνσταντίνος</t>
-  </si>
-  <si>
-    <t>2109415410</t>
-  </si>
-  <si>
-    <t>6943658271</t>
-  </si>
-  <si>
-    <t>safianidhs@gmail.com</t>
-  </si>
-  <si>
-    <t>Σμυρνόπουλος Στέφανος</t>
-  </si>
-  <si>
     <t>6945840662</t>
   </si>
   <si>
     <t>smyrnopoulos@gmail.com</t>
-  </si>
-  <si>
-    <t>Σμυρνοπούλου Καίτη</t>
-  </si>
-  <si>
-    <t>6980219840</t>
-  </si>
-  <si>
-    <t>aikaterinh.doksopoulou@gmail.com</t>
-  </si>
-  <si>
-    <t>Σμυρνοπούλου Ροϊδούλα</t>
-  </si>
-  <si>
-    <t>6970685495</t>
-  </si>
-  <si>
-    <t>kalogianniroidoula@hotmail.gr</t>
-  </si>
-  <si>
-    <t>Σοπιλίδη Ελπίδα</t>
-  </si>
-  <si>
-    <t>6980082055</t>
-  </si>
-  <si>
-    <t>kremonael@gmail.com</t>
-  </si>
-  <si>
-    <t>Σοπιλίδης Νίκος</t>
-  </si>
-  <si>
-    <t>6981059594</t>
-  </si>
-  <si>
-    <t>nicksopis21@hotmail.com</t>
-  </si>
-  <si>
-    <t>Σουρή Σούλα</t>
-  </si>
-  <si>
-    <t>2104830944</t>
-  </si>
-  <si>
-    <t>6973823681</t>
-  </si>
-  <si>
-    <t>Σπύρο Κατερίνα</t>
-  </si>
-  <si>
-    <t>2111116000</t>
-  </si>
-  <si>
-    <t>6955378161</t>
-  </si>
-  <si>
-    <t>ekaterinispiro@hotmail.com</t>
-  </si>
-  <si>
-    <t>Στεργιόγλου Μαρία</t>
-  </si>
-  <si>
-    <t>6977608395</t>
-  </si>
-  <si>
-    <t>mariastergioglou@gmail.com</t>
-  </si>
-  <si>
-    <t>Τέγος Τάσος</t>
-  </si>
-  <si>
-    <t>6975517136</t>
-  </si>
-  <si>
-    <t>tasostegos484@gmail.com</t>
-  </si>
-  <si>
-    <t>Τέγου Αννίτα</t>
-  </si>
-  <si>
-    <t>6939662926</t>
-  </si>
-  <si>
-    <t>teguannita@gmail.com</t>
-  </si>
-  <si>
-    <t>Τζαγκαράκη Γεωργία</t>
-  </si>
-  <si>
-    <t>6972301383</t>
-  </si>
-  <si>
-    <t>tzaglaraki.georgia@gmail.com</t>
-  </si>
-  <si>
-    <t>Τροχαλίδη Μάρω</t>
-  </si>
-  <si>
-    <t>2107643763</t>
-  </si>
-  <si>
-    <t>6949927518</t>
-  </si>
-  <si>
-    <t>maro_maroulitsa@yahoo.gr</t>
-  </si>
-  <si>
-    <t>Χαϊδεμενάκης Γρηγόρης</t>
-  </si>
-  <si>
-    <t>6947702098</t>
-  </si>
-  <si>
-    <t>grehaid@yahoo.com</t>
   </si>
 </sst>
 </file>
@@ -817,7 +350,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
@@ -840,1086 +373,428 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>73</v>
-      </c>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>77</v>
-      </c>
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>80</v>
-      </c>
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>84</v>
-      </c>
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>87</v>
-      </c>
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>90</v>
-      </c>
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>94</v>
-      </c>
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>97</v>
-      </c>
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>100</v>
-      </c>
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>103</v>
-      </c>
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>106</v>
-      </c>
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>109</v>
-      </c>
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>112</v>
-      </c>
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>116</v>
-      </c>
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>119</v>
-      </c>
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>122</v>
-      </c>
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>126</v>
-      </c>
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>129</v>
-      </c>
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>132</v>
-      </c>
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>135</v>
-      </c>
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>138</v>
-      </c>
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>141</v>
-      </c>
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>148</v>
-      </c>
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>151</v>
-      </c>
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>154</v>
-      </c>
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>157</v>
-      </c>
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>160</v>
-      </c>
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>164</v>
-      </c>
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>167</v>
-      </c>
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="2"/>
@@ -10057,431 +8932,7 @@
       <c r="F953" s="2"/>
       <c r="G953" s="2"/>
     </row>
-    <row r="954" ht="15.75" customHeight="1">
-      <c r="A954" s="2"/>
-      <c r="B954" s="2"/>
-      <c r="C954" s="2"/>
-      <c r="D954" s="2"/>
-      <c r="E954" s="2"/>
-      <c r="F954" s="2"/>
-      <c r="G954" s="2"/>
-    </row>
-    <row r="955" ht="15.75" customHeight="1">
-      <c r="A955" s="2"/>
-      <c r="B955" s="2"/>
-      <c r="C955" s="2"/>
-      <c r="D955" s="2"/>
-      <c r="E955" s="2"/>
-      <c r="F955" s="2"/>
-      <c r="G955" s="2"/>
-    </row>
-    <row r="956" ht="15.75" customHeight="1">
-      <c r="A956" s="2"/>
-      <c r="B956" s="2"/>
-      <c r="C956" s="2"/>
-      <c r="D956" s="2"/>
-      <c r="E956" s="2"/>
-      <c r="F956" s="2"/>
-      <c r="G956" s="2"/>
-    </row>
-    <row r="957" ht="15.75" customHeight="1">
-      <c r="A957" s="2"/>
-      <c r="B957" s="2"/>
-      <c r="C957" s="2"/>
-      <c r="D957" s="2"/>
-      <c r="E957" s="2"/>
-      <c r="F957" s="2"/>
-      <c r="G957" s="2"/>
-    </row>
-    <row r="958" ht="15.75" customHeight="1">
-      <c r="A958" s="2"/>
-      <c r="B958" s="2"/>
-      <c r="C958" s="2"/>
-      <c r="D958" s="2"/>
-      <c r="E958" s="2"/>
-      <c r="F958" s="2"/>
-      <c r="G958" s="2"/>
-    </row>
-    <row r="959" ht="15.75" customHeight="1">
-      <c r="A959" s="2"/>
-      <c r="B959" s="2"/>
-      <c r="C959" s="2"/>
-      <c r="D959" s="2"/>
-      <c r="E959" s="2"/>
-      <c r="F959" s="2"/>
-      <c r="G959" s="2"/>
-    </row>
-    <row r="960" ht="15.75" customHeight="1">
-      <c r="A960" s="2"/>
-      <c r="B960" s="2"/>
-      <c r="C960" s="2"/>
-      <c r="D960" s="2"/>
-      <c r="E960" s="2"/>
-      <c r="F960" s="2"/>
-      <c r="G960" s="2"/>
-    </row>
-    <row r="961" ht="15.75" customHeight="1">
-      <c r="A961" s="2"/>
-      <c r="B961" s="2"/>
-      <c r="C961" s="2"/>
-      <c r="D961" s="2"/>
-      <c r="E961" s="2"/>
-      <c r="F961" s="2"/>
-      <c r="G961" s="2"/>
-    </row>
-    <row r="962" ht="15.75" customHeight="1">
-      <c r="A962" s="2"/>
-      <c r="B962" s="2"/>
-      <c r="C962" s="2"/>
-      <c r="D962" s="2"/>
-      <c r="E962" s="2"/>
-      <c r="F962" s="2"/>
-      <c r="G962" s="2"/>
-    </row>
-    <row r="963" ht="15.75" customHeight="1">
-      <c r="A963" s="2"/>
-      <c r="B963" s="2"/>
-      <c r="C963" s="2"/>
-      <c r="D963" s="2"/>
-      <c r="E963" s="2"/>
-      <c r="F963" s="2"/>
-      <c r="G963" s="2"/>
-    </row>
-    <row r="964" ht="15.75" customHeight="1">
-      <c r="A964" s="2"/>
-      <c r="B964" s="2"/>
-      <c r="C964" s="2"/>
-      <c r="D964" s="2"/>
-      <c r="E964" s="2"/>
-      <c r="F964" s="2"/>
-      <c r="G964" s="2"/>
-    </row>
-    <row r="965" ht="15.75" customHeight="1">
-      <c r="A965" s="2"/>
-      <c r="B965" s="2"/>
-      <c r="C965" s="2"/>
-      <c r="D965" s="2"/>
-      <c r="E965" s="2"/>
-      <c r="F965" s="2"/>
-      <c r="G965" s="2"/>
-    </row>
-    <row r="966" ht="15.75" customHeight="1">
-      <c r="A966" s="2"/>
-      <c r="B966" s="2"/>
-      <c r="C966" s="2"/>
-      <c r="D966" s="2"/>
-      <c r="E966" s="2"/>
-      <c r="F966" s="2"/>
-      <c r="G966" s="2"/>
-    </row>
-    <row r="967" ht="15.75" customHeight="1">
-      <c r="A967" s="2"/>
-      <c r="B967" s="2"/>
-      <c r="C967" s="2"/>
-      <c r="D967" s="2"/>
-      <c r="E967" s="2"/>
-      <c r="F967" s="2"/>
-      <c r="G967" s="2"/>
-    </row>
-    <row r="968" ht="15.75" customHeight="1">
-      <c r="A968" s="2"/>
-      <c r="B968" s="2"/>
-      <c r="C968" s="2"/>
-      <c r="D968" s="2"/>
-      <c r="E968" s="2"/>
-      <c r="F968" s="2"/>
-      <c r="G968" s="2"/>
-    </row>
-    <row r="969" ht="15.75" customHeight="1">
-      <c r="A969" s="2"/>
-      <c r="B969" s="2"/>
-      <c r="C969" s="2"/>
-      <c r="D969" s="2"/>
-      <c r="E969" s="2"/>
-      <c r="F969" s="2"/>
-      <c r="G969" s="2"/>
-    </row>
-    <row r="970" ht="15.75" customHeight="1">
-      <c r="A970" s="2"/>
-      <c r="B970" s="2"/>
-      <c r="C970" s="2"/>
-      <c r="D970" s="2"/>
-      <c r="E970" s="2"/>
-      <c r="F970" s="2"/>
-      <c r="G970" s="2"/>
-    </row>
-    <row r="971" ht="15.75" customHeight="1">
-      <c r="A971" s="2"/>
-      <c r="B971" s="2"/>
-      <c r="C971" s="2"/>
-      <c r="D971" s="2"/>
-      <c r="E971" s="2"/>
-      <c r="F971" s="2"/>
-      <c r="G971" s="2"/>
-    </row>
-    <row r="972" ht="15.75" customHeight="1">
-      <c r="A972" s="2"/>
-      <c r="B972" s="2"/>
-      <c r="C972" s="2"/>
-      <c r="D972" s="2"/>
-      <c r="E972" s="2"/>
-      <c r="F972" s="2"/>
-      <c r="G972" s="2"/>
-    </row>
-    <row r="973" ht="15.75" customHeight="1">
-      <c r="A973" s="2"/>
-      <c r="B973" s="2"/>
-      <c r="C973" s="2"/>
-      <c r="D973" s="2"/>
-      <c r="E973" s="2"/>
-      <c r="F973" s="2"/>
-      <c r="G973" s="2"/>
-    </row>
-    <row r="974" ht="15.75" customHeight="1">
-      <c r="A974" s="2"/>
-      <c r="B974" s="2"/>
-      <c r="C974" s="2"/>
-      <c r="D974" s="2"/>
-      <c r="E974" s="2"/>
-      <c r="F974" s="2"/>
-      <c r="G974" s="2"/>
-    </row>
-    <row r="975" ht="15.75" customHeight="1">
-      <c r="A975" s="2"/>
-      <c r="B975" s="2"/>
-      <c r="C975" s="2"/>
-      <c r="D975" s="2"/>
-      <c r="E975" s="2"/>
-      <c r="F975" s="2"/>
-      <c r="G975" s="2"/>
-    </row>
-    <row r="976" ht="15.75" customHeight="1">
-      <c r="A976" s="2"/>
-      <c r="B976" s="2"/>
-      <c r="C976" s="2"/>
-      <c r="D976" s="2"/>
-      <c r="E976" s="2"/>
-      <c r="F976" s="2"/>
-      <c r="G976" s="2"/>
-    </row>
-    <row r="977" ht="15.75" customHeight="1">
-      <c r="A977" s="2"/>
-      <c r="B977" s="2"/>
-      <c r="C977" s="2"/>
-      <c r="D977" s="2"/>
-      <c r="E977" s="2"/>
-      <c r="F977" s="2"/>
-      <c r="G977" s="2"/>
-    </row>
-    <row r="978" ht="15.75" customHeight="1">
-      <c r="A978" s="2"/>
-      <c r="B978" s="2"/>
-      <c r="C978" s="2"/>
-      <c r="D978" s="2"/>
-      <c r="E978" s="2"/>
-      <c r="F978" s="2"/>
-      <c r="G978" s="2"/>
-    </row>
-    <row r="979" ht="15.75" customHeight="1">
-      <c r="A979" s="2"/>
-      <c r="B979" s="2"/>
-      <c r="C979" s="2"/>
-      <c r="D979" s="2"/>
-      <c r="E979" s="2"/>
-      <c r="F979" s="2"/>
-      <c r="G979" s="2"/>
-    </row>
-    <row r="980" ht="15.75" customHeight="1">
-      <c r="A980" s="2"/>
-      <c r="B980" s="2"/>
-      <c r="C980" s="2"/>
-      <c r="D980" s="2"/>
-      <c r="E980" s="2"/>
-      <c r="F980" s="2"/>
-      <c r="G980" s="2"/>
-    </row>
-    <row r="981" ht="15.75" customHeight="1">
-      <c r="A981" s="2"/>
-      <c r="B981" s="2"/>
-      <c r="C981" s="2"/>
-      <c r="D981" s="2"/>
-      <c r="E981" s="2"/>
-      <c r="F981" s="2"/>
-      <c r="G981" s="2"/>
-    </row>
-    <row r="982" ht="15.75" customHeight="1">
-      <c r="A982" s="2"/>
-      <c r="B982" s="2"/>
-      <c r="C982" s="2"/>
-      <c r="D982" s="2"/>
-      <c r="E982" s="2"/>
-      <c r="F982" s="2"/>
-      <c r="G982" s="2"/>
-    </row>
-    <row r="983" ht="15.75" customHeight="1">
-      <c r="A983" s="2"/>
-      <c r="B983" s="2"/>
-      <c r="C983" s="2"/>
-      <c r="D983" s="2"/>
-      <c r="E983" s="2"/>
-      <c r="F983" s="2"/>
-      <c r="G983" s="2"/>
-    </row>
-    <row r="984" ht="15.75" customHeight="1">
-      <c r="A984" s="2"/>
-      <c r="B984" s="2"/>
-      <c r="C984" s="2"/>
-      <c r="D984" s="2"/>
-      <c r="E984" s="2"/>
-      <c r="F984" s="2"/>
-      <c r="G984" s="2"/>
-    </row>
-    <row r="985" ht="15.75" customHeight="1">
-      <c r="A985" s="2"/>
-      <c r="B985" s="2"/>
-      <c r="C985" s="2"/>
-      <c r="D985" s="2"/>
-      <c r="E985" s="2"/>
-      <c r="F985" s="2"/>
-      <c r="G985" s="2"/>
-    </row>
-    <row r="986" ht="15.75" customHeight="1">
-      <c r="A986" s="2"/>
-      <c r="B986" s="2"/>
-      <c r="C986" s="2"/>
-      <c r="D986" s="2"/>
-      <c r="E986" s="2"/>
-      <c r="F986" s="2"/>
-      <c r="G986" s="2"/>
-    </row>
-    <row r="987" ht="15.75" customHeight="1">
-      <c r="A987" s="2"/>
-      <c r="B987" s="2"/>
-      <c r="C987" s="2"/>
-      <c r="D987" s="2"/>
-      <c r="E987" s="2"/>
-      <c r="F987" s="2"/>
-      <c r="G987" s="2"/>
-    </row>
-    <row r="988" ht="15.75" customHeight="1">
-      <c r="A988" s="2"/>
-      <c r="B988" s="2"/>
-      <c r="C988" s="2"/>
-      <c r="D988" s="2"/>
-      <c r="E988" s="2"/>
-      <c r="F988" s="2"/>
-      <c r="G988" s="2"/>
-    </row>
-    <row r="989" ht="15.75" customHeight="1">
-      <c r="A989" s="2"/>
-      <c r="B989" s="2"/>
-      <c r="C989" s="2"/>
-      <c r="D989" s="2"/>
-      <c r="E989" s="2"/>
-      <c r="F989" s="2"/>
-      <c r="G989" s="2"/>
-    </row>
-    <row r="990" ht="15.75" customHeight="1">
-      <c r="A990" s="2"/>
-      <c r="B990" s="2"/>
-      <c r="C990" s="2"/>
-      <c r="D990" s="2"/>
-      <c r="E990" s="2"/>
-      <c r="F990" s="2"/>
-      <c r="G990" s="2"/>
-    </row>
-    <row r="991" ht="15.75" customHeight="1">
-      <c r="A991" s="2"/>
-      <c r="B991" s="2"/>
-      <c r="C991" s="2"/>
-      <c r="D991" s="2"/>
-      <c r="E991" s="2"/>
-      <c r="F991" s="2"/>
-      <c r="G991" s="2"/>
-    </row>
-    <row r="992" ht="15.75" customHeight="1">
-      <c r="A992" s="2"/>
-      <c r="B992" s="2"/>
-      <c r="C992" s="2"/>
-      <c r="D992" s="2"/>
-      <c r="E992" s="2"/>
-      <c r="F992" s="2"/>
-      <c r="G992" s="2"/>
-    </row>
-    <row r="993" ht="15.75" customHeight="1">
-      <c r="A993" s="2"/>
-      <c r="B993" s="2"/>
-      <c r="C993" s="2"/>
-      <c r="D993" s="2"/>
-      <c r="E993" s="2"/>
-      <c r="F993" s="2"/>
-      <c r="G993" s="2"/>
-    </row>
-    <row r="994" ht="15.75" customHeight="1">
-      <c r="A994" s="2"/>
-      <c r="B994" s="2"/>
-      <c r="C994" s="2"/>
-      <c r="D994" s="2"/>
-      <c r="E994" s="2"/>
-      <c r="F994" s="2"/>
-      <c r="G994" s="2"/>
-    </row>
-    <row r="995" ht="15.75" customHeight="1">
-      <c r="A995" s="2"/>
-      <c r="B995" s="2"/>
-      <c r="C995" s="2"/>
-      <c r="D995" s="2"/>
-      <c r="E995" s="2"/>
-      <c r="F995" s="2"/>
-      <c r="G995" s="2"/>
-    </row>
-    <row r="996" ht="15.75" customHeight="1">
-      <c r="A996" s="2"/>
-      <c r="B996" s="2"/>
-      <c r="C996" s="2"/>
-      <c r="D996" s="2"/>
-      <c r="E996" s="2"/>
-      <c r="F996" s="2"/>
-      <c r="G996" s="2"/>
-    </row>
-    <row r="997" ht="15.75" customHeight="1">
-      <c r="A997" s="2"/>
-      <c r="B997" s="2"/>
-      <c r="C997" s="2"/>
-      <c r="D997" s="2"/>
-      <c r="E997" s="2"/>
-      <c r="F997" s="2"/>
-      <c r="G997" s="2"/>
-    </row>
-    <row r="998" ht="15.75" customHeight="1">
-      <c r="A998" s="2"/>
-      <c r="B998" s="2"/>
-      <c r="C998" s="2"/>
-      <c r="D998" s="2"/>
-      <c r="E998" s="2"/>
-      <c r="F998" s="2"/>
-      <c r="G998" s="2"/>
-    </row>
-    <row r="999" ht="15.75" customHeight="1">
-      <c r="A999" s="2"/>
-      <c r="B999" s="2"/>
-      <c r="C999" s="2"/>
-      <c r="D999" s="2"/>
-      <c r="E999" s="2"/>
-      <c r="F999" s="2"/>
-      <c r="G999" s="2"/>
-    </row>
-    <row r="1000" ht="15.75" customHeight="1">
-      <c r="A1000" s="2"/>
-      <c r="B1000" s="2"/>
-      <c r="C1000" s="2"/>
-      <c r="D1000" s="2"/>
-      <c r="E1000" s="2"/>
-      <c r="F1000" s="2"/>
-      <c r="G1000" s="2"/>
-    </row>
   </sheetData>
-  <autoFilter ref="$A$1:$G$49"/>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>

--- a/ΕΥΑΓΓΕΛΙΖΟΜΕΝΟΙ.xlsx
+++ b/ΕΥΑΓΓΕΛΙΖΟΜΕΝΟΙ.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="TatrjW3kLCmVr1a+WBmaXxpZdL+hLfrS13V+GIzWn04="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="T82blOwtly4NzMmjWIv2MNiYcBjU47KnGmCPptrFg60="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>publisher</t>
   </si>
@@ -39,6 +39,9 @@
     <t>Email</t>
   </si>
   <si>
+    <t>Password</t>
+  </si>
+  <si>
     <t>Σμυρνόπουλος Στέφανος</t>
   </si>
   <si>
@@ -55,6 +58,9 @@
   </si>
   <si>
     <t>smyrnopoulos@gmail.com</t>
+  </si>
+  <si>
+    <t>251219912@</t>
   </si>
 </sst>
 </file>
@@ -102,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -110,6 +116,10 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -324,7 +334,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="7" width="28.57"/>
+    <col customWidth="1" min="1" max="8" width="28.57"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -349,28 +359,34 @@
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>10</v>
+      <c r="G2" s="2" t="s">
+        <v>13</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>12</v>
+      <c r="H2" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
@@ -381,6 +397,7 @@
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
+      <c r="H3" s="4"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="2"/>
@@ -390,6 +407,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
+      <c r="H4" s="4"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="2"/>
@@ -399,6 +417,7 @@
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
+      <c r="H5" s="4"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="2"/>
@@ -408,6 +427,7 @@
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
+      <c r="H6" s="4"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="2"/>
@@ -417,6 +437,7 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
+      <c r="H7" s="4"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="2"/>
@@ -426,6 +447,7 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
+      <c r="H8" s="4"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="2"/>
@@ -435,6 +457,7 @@
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
+      <c r="H9" s="4"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="2"/>
@@ -444,6 +467,7 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
+      <c r="H10" s="4"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="2"/>
@@ -453,6 +477,7 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
+      <c r="H11" s="4"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="2"/>
@@ -462,6 +487,7 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
+      <c r="H12" s="4"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="2"/>
@@ -471,6 +497,7 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
+      <c r="H13" s="4"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="2"/>
@@ -480,6 +507,7 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
+      <c r="H14" s="4"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="2"/>
@@ -489,6 +517,7 @@
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
+      <c r="H15" s="4"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="2"/>
@@ -498,6 +527,7 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
+      <c r="H16" s="4"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="2"/>
@@ -507,6 +537,7 @@
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
+      <c r="H17" s="4"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="2"/>
@@ -516,6 +547,7 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
+      <c r="H18" s="4"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="2"/>
@@ -525,6 +557,7 @@
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
+      <c r="H19" s="4"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="2"/>
@@ -534,6 +567,7 @@
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
+      <c r="H20" s="4"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2"/>
@@ -543,6 +577,7 @@
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
+      <c r="H21" s="4"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2"/>
@@ -552,6 +587,7 @@
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
+      <c r="H22" s="4"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2"/>
@@ -561,6 +597,7 @@
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
+      <c r="H23" s="4"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="2"/>
@@ -570,6 +607,7 @@
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
+      <c r="H24" s="4"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="2"/>
@@ -579,6 +617,7 @@
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
+      <c r="H25" s="4"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="2"/>
@@ -588,6 +627,7 @@
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
+      <c r="H26" s="4"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="2"/>
@@ -597,6 +637,7 @@
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
+      <c r="H27" s="4"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2"/>
@@ -606,6 +647,7 @@
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
+      <c r="H28" s="4"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="2"/>
@@ -615,6 +657,7 @@
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
+      <c r="H29" s="4"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="2"/>
@@ -624,6 +667,7 @@
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
+      <c r="H30" s="4"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="2"/>
@@ -633,6 +677,7 @@
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
+      <c r="H31" s="4"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="2"/>
@@ -642,6 +687,7 @@
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
+      <c r="H32" s="4"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="2"/>
@@ -651,6 +697,7 @@
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
+      <c r="H33" s="4"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="2"/>
@@ -660,6 +707,7 @@
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
+      <c r="H34" s="4"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="2"/>
@@ -669,6 +717,7 @@
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
+      <c r="H35" s="4"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="2"/>
@@ -678,6 +727,7 @@
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
+      <c r="H36" s="4"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="2"/>
@@ -687,6 +737,7 @@
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
+      <c r="H37" s="4"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="2"/>
@@ -696,6 +747,7 @@
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
+      <c r="H38" s="4"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="2"/>
@@ -705,6 +757,7 @@
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
       <c r="G39" s="2"/>
+      <c r="H39" s="4"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="2"/>
@@ -714,6 +767,7 @@
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
       <c r="G40" s="2"/>
+      <c r="H40" s="4"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="2"/>
@@ -723,6 +777,7 @@
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
       <c r="G41" s="2"/>
+      <c r="H41" s="4"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="2"/>
@@ -732,6 +787,7 @@
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
+      <c r="H42" s="4"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="2"/>
@@ -741,6 +797,7 @@
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
+      <c r="H43" s="4"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="2"/>
@@ -750,6 +807,7 @@
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
+      <c r="H44" s="4"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="2"/>
@@ -759,6 +817,7 @@
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
       <c r="G45" s="2"/>
+      <c r="H45" s="4"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="2"/>
@@ -768,6 +827,7 @@
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
+      <c r="H46" s="4"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="2"/>
@@ -777,6 +837,7 @@
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
+      <c r="H47" s="4"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="2"/>
@@ -786,6 +847,7 @@
       <c r="E48" s="2"/>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
+      <c r="H48" s="4"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="2"/>
@@ -795,6 +857,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
+      <c r="H49" s="4"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="2"/>
@@ -804,6 +867,7 @@
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
+      <c r="H50" s="4"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="2"/>
@@ -813,6 +877,7 @@
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
+      <c r="H51" s="4"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="2"/>
@@ -822,6 +887,7 @@
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
+      <c r="H52" s="4"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="2"/>
@@ -831,6 +897,7 @@
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
+      <c r="H53" s="4"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="2"/>
@@ -840,6 +907,7 @@
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
+      <c r="H54" s="4"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="2"/>
@@ -849,6 +917,7 @@
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
+      <c r="H55" s="4"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="2"/>
@@ -858,6 +927,7 @@
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
+      <c r="H56" s="4"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="2"/>
@@ -867,6 +937,7 @@
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
+      <c r="H57" s="4"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="2"/>
@@ -876,6 +947,7 @@
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
+      <c r="H58" s="4"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="2"/>
@@ -885,6 +957,7 @@
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
+      <c r="H59" s="4"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="2"/>
@@ -894,6 +967,7 @@
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
+      <c r="H60" s="4"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="2"/>
@@ -903,6 +977,7 @@
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
+      <c r="H61" s="4"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="2"/>
@@ -912,6 +987,7 @@
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
+      <c r="H62" s="4"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="2"/>
@@ -921,6 +997,7 @@
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
+      <c r="H63" s="4"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="2"/>
@@ -930,6 +1007,7 @@
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
+      <c r="H64" s="4"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="2"/>
@@ -939,6 +1017,7 @@
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
+      <c r="H65" s="4"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="2"/>
@@ -948,6 +1027,7 @@
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
+      <c r="H66" s="4"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="2"/>
@@ -957,6 +1037,7 @@
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
+      <c r="H67" s="4"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="2"/>
@@ -966,6 +1047,7 @@
       <c r="E68" s="2"/>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
+      <c r="H68" s="4"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="2"/>
@@ -975,6 +1057,7 @@
       <c r="E69" s="2"/>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
+      <c r="H69" s="4"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="2"/>
@@ -984,6 +1067,7 @@
       <c r="E70" s="2"/>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
+      <c r="H70" s="4"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="2"/>
@@ -993,6 +1077,7 @@
       <c r="E71" s="2"/>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
+      <c r="H71" s="4"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="2"/>
@@ -1002,6 +1087,7 @@
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
+      <c r="H72" s="4"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="2"/>
@@ -1011,6 +1097,7 @@
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
+      <c r="H73" s="4"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="2"/>
@@ -1020,6 +1107,7 @@
       <c r="E74" s="2"/>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
+      <c r="H74" s="4"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="2"/>
@@ -1029,6 +1117,7 @@
       <c r="E75" s="2"/>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
+      <c r="H75" s="4"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="2"/>
@@ -1038,6 +1127,7 @@
       <c r="E76" s="2"/>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
+      <c r="H76" s="4"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="2"/>
@@ -1047,6 +1137,7 @@
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
+      <c r="H77" s="4"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="2"/>
@@ -1056,6 +1147,7 @@
       <c r="E78" s="2"/>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
+      <c r="H78" s="4"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="2"/>
@@ -1065,6 +1157,7 @@
       <c r="E79" s="2"/>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
+      <c r="H79" s="4"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="2"/>
@@ -1074,6 +1167,7 @@
       <c r="E80" s="2"/>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
+      <c r="H80" s="4"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="2"/>
@@ -1083,6 +1177,7 @@
       <c r="E81" s="2"/>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
+      <c r="H81" s="4"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="2"/>
@@ -1092,6 +1187,7 @@
       <c r="E82" s="2"/>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
+      <c r="H82" s="4"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="2"/>
@@ -1101,6 +1197,7 @@
       <c r="E83" s="2"/>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
+      <c r="H83" s="4"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="2"/>
@@ -1110,6 +1207,7 @@
       <c r="E84" s="2"/>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
+      <c r="H84" s="4"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="2"/>
@@ -1119,6 +1217,7 @@
       <c r="E85" s="2"/>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
+      <c r="H85" s="4"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="2"/>
@@ -1128,6 +1227,7 @@
       <c r="E86" s="2"/>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
+      <c r="H86" s="4"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="2"/>
@@ -1137,6 +1237,7 @@
       <c r="E87" s="2"/>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
+      <c r="H87" s="4"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="2"/>
@@ -1146,6 +1247,7 @@
       <c r="E88" s="2"/>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
+      <c r="H88" s="4"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="2"/>
@@ -1155,6 +1257,7 @@
       <c r="E89" s="2"/>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
+      <c r="H89" s="4"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="2"/>
@@ -1164,6 +1267,7 @@
       <c r="E90" s="2"/>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
+      <c r="H90" s="4"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="2"/>
@@ -1173,6 +1277,7 @@
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
+      <c r="H91" s="4"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="2"/>
@@ -1182,6 +1287,7 @@
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
+      <c r="H92" s="4"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="2"/>
@@ -1191,6 +1297,7 @@
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
+      <c r="H93" s="4"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="2"/>
@@ -1200,6 +1307,7 @@
       <c r="E94" s="2"/>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
+      <c r="H94" s="4"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="2"/>
@@ -1209,6 +1317,7 @@
       <c r="E95" s="2"/>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
+      <c r="H95" s="4"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="2"/>
@@ -1218,6 +1327,7 @@
       <c r="E96" s="2"/>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
+      <c r="H96" s="4"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="2"/>
@@ -1227,6 +1337,7 @@
       <c r="E97" s="2"/>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
+      <c r="H97" s="4"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="2"/>
@@ -1236,6 +1347,7 @@
       <c r="E98" s="2"/>
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
+      <c r="H98" s="4"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="2"/>
@@ -1245,6 +1357,7 @@
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
+      <c r="H99" s="4"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="2"/>
@@ -1254,6 +1367,7 @@
       <c r="E100" s="2"/>
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
+      <c r="H100" s="4"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="2"/>
@@ -1263,6 +1377,7 @@
       <c r="E101" s="2"/>
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
+      <c r="H101" s="4"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="2"/>
@@ -1272,6 +1387,7 @@
       <c r="E102" s="2"/>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
+      <c r="H102" s="4"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="2"/>
@@ -1281,6 +1397,7 @@
       <c r="E103" s="2"/>
       <c r="F103" s="2"/>
       <c r="G103" s="2"/>
+      <c r="H103" s="4"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="2"/>
@@ -1290,6 +1407,7 @@
       <c r="E104" s="2"/>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
+      <c r="H104" s="4"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="2"/>
@@ -1299,6 +1417,7 @@
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
+      <c r="H105" s="4"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="2"/>
@@ -1308,6 +1427,7 @@
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
+      <c r="H106" s="4"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="2"/>
@@ -1317,6 +1437,7 @@
       <c r="E107" s="2"/>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
+      <c r="H107" s="4"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="2"/>
@@ -1326,6 +1447,7 @@
       <c r="E108" s="2"/>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
+      <c r="H108" s="4"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="2"/>
@@ -1335,6 +1457,7 @@
       <c r="E109" s="2"/>
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
+      <c r="H109" s="4"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="2"/>
@@ -1344,6 +1467,7 @@
       <c r="E110" s="2"/>
       <c r="F110" s="2"/>
       <c r="G110" s="2"/>
+      <c r="H110" s="4"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="2"/>
@@ -1353,6 +1477,7 @@
       <c r="E111" s="2"/>
       <c r="F111" s="2"/>
       <c r="G111" s="2"/>
+      <c r="H111" s="4"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="2"/>
@@ -1362,6 +1487,7 @@
       <c r="E112" s="2"/>
       <c r="F112" s="2"/>
       <c r="G112" s="2"/>
+      <c r="H112" s="4"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="2"/>
@@ -1371,6 +1497,7 @@
       <c r="E113" s="2"/>
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
+      <c r="H113" s="4"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="2"/>
@@ -1380,6 +1507,7 @@
       <c r="E114" s="2"/>
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
+      <c r="H114" s="4"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="2"/>
@@ -1389,6 +1517,7 @@
       <c r="E115" s="2"/>
       <c r="F115" s="2"/>
       <c r="G115" s="2"/>
+      <c r="H115" s="4"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="2"/>
@@ -1398,6 +1527,7 @@
       <c r="E116" s="2"/>
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
+      <c r="H116" s="4"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="2"/>
@@ -1407,6 +1537,7 @@
       <c r="E117" s="2"/>
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
+      <c r="H117" s="4"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="2"/>
@@ -1416,6 +1547,7 @@
       <c r="E118" s="2"/>
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
+      <c r="H118" s="4"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="2"/>
@@ -1425,6 +1557,7 @@
       <c r="E119" s="2"/>
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
+      <c r="H119" s="4"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="2"/>
@@ -1434,6 +1567,7 @@
       <c r="E120" s="2"/>
       <c r="F120" s="2"/>
       <c r="G120" s="2"/>
+      <c r="H120" s="4"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="2"/>
@@ -1443,6 +1577,7 @@
       <c r="E121" s="2"/>
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
+      <c r="H121" s="4"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="2"/>
@@ -1452,6 +1587,7 @@
       <c r="E122" s="2"/>
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
+      <c r="H122" s="4"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="2"/>
@@ -1461,6 +1597,7 @@
       <c r="E123" s="2"/>
       <c r="F123" s="2"/>
       <c r="G123" s="2"/>
+      <c r="H123" s="4"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="2"/>
@@ -1470,6 +1607,7 @@
       <c r="E124" s="2"/>
       <c r="F124" s="2"/>
       <c r="G124" s="2"/>
+      <c r="H124" s="4"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="2"/>
@@ -1479,6 +1617,7 @@
       <c r="E125" s="2"/>
       <c r="F125" s="2"/>
       <c r="G125" s="2"/>
+      <c r="H125" s="4"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="2"/>
@@ -1488,6 +1627,7 @@
       <c r="E126" s="2"/>
       <c r="F126" s="2"/>
       <c r="G126" s="2"/>
+      <c r="H126" s="4"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="2"/>
@@ -1497,6 +1637,7 @@
       <c r="E127" s="2"/>
       <c r="F127" s="2"/>
       <c r="G127" s="2"/>
+      <c r="H127" s="4"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="2"/>
@@ -1506,6 +1647,7 @@
       <c r="E128" s="2"/>
       <c r="F128" s="2"/>
       <c r="G128" s="2"/>
+      <c r="H128" s="4"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="2"/>
@@ -1515,6 +1657,7 @@
       <c r="E129" s="2"/>
       <c r="F129" s="2"/>
       <c r="G129" s="2"/>
+      <c r="H129" s="4"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="2"/>
@@ -1524,6 +1667,7 @@
       <c r="E130" s="2"/>
       <c r="F130" s="2"/>
       <c r="G130" s="2"/>
+      <c r="H130" s="4"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="2"/>
@@ -1533,6 +1677,7 @@
       <c r="E131" s="2"/>
       <c r="F131" s="2"/>
       <c r="G131" s="2"/>
+      <c r="H131" s="4"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="2"/>
@@ -1542,6 +1687,7 @@
       <c r="E132" s="2"/>
       <c r="F132" s="2"/>
       <c r="G132" s="2"/>
+      <c r="H132" s="4"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="2"/>
@@ -1551,6 +1697,7 @@
       <c r="E133" s="2"/>
       <c r="F133" s="2"/>
       <c r="G133" s="2"/>
+      <c r="H133" s="4"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="2"/>
@@ -1560,6 +1707,7 @@
       <c r="E134" s="2"/>
       <c r="F134" s="2"/>
       <c r="G134" s="2"/>
+      <c r="H134" s="4"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="2"/>
@@ -1569,6 +1717,7 @@
       <c r="E135" s="2"/>
       <c r="F135" s="2"/>
       <c r="G135" s="2"/>
+      <c r="H135" s="4"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="2"/>
@@ -1578,6 +1727,7 @@
       <c r="E136" s="2"/>
       <c r="F136" s="2"/>
       <c r="G136" s="2"/>
+      <c r="H136" s="4"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="2"/>
@@ -1587,6 +1737,7 @@
       <c r="E137" s="2"/>
       <c r="F137" s="2"/>
       <c r="G137" s="2"/>
+      <c r="H137" s="4"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="2"/>
@@ -1596,6 +1747,7 @@
       <c r="E138" s="2"/>
       <c r="F138" s="2"/>
       <c r="G138" s="2"/>
+      <c r="H138" s="4"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="2"/>
@@ -1605,6 +1757,7 @@
       <c r="E139" s="2"/>
       <c r="F139" s="2"/>
       <c r="G139" s="2"/>
+      <c r="H139" s="4"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="2"/>
@@ -1614,6 +1767,7 @@
       <c r="E140" s="2"/>
       <c r="F140" s="2"/>
       <c r="G140" s="2"/>
+      <c r="H140" s="4"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="2"/>
@@ -1623,6 +1777,7 @@
       <c r="E141" s="2"/>
       <c r="F141" s="2"/>
       <c r="G141" s="2"/>
+      <c r="H141" s="4"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="2"/>
@@ -1632,6 +1787,7 @@
       <c r="E142" s="2"/>
       <c r="F142" s="2"/>
       <c r="G142" s="2"/>
+      <c r="H142" s="4"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="2"/>
@@ -1641,6 +1797,7 @@
       <c r="E143" s="2"/>
       <c r="F143" s="2"/>
       <c r="G143" s="2"/>
+      <c r="H143" s="4"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="2"/>
@@ -1650,6 +1807,7 @@
       <c r="E144" s="2"/>
       <c r="F144" s="2"/>
       <c r="G144" s="2"/>
+      <c r="H144" s="4"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="2"/>
@@ -1659,6 +1817,7 @@
       <c r="E145" s="2"/>
       <c r="F145" s="2"/>
       <c r="G145" s="2"/>
+      <c r="H145" s="4"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="2"/>
@@ -1668,6 +1827,7 @@
       <c r="E146" s="2"/>
       <c r="F146" s="2"/>
       <c r="G146" s="2"/>
+      <c r="H146" s="4"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="2"/>
@@ -1677,6 +1837,7 @@
       <c r="E147" s="2"/>
       <c r="F147" s="2"/>
       <c r="G147" s="2"/>
+      <c r="H147" s="4"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="2"/>
@@ -1686,6 +1847,7 @@
       <c r="E148" s="2"/>
       <c r="F148" s="2"/>
       <c r="G148" s="2"/>
+      <c r="H148" s="4"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="2"/>
@@ -1695,6 +1857,7 @@
       <c r="E149" s="2"/>
       <c r="F149" s="2"/>
       <c r="G149" s="2"/>
+      <c r="H149" s="4"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="2"/>
@@ -1704,6 +1867,7 @@
       <c r="E150" s="2"/>
       <c r="F150" s="2"/>
       <c r="G150" s="2"/>
+      <c r="H150" s="4"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="2"/>
@@ -1713,6 +1877,7 @@
       <c r="E151" s="2"/>
       <c r="F151" s="2"/>
       <c r="G151" s="2"/>
+      <c r="H151" s="4"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="2"/>
@@ -1722,6 +1887,7 @@
       <c r="E152" s="2"/>
       <c r="F152" s="2"/>
       <c r="G152" s="2"/>
+      <c r="H152" s="4"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="2"/>
@@ -1731,6 +1897,7 @@
       <c r="E153" s="2"/>
       <c r="F153" s="2"/>
       <c r="G153" s="2"/>
+      <c r="H153" s="4"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="2"/>
@@ -1740,6 +1907,7 @@
       <c r="E154" s="2"/>
       <c r="F154" s="2"/>
       <c r="G154" s="2"/>
+      <c r="H154" s="4"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="2"/>
@@ -1749,6 +1917,7 @@
       <c r="E155" s="2"/>
       <c r="F155" s="2"/>
       <c r="G155" s="2"/>
+      <c r="H155" s="4"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="2"/>
@@ -1758,6 +1927,7 @@
       <c r="E156" s="2"/>
       <c r="F156" s="2"/>
       <c r="G156" s="2"/>
+      <c r="H156" s="4"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="2"/>
@@ -1767,6 +1937,7 @@
       <c r="E157" s="2"/>
       <c r="F157" s="2"/>
       <c r="G157" s="2"/>
+      <c r="H157" s="4"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="2"/>
@@ -1776,6 +1947,7 @@
       <c r="E158" s="2"/>
       <c r="F158" s="2"/>
       <c r="G158" s="2"/>
+      <c r="H158" s="4"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="2"/>
@@ -1785,6 +1957,7 @@
       <c r="E159" s="2"/>
       <c r="F159" s="2"/>
       <c r="G159" s="2"/>
+      <c r="H159" s="4"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="2"/>
@@ -1794,6 +1967,7 @@
       <c r="E160" s="2"/>
       <c r="F160" s="2"/>
       <c r="G160" s="2"/>
+      <c r="H160" s="4"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="2"/>
@@ -1803,6 +1977,7 @@
       <c r="E161" s="2"/>
       <c r="F161" s="2"/>
       <c r="G161" s="2"/>
+      <c r="H161" s="4"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="2"/>
@@ -1812,6 +1987,7 @@
       <c r="E162" s="2"/>
       <c r="F162" s="2"/>
       <c r="G162" s="2"/>
+      <c r="H162" s="4"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="2"/>
@@ -1821,6 +1997,7 @@
       <c r="E163" s="2"/>
       <c r="F163" s="2"/>
       <c r="G163" s="2"/>
+      <c r="H163" s="4"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="2"/>
@@ -1830,6 +2007,7 @@
       <c r="E164" s="2"/>
       <c r="F164" s="2"/>
       <c r="G164" s="2"/>
+      <c r="H164" s="4"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="2"/>
@@ -1839,6 +2017,7 @@
       <c r="E165" s="2"/>
       <c r="F165" s="2"/>
       <c r="G165" s="2"/>
+      <c r="H165" s="4"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="2"/>
@@ -1848,6 +2027,7 @@
       <c r="E166" s="2"/>
       <c r="F166" s="2"/>
       <c r="G166" s="2"/>
+      <c r="H166" s="4"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="2"/>
@@ -1857,6 +2037,7 @@
       <c r="E167" s="2"/>
       <c r="F167" s="2"/>
       <c r="G167" s="2"/>
+      <c r="H167" s="4"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="2"/>
@@ -1866,6 +2047,7 @@
       <c r="E168" s="2"/>
       <c r="F168" s="2"/>
       <c r="G168" s="2"/>
+      <c r="H168" s="4"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="2"/>
@@ -1875,6 +2057,7 @@
       <c r="E169" s="2"/>
       <c r="F169" s="2"/>
       <c r="G169" s="2"/>
+      <c r="H169" s="4"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="2"/>
@@ -1884,6 +2067,7 @@
       <c r="E170" s="2"/>
       <c r="F170" s="2"/>
       <c r="G170" s="2"/>
+      <c r="H170" s="4"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="2"/>
@@ -1893,6 +2077,7 @@
       <c r="E171" s="2"/>
       <c r="F171" s="2"/>
       <c r="G171" s="2"/>
+      <c r="H171" s="4"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
       <c r="A172" s="2"/>
@@ -1902,6 +2087,7 @@
       <c r="E172" s="2"/>
       <c r="F172" s="2"/>
       <c r="G172" s="2"/>
+      <c r="H172" s="4"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="2"/>
@@ -1911,6 +2097,7 @@
       <c r="E173" s="2"/>
       <c r="F173" s="2"/>
       <c r="G173" s="2"/>
+      <c r="H173" s="4"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="2"/>
@@ -1920,6 +2107,7 @@
       <c r="E174" s="2"/>
       <c r="F174" s="2"/>
       <c r="G174" s="2"/>
+      <c r="H174" s="4"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
       <c r="A175" s="2"/>
@@ -1929,6 +2117,7 @@
       <c r="E175" s="2"/>
       <c r="F175" s="2"/>
       <c r="G175" s="2"/>
+      <c r="H175" s="4"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="2"/>
@@ -1938,6 +2127,7 @@
       <c r="E176" s="2"/>
       <c r="F176" s="2"/>
       <c r="G176" s="2"/>
+      <c r="H176" s="4"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
       <c r="A177" s="2"/>
@@ -1947,6 +2137,7 @@
       <c r="E177" s="2"/>
       <c r="F177" s="2"/>
       <c r="G177" s="2"/>
+      <c r="H177" s="4"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="2"/>
@@ -1956,6 +2147,7 @@
       <c r="E178" s="2"/>
       <c r="F178" s="2"/>
       <c r="G178" s="2"/>
+      <c r="H178" s="4"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
       <c r="A179" s="2"/>
@@ -1965,6 +2157,7 @@
       <c r="E179" s="2"/>
       <c r="F179" s="2"/>
       <c r="G179" s="2"/>
+      <c r="H179" s="4"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
       <c r="A180" s="2"/>
@@ -1974,6 +2167,7 @@
       <c r="E180" s="2"/>
       <c r="F180" s="2"/>
       <c r="G180" s="2"/>
+      <c r="H180" s="4"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="2"/>
@@ -1983,6 +2177,7 @@
       <c r="E181" s="2"/>
       <c r="F181" s="2"/>
       <c r="G181" s="2"/>
+      <c r="H181" s="4"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="2"/>
@@ -1992,6 +2187,7 @@
       <c r="E182" s="2"/>
       <c r="F182" s="2"/>
       <c r="G182" s="2"/>
+      <c r="H182" s="4"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
       <c r="A183" s="2"/>
@@ -2001,6 +2197,7 @@
       <c r="E183" s="2"/>
       <c r="F183" s="2"/>
       <c r="G183" s="2"/>
+      <c r="H183" s="4"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
       <c r="A184" s="2"/>
@@ -2010,6 +2207,7 @@
       <c r="E184" s="2"/>
       <c r="F184" s="2"/>
       <c r="G184" s="2"/>
+      <c r="H184" s="4"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="2"/>
@@ -2019,6 +2217,7 @@
       <c r="E185" s="2"/>
       <c r="F185" s="2"/>
       <c r="G185" s="2"/>
+      <c r="H185" s="4"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
       <c r="A186" s="2"/>
@@ -2028,6 +2227,7 @@
       <c r="E186" s="2"/>
       <c r="F186" s="2"/>
       <c r="G186" s="2"/>
+      <c r="H186" s="4"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="2"/>
@@ -2037,6 +2237,7 @@
       <c r="E187" s="2"/>
       <c r="F187" s="2"/>
       <c r="G187" s="2"/>
+      <c r="H187" s="4"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
       <c r="A188" s="2"/>
@@ -2046,6 +2247,7 @@
       <c r="E188" s="2"/>
       <c r="F188" s="2"/>
       <c r="G188" s="2"/>
+      <c r="H188" s="4"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
       <c r="A189" s="2"/>
@@ -2055,6 +2257,7 @@
       <c r="E189" s="2"/>
       <c r="F189" s="2"/>
       <c r="G189" s="2"/>
+      <c r="H189" s="4"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="2"/>
@@ -2064,6 +2267,7 @@
       <c r="E190" s="2"/>
       <c r="F190" s="2"/>
       <c r="G190" s="2"/>
+      <c r="H190" s="4"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
       <c r="A191" s="2"/>
@@ -2073,6 +2277,7 @@
       <c r="E191" s="2"/>
       <c r="F191" s="2"/>
       <c r="G191" s="2"/>
+      <c r="H191" s="4"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
       <c r="A192" s="2"/>
@@ -2082,6 +2287,7 @@
       <c r="E192" s="2"/>
       <c r="F192" s="2"/>
       <c r="G192" s="2"/>
+      <c r="H192" s="4"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
       <c r="A193" s="2"/>
@@ -2091,6 +2297,7 @@
       <c r="E193" s="2"/>
       <c r="F193" s="2"/>
       <c r="G193" s="2"/>
+      <c r="H193" s="4"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
       <c r="A194" s="2"/>
@@ -2100,6 +2307,7 @@
       <c r="E194" s="2"/>
       <c r="F194" s="2"/>
       <c r="G194" s="2"/>
+      <c r="H194" s="4"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
       <c r="A195" s="2"/>
@@ -2109,6 +2317,7 @@
       <c r="E195" s="2"/>
       <c r="F195" s="2"/>
       <c r="G195" s="2"/>
+      <c r="H195" s="4"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
       <c r="A196" s="2"/>
@@ -2118,6 +2327,7 @@
       <c r="E196" s="2"/>
       <c r="F196" s="2"/>
       <c r="G196" s="2"/>
+      <c r="H196" s="4"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
       <c r="A197" s="2"/>
@@ -2127,6 +2337,7 @@
       <c r="E197" s="2"/>
       <c r="F197" s="2"/>
       <c r="G197" s="2"/>
+      <c r="H197" s="4"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
       <c r="A198" s="2"/>
@@ -2136,6 +2347,7 @@
       <c r="E198" s="2"/>
       <c r="F198" s="2"/>
       <c r="G198" s="2"/>
+      <c r="H198" s="4"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
       <c r="A199" s="2"/>
@@ -2145,6 +2357,7 @@
       <c r="E199" s="2"/>
       <c r="F199" s="2"/>
       <c r="G199" s="2"/>
+      <c r="H199" s="4"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
       <c r="A200" s="2"/>
@@ -2154,6 +2367,7 @@
       <c r="E200" s="2"/>
       <c r="F200" s="2"/>
       <c r="G200" s="2"/>
+      <c r="H200" s="4"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
       <c r="A201" s="2"/>
@@ -2163,6 +2377,7 @@
       <c r="E201" s="2"/>
       <c r="F201" s="2"/>
       <c r="G201" s="2"/>
+      <c r="H201" s="4"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
       <c r="A202" s="2"/>
@@ -2172,6 +2387,7 @@
       <c r="E202" s="2"/>
       <c r="F202" s="2"/>
       <c r="G202" s="2"/>
+      <c r="H202" s="4"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
       <c r="A203" s="2"/>
@@ -2181,6 +2397,7 @@
       <c r="E203" s="2"/>
       <c r="F203" s="2"/>
       <c r="G203" s="2"/>
+      <c r="H203" s="4"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
       <c r="A204" s="2"/>
@@ -2190,6 +2407,7 @@
       <c r="E204" s="2"/>
       <c r="F204" s="2"/>
       <c r="G204" s="2"/>
+      <c r="H204" s="4"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
       <c r="A205" s="2"/>
@@ -2199,6 +2417,7 @@
       <c r="E205" s="2"/>
       <c r="F205" s="2"/>
       <c r="G205" s="2"/>
+      <c r="H205" s="4"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
       <c r="A206" s="2"/>
@@ -2208,6 +2427,7 @@
       <c r="E206" s="2"/>
       <c r="F206" s="2"/>
       <c r="G206" s="2"/>
+      <c r="H206" s="4"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
       <c r="A207" s="2"/>
@@ -2217,6 +2437,7 @@
       <c r="E207" s="2"/>
       <c r="F207" s="2"/>
       <c r="G207" s="2"/>
+      <c r="H207" s="4"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
       <c r="A208" s="2"/>
@@ -2226,6 +2447,7 @@
       <c r="E208" s="2"/>
       <c r="F208" s="2"/>
       <c r="G208" s="2"/>
+      <c r="H208" s="4"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
       <c r="A209" s="2"/>
@@ -2235,6 +2457,7 @@
       <c r="E209" s="2"/>
       <c r="F209" s="2"/>
       <c r="G209" s="2"/>
+      <c r="H209" s="4"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
       <c r="A210" s="2"/>
@@ -2244,6 +2467,7 @@
       <c r="E210" s="2"/>
       <c r="F210" s="2"/>
       <c r="G210" s="2"/>
+      <c r="H210" s="4"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
       <c r="A211" s="2"/>
@@ -2253,6 +2477,7 @@
       <c r="E211" s="2"/>
       <c r="F211" s="2"/>
       <c r="G211" s="2"/>
+      <c r="H211" s="4"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
       <c r="A212" s="2"/>
@@ -2262,6 +2487,7 @@
       <c r="E212" s="2"/>
       <c r="F212" s="2"/>
       <c r="G212" s="2"/>
+      <c r="H212" s="4"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
       <c r="A213" s="2"/>
@@ -2271,6 +2497,7 @@
       <c r="E213" s="2"/>
       <c r="F213" s="2"/>
       <c r="G213" s="2"/>
+      <c r="H213" s="4"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="2"/>
@@ -2280,6 +2507,7 @@
       <c r="E214" s="2"/>
       <c r="F214" s="2"/>
       <c r="G214" s="2"/>
+      <c r="H214" s="4"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="2"/>
@@ -2289,6 +2517,7 @@
       <c r="E215" s="2"/>
       <c r="F215" s="2"/>
       <c r="G215" s="2"/>
+      <c r="H215" s="4"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="2"/>
@@ -2298,6 +2527,7 @@
       <c r="E216" s="2"/>
       <c r="F216" s="2"/>
       <c r="G216" s="2"/>
+      <c r="H216" s="4"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
       <c r="A217" s="2"/>
@@ -2307,6 +2537,7 @@
       <c r="E217" s="2"/>
       <c r="F217" s="2"/>
       <c r="G217" s="2"/>
+      <c r="H217" s="4"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
       <c r="A218" s="2"/>
@@ -2316,6 +2547,7 @@
       <c r="E218" s="2"/>
       <c r="F218" s="2"/>
       <c r="G218" s="2"/>
+      <c r="H218" s="4"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="2"/>
@@ -2325,6 +2557,7 @@
       <c r="E219" s="2"/>
       <c r="F219" s="2"/>
       <c r="G219" s="2"/>
+      <c r="H219" s="4"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
       <c r="A220" s="2"/>
@@ -2334,6 +2567,7 @@
       <c r="E220" s="2"/>
       <c r="F220" s="2"/>
       <c r="G220" s="2"/>
+      <c r="H220" s="4"/>
     </row>
     <row r="221" ht="15.75" customHeight="1">
       <c r="A221" s="2"/>
@@ -2343,6 +2577,7 @@
       <c r="E221" s="2"/>
       <c r="F221" s="2"/>
       <c r="G221" s="2"/>
+      <c r="H221" s="4"/>
     </row>
     <row r="222" ht="15.75" customHeight="1">
       <c r="A222" s="2"/>
@@ -2352,6 +2587,7 @@
       <c r="E222" s="2"/>
       <c r="F222" s="2"/>
       <c r="G222" s="2"/>
+      <c r="H222" s="4"/>
     </row>
     <row r="223" ht="15.75" customHeight="1">
       <c r="A223" s="2"/>
@@ -2361,6 +2597,7 @@
       <c r="E223" s="2"/>
       <c r="F223" s="2"/>
       <c r="G223" s="2"/>
+      <c r="H223" s="4"/>
     </row>
     <row r="224" ht="15.75" customHeight="1">
       <c r="A224" s="2"/>
@@ -2370,6 +2607,7 @@
       <c r="E224" s="2"/>
       <c r="F224" s="2"/>
       <c r="G224" s="2"/>
+      <c r="H224" s="4"/>
     </row>
     <row r="225" ht="15.75" customHeight="1">
       <c r="A225" s="2"/>
@@ -2379,6 +2617,7 @@
       <c r="E225" s="2"/>
       <c r="F225" s="2"/>
       <c r="G225" s="2"/>
+      <c r="H225" s="4"/>
     </row>
     <row r="226" ht="15.75" customHeight="1">
       <c r="A226" s="2"/>
@@ -2388,6 +2627,7 @@
       <c r="E226" s="2"/>
       <c r="F226" s="2"/>
       <c r="G226" s="2"/>
+      <c r="H226" s="4"/>
     </row>
     <row r="227" ht="15.75" customHeight="1">
       <c r="A227" s="2"/>
@@ -2397,6 +2637,7 @@
       <c r="E227" s="2"/>
       <c r="F227" s="2"/>
       <c r="G227" s="2"/>
+      <c r="H227" s="4"/>
     </row>
     <row r="228" ht="15.75" customHeight="1">
       <c r="A228" s="2"/>
@@ -2406,6 +2647,7 @@
       <c r="E228" s="2"/>
       <c r="F228" s="2"/>
       <c r="G228" s="2"/>
+      <c r="H228" s="4"/>
     </row>
     <row r="229" ht="15.75" customHeight="1">
       <c r="A229" s="2"/>
@@ -2415,6 +2657,7 @@
       <c r="E229" s="2"/>
       <c r="F229" s="2"/>
       <c r="G229" s="2"/>
+      <c r="H229" s="4"/>
     </row>
     <row r="230" ht="15.75" customHeight="1">
       <c r="A230" s="2"/>
@@ -2424,6 +2667,7 @@
       <c r="E230" s="2"/>
       <c r="F230" s="2"/>
       <c r="G230" s="2"/>
+      <c r="H230" s="4"/>
     </row>
     <row r="231" ht="15.75" customHeight="1">
       <c r="A231" s="2"/>
@@ -2433,6 +2677,7 @@
       <c r="E231" s="2"/>
       <c r="F231" s="2"/>
       <c r="G231" s="2"/>
+      <c r="H231" s="4"/>
     </row>
     <row r="232" ht="15.75" customHeight="1">
       <c r="A232" s="2"/>
@@ -2442,6 +2687,7 @@
       <c r="E232" s="2"/>
       <c r="F232" s="2"/>
       <c r="G232" s="2"/>
+      <c r="H232" s="4"/>
     </row>
     <row r="233" ht="15.75" customHeight="1">
       <c r="A233" s="2"/>
@@ -2451,6 +2697,7 @@
       <c r="E233" s="2"/>
       <c r="F233" s="2"/>
       <c r="G233" s="2"/>
+      <c r="H233" s="4"/>
     </row>
     <row r="234" ht="15.75" customHeight="1">
       <c r="A234" s="2"/>
@@ -2460,6 +2707,7 @@
       <c r="E234" s="2"/>
       <c r="F234" s="2"/>
       <c r="G234" s="2"/>
+      <c r="H234" s="4"/>
     </row>
     <row r="235" ht="15.75" customHeight="1">
       <c r="A235" s="2"/>
@@ -2469,6 +2717,7 @@
       <c r="E235" s="2"/>
       <c r="F235" s="2"/>
       <c r="G235" s="2"/>
+      <c r="H235" s="4"/>
     </row>
     <row r="236" ht="15.75" customHeight="1">
       <c r="A236" s="2"/>
@@ -2478,6 +2727,7 @@
       <c r="E236" s="2"/>
       <c r="F236" s="2"/>
       <c r="G236" s="2"/>
+      <c r="H236" s="4"/>
     </row>
     <row r="237" ht="15.75" customHeight="1">
       <c r="A237" s="2"/>
@@ -2487,6 +2737,7 @@
       <c r="E237" s="2"/>
       <c r="F237" s="2"/>
       <c r="G237" s="2"/>
+      <c r="H237" s="4"/>
     </row>
     <row r="238" ht="15.75" customHeight="1">
       <c r="A238" s="2"/>
@@ -2496,6 +2747,7 @@
       <c r="E238" s="2"/>
       <c r="F238" s="2"/>
       <c r="G238" s="2"/>
+      <c r="H238" s="4"/>
     </row>
     <row r="239" ht="15.75" customHeight="1">
       <c r="A239" s="2"/>
@@ -2505,6 +2757,7 @@
       <c r="E239" s="2"/>
       <c r="F239" s="2"/>
       <c r="G239" s="2"/>
+      <c r="H239" s="4"/>
     </row>
     <row r="240" ht="15.75" customHeight="1">
       <c r="A240" s="2"/>
@@ -2514,6 +2767,7 @@
       <c r="E240" s="2"/>
       <c r="F240" s="2"/>
       <c r="G240" s="2"/>
+      <c r="H240" s="4"/>
     </row>
     <row r="241" ht="15.75" customHeight="1">
       <c r="A241" s="2"/>
@@ -2523,6 +2777,7 @@
       <c r="E241" s="2"/>
       <c r="F241" s="2"/>
       <c r="G241" s="2"/>
+      <c r="H241" s="4"/>
     </row>
     <row r="242" ht="15.75" customHeight="1">
       <c r="A242" s="2"/>
@@ -2532,6 +2787,7 @@
       <c r="E242" s="2"/>
       <c r="F242" s="2"/>
       <c r="G242" s="2"/>
+      <c r="H242" s="4"/>
     </row>
     <row r="243" ht="15.75" customHeight="1">
       <c r="A243" s="2"/>
@@ -2541,6 +2797,7 @@
       <c r="E243" s="2"/>
       <c r="F243" s="2"/>
       <c r="G243" s="2"/>
+      <c r="H243" s="4"/>
     </row>
     <row r="244" ht="15.75" customHeight="1">
       <c r="A244" s="2"/>
@@ -2550,6 +2807,7 @@
       <c r="E244" s="2"/>
       <c r="F244" s="2"/>
       <c r="G244" s="2"/>
+      <c r="H244" s="4"/>
     </row>
     <row r="245" ht="15.75" customHeight="1">
       <c r="A245" s="2"/>
@@ -2559,6 +2817,7 @@
       <c r="E245" s="2"/>
       <c r="F245" s="2"/>
       <c r="G245" s="2"/>
+      <c r="H245" s="4"/>
     </row>
     <row r="246" ht="15.75" customHeight="1">
       <c r="A246" s="2"/>
@@ -2568,6 +2827,7 @@
       <c r="E246" s="2"/>
       <c r="F246" s="2"/>
       <c r="G246" s="2"/>
+      <c r="H246" s="4"/>
     </row>
     <row r="247" ht="15.75" customHeight="1">
       <c r="A247" s="2"/>
@@ -2577,6 +2837,7 @@
       <c r="E247" s="2"/>
       <c r="F247" s="2"/>
       <c r="G247" s="2"/>
+      <c r="H247" s="4"/>
     </row>
     <row r="248" ht="15.75" customHeight="1">
       <c r="A248" s="2"/>
@@ -2586,6 +2847,7 @@
       <c r="E248" s="2"/>
       <c r="F248" s="2"/>
       <c r="G248" s="2"/>
+      <c r="H248" s="4"/>
     </row>
     <row r="249" ht="15.75" customHeight="1">
       <c r="A249" s="2"/>
@@ -2595,6 +2857,7 @@
       <c r="E249" s="2"/>
       <c r="F249" s="2"/>
       <c r="G249" s="2"/>
+      <c r="H249" s="4"/>
     </row>
     <row r="250" ht="15.75" customHeight="1">
       <c r="A250" s="2"/>
@@ -2604,6 +2867,7 @@
       <c r="E250" s="2"/>
       <c r="F250" s="2"/>
       <c r="G250" s="2"/>
+      <c r="H250" s="4"/>
     </row>
     <row r="251" ht="15.75" customHeight="1">
       <c r="A251" s="2"/>
@@ -2613,6 +2877,7 @@
       <c r="E251" s="2"/>
       <c r="F251" s="2"/>
       <c r="G251" s="2"/>
+      <c r="H251" s="4"/>
     </row>
     <row r="252" ht="15.75" customHeight="1">
       <c r="A252" s="2"/>
@@ -2622,6 +2887,7 @@
       <c r="E252" s="2"/>
       <c r="F252" s="2"/>
       <c r="G252" s="2"/>
+      <c r="H252" s="4"/>
     </row>
     <row r="253" ht="15.75" customHeight="1">
       <c r="A253" s="2"/>
@@ -2631,6 +2897,7 @@
       <c r="E253" s="2"/>
       <c r="F253" s="2"/>
       <c r="G253" s="2"/>
+      <c r="H253" s="4"/>
     </row>
     <row r="254" ht="15.75" customHeight="1">
       <c r="A254" s="2"/>
@@ -2640,6 +2907,7 @@
       <c r="E254" s="2"/>
       <c r="F254" s="2"/>
       <c r="G254" s="2"/>
+      <c r="H254" s="4"/>
     </row>
     <row r="255" ht="15.75" customHeight="1">
       <c r="A255" s="2"/>
@@ -2649,6 +2917,7 @@
       <c r="E255" s="2"/>
       <c r="F255" s="2"/>
       <c r="G255" s="2"/>
+      <c r="H255" s="4"/>
     </row>
     <row r="256" ht="15.75" customHeight="1">
       <c r="A256" s="2"/>
@@ -2658,6 +2927,7 @@
       <c r="E256" s="2"/>
       <c r="F256" s="2"/>
       <c r="G256" s="2"/>
+      <c r="H256" s="4"/>
     </row>
     <row r="257" ht="15.75" customHeight="1">
       <c r="A257" s="2"/>
@@ -2667,6 +2937,7 @@
       <c r="E257" s="2"/>
       <c r="F257" s="2"/>
       <c r="G257" s="2"/>
+      <c r="H257" s="4"/>
     </row>
     <row r="258" ht="15.75" customHeight="1">
       <c r="A258" s="2"/>
@@ -2676,6 +2947,7 @@
       <c r="E258" s="2"/>
       <c r="F258" s="2"/>
       <c r="G258" s="2"/>
+      <c r="H258" s="4"/>
     </row>
     <row r="259" ht="15.75" customHeight="1">
       <c r="A259" s="2"/>
@@ -2685,6 +2957,7 @@
       <c r="E259" s="2"/>
       <c r="F259" s="2"/>
       <c r="G259" s="2"/>
+      <c r="H259" s="4"/>
     </row>
     <row r="260" ht="15.75" customHeight="1">
       <c r="A260" s="2"/>
@@ -2694,6 +2967,7 @@
       <c r="E260" s="2"/>
       <c r="F260" s="2"/>
       <c r="G260" s="2"/>
+      <c r="H260" s="4"/>
     </row>
     <row r="261" ht="15.75" customHeight="1">
       <c r="A261" s="2"/>
@@ -2703,6 +2977,7 @@
       <c r="E261" s="2"/>
       <c r="F261" s="2"/>
       <c r="G261" s="2"/>
+      <c r="H261" s="4"/>
     </row>
     <row r="262" ht="15.75" customHeight="1">
       <c r="A262" s="2"/>
@@ -2712,6 +2987,7 @@
       <c r="E262" s="2"/>
       <c r="F262" s="2"/>
       <c r="G262" s="2"/>
+      <c r="H262" s="4"/>
     </row>
     <row r="263" ht="15.75" customHeight="1">
       <c r="A263" s="2"/>
@@ -2721,6 +2997,7 @@
       <c r="E263" s="2"/>
       <c r="F263" s="2"/>
       <c r="G263" s="2"/>
+      <c r="H263" s="4"/>
     </row>
     <row r="264" ht="15.75" customHeight="1">
       <c r="A264" s="2"/>
@@ -2730,6 +3007,7 @@
       <c r="E264" s="2"/>
       <c r="F264" s="2"/>
       <c r="G264" s="2"/>
+      <c r="H264" s="4"/>
     </row>
     <row r="265" ht="15.75" customHeight="1">
       <c r="A265" s="2"/>
@@ -2739,6 +3017,7 @@
       <c r="E265" s="2"/>
       <c r="F265" s="2"/>
       <c r="G265" s="2"/>
+      <c r="H265" s="4"/>
     </row>
     <row r="266" ht="15.75" customHeight="1">
       <c r="A266" s="2"/>
@@ -2748,6 +3027,7 @@
       <c r="E266" s="2"/>
       <c r="F266" s="2"/>
       <c r="G266" s="2"/>
+      <c r="H266" s="4"/>
     </row>
     <row r="267" ht="15.75" customHeight="1">
       <c r="A267" s="2"/>
@@ -2757,6 +3037,7 @@
       <c r="E267" s="2"/>
       <c r="F267" s="2"/>
       <c r="G267" s="2"/>
+      <c r="H267" s="4"/>
     </row>
     <row r="268" ht="15.75" customHeight="1">
       <c r="A268" s="2"/>
@@ -2766,6 +3047,7 @@
       <c r="E268" s="2"/>
       <c r="F268" s="2"/>
       <c r="G268" s="2"/>
+      <c r="H268" s="4"/>
     </row>
     <row r="269" ht="15.75" customHeight="1">
       <c r="A269" s="2"/>
@@ -2775,6 +3057,7 @@
       <c r="E269" s="2"/>
       <c r="F269" s="2"/>
       <c r="G269" s="2"/>
+      <c r="H269" s="4"/>
     </row>
     <row r="270" ht="15.75" customHeight="1">
       <c r="A270" s="2"/>
@@ -2784,6 +3067,7 @@
       <c r="E270" s="2"/>
       <c r="F270" s="2"/>
       <c r="G270" s="2"/>
+      <c r="H270" s="4"/>
     </row>
     <row r="271" ht="15.75" customHeight="1">
       <c r="A271" s="2"/>
@@ -2793,6 +3077,7 @@
       <c r="E271" s="2"/>
       <c r="F271" s="2"/>
       <c r="G271" s="2"/>
+      <c r="H271" s="4"/>
     </row>
     <row r="272" ht="15.75" customHeight="1">
       <c r="A272" s="2"/>
@@ -2802,6 +3087,7 @@
       <c r="E272" s="2"/>
       <c r="F272" s="2"/>
       <c r="G272" s="2"/>
+      <c r="H272" s="4"/>
     </row>
     <row r="273" ht="15.75" customHeight="1">
       <c r="A273" s="2"/>
@@ -2811,6 +3097,7 @@
       <c r="E273" s="2"/>
       <c r="F273" s="2"/>
       <c r="G273" s="2"/>
+      <c r="H273" s="4"/>
     </row>
     <row r="274" ht="15.75" customHeight="1">
       <c r="A274" s="2"/>
@@ -2820,6 +3107,7 @@
       <c r="E274" s="2"/>
       <c r="F274" s="2"/>
       <c r="G274" s="2"/>
+      <c r="H274" s="4"/>
     </row>
     <row r="275" ht="15.75" customHeight="1">
       <c r="A275" s="2"/>
@@ -2829,6 +3117,7 @@
       <c r="E275" s="2"/>
       <c r="F275" s="2"/>
       <c r="G275" s="2"/>
+      <c r="H275" s="4"/>
     </row>
     <row r="276" ht="15.75" customHeight="1">
       <c r="A276" s="2"/>
@@ -2838,6 +3127,7 @@
       <c r="E276" s="2"/>
       <c r="F276" s="2"/>
       <c r="G276" s="2"/>
+      <c r="H276" s="4"/>
     </row>
     <row r="277" ht="15.75" customHeight="1">
       <c r="A277" s="2"/>
@@ -2847,6 +3137,7 @@
       <c r="E277" s="2"/>
       <c r="F277" s="2"/>
       <c r="G277" s="2"/>
+      <c r="H277" s="4"/>
     </row>
     <row r="278" ht="15.75" customHeight="1">
       <c r="A278" s="2"/>
@@ -2856,6 +3147,7 @@
       <c r="E278" s="2"/>
       <c r="F278" s="2"/>
       <c r="G278" s="2"/>
+      <c r="H278" s="4"/>
     </row>
     <row r="279" ht="15.75" customHeight="1">
       <c r="A279" s="2"/>
@@ -2865,6 +3157,7 @@
       <c r="E279" s="2"/>
       <c r="F279" s="2"/>
       <c r="G279" s="2"/>
+      <c r="H279" s="4"/>
     </row>
     <row r="280" ht="15.75" customHeight="1">
       <c r="A280" s="2"/>
@@ -2874,6 +3167,7 @@
       <c r="E280" s="2"/>
       <c r="F280" s="2"/>
       <c r="G280" s="2"/>
+      <c r="H280" s="4"/>
     </row>
     <row r="281" ht="15.75" customHeight="1">
       <c r="A281" s="2"/>
@@ -2883,6 +3177,7 @@
       <c r="E281" s="2"/>
       <c r="F281" s="2"/>
       <c r="G281" s="2"/>
+      <c r="H281" s="4"/>
     </row>
     <row r="282" ht="15.75" customHeight="1">
       <c r="A282" s="2"/>
@@ -2892,6 +3187,7 @@
       <c r="E282" s="2"/>
       <c r="F282" s="2"/>
       <c r="G282" s="2"/>
+      <c r="H282" s="4"/>
     </row>
     <row r="283" ht="15.75" customHeight="1">
       <c r="A283" s="2"/>
@@ -2901,6 +3197,7 @@
       <c r="E283" s="2"/>
       <c r="F283" s="2"/>
       <c r="G283" s="2"/>
+      <c r="H283" s="4"/>
     </row>
     <row r="284" ht="15.75" customHeight="1">
       <c r="A284" s="2"/>
@@ -2910,6 +3207,7 @@
       <c r="E284" s="2"/>
       <c r="F284" s="2"/>
       <c r="G284" s="2"/>
+      <c r="H284" s="4"/>
     </row>
     <row r="285" ht="15.75" customHeight="1">
       <c r="A285" s="2"/>
@@ -2919,6 +3217,7 @@
       <c r="E285" s="2"/>
       <c r="F285" s="2"/>
       <c r="G285" s="2"/>
+      <c r="H285" s="4"/>
     </row>
     <row r="286" ht="15.75" customHeight="1">
       <c r="A286" s="2"/>
@@ -2928,6 +3227,7 @@
       <c r="E286" s="2"/>
       <c r="F286" s="2"/>
       <c r="G286" s="2"/>
+      <c r="H286" s="4"/>
     </row>
     <row r="287" ht="15.75" customHeight="1">
       <c r="A287" s="2"/>
@@ -2937,6 +3237,7 @@
       <c r="E287" s="2"/>
       <c r="F287" s="2"/>
       <c r="G287" s="2"/>
+      <c r="H287" s="4"/>
     </row>
     <row r="288" ht="15.75" customHeight="1">
       <c r="A288" s="2"/>
@@ -2946,6 +3247,7 @@
       <c r="E288" s="2"/>
       <c r="F288" s="2"/>
       <c r="G288" s="2"/>
+      <c r="H288" s="4"/>
     </row>
     <row r="289" ht="15.75" customHeight="1">
       <c r="A289" s="2"/>
@@ -2955,6 +3257,7 @@
       <c r="E289" s="2"/>
       <c r="F289" s="2"/>
       <c r="G289" s="2"/>
+      <c r="H289" s="4"/>
     </row>
     <row r="290" ht="15.75" customHeight="1">
       <c r="A290" s="2"/>
@@ -2964,6 +3267,7 @@
       <c r="E290" s="2"/>
       <c r="F290" s="2"/>
       <c r="G290" s="2"/>
+      <c r="H290" s="4"/>
     </row>
     <row r="291" ht="15.75" customHeight="1">
       <c r="A291" s="2"/>
@@ -2973,6 +3277,7 @@
       <c r="E291" s="2"/>
       <c r="F291" s="2"/>
       <c r="G291" s="2"/>
+      <c r="H291" s="4"/>
     </row>
     <row r="292" ht="15.75" customHeight="1">
       <c r="A292" s="2"/>
@@ -2982,6 +3287,7 @@
       <c r="E292" s="2"/>
       <c r="F292" s="2"/>
       <c r="G292" s="2"/>
+      <c r="H292" s="4"/>
     </row>
     <row r="293" ht="15.75" customHeight="1">
       <c r="A293" s="2"/>
@@ -2991,6 +3297,7 @@
       <c r="E293" s="2"/>
       <c r="F293" s="2"/>
       <c r="G293" s="2"/>
+      <c r="H293" s="4"/>
     </row>
     <row r="294" ht="15.75" customHeight="1">
       <c r="A294" s="2"/>
@@ -3000,6 +3307,7 @@
       <c r="E294" s="2"/>
       <c r="F294" s="2"/>
       <c r="G294" s="2"/>
+      <c r="H294" s="4"/>
     </row>
     <row r="295" ht="15.75" customHeight="1">
       <c r="A295" s="2"/>
@@ -3009,6 +3317,7 @@
       <c r="E295" s="2"/>
       <c r="F295" s="2"/>
       <c r="G295" s="2"/>
+      <c r="H295" s="4"/>
     </row>
     <row r="296" ht="15.75" customHeight="1">
       <c r="A296" s="2"/>
@@ -3018,6 +3327,7 @@
       <c r="E296" s="2"/>
       <c r="F296" s="2"/>
       <c r="G296" s="2"/>
+      <c r="H296" s="4"/>
     </row>
     <row r="297" ht="15.75" customHeight="1">
       <c r="A297" s="2"/>
@@ -3027,6 +3337,7 @@
       <c r="E297" s="2"/>
       <c r="F297" s="2"/>
       <c r="G297" s="2"/>
+      <c r="H297" s="4"/>
     </row>
     <row r="298" ht="15.75" customHeight="1">
       <c r="A298" s="2"/>
@@ -3036,6 +3347,7 @@
       <c r="E298" s="2"/>
       <c r="F298" s="2"/>
       <c r="G298" s="2"/>
+      <c r="H298" s="4"/>
     </row>
     <row r="299" ht="15.75" customHeight="1">
       <c r="A299" s="2"/>
@@ -3045,6 +3357,7 @@
       <c r="E299" s="2"/>
       <c r="F299" s="2"/>
       <c r="G299" s="2"/>
+      <c r="H299" s="4"/>
     </row>
     <row r="300" ht="15.75" customHeight="1">
       <c r="A300" s="2"/>
@@ -3054,6 +3367,7 @@
       <c r="E300" s="2"/>
       <c r="F300" s="2"/>
       <c r="G300" s="2"/>
+      <c r="H300" s="4"/>
     </row>
     <row r="301" ht="15.75" customHeight="1">
       <c r="A301" s="2"/>
@@ -3063,6 +3377,7 @@
       <c r="E301" s="2"/>
       <c r="F301" s="2"/>
       <c r="G301" s="2"/>
+      <c r="H301" s="4"/>
     </row>
     <row r="302" ht="15.75" customHeight="1">
       <c r="A302" s="2"/>
@@ -3072,6 +3387,7 @@
       <c r="E302" s="2"/>
       <c r="F302" s="2"/>
       <c r="G302" s="2"/>
+      <c r="H302" s="4"/>
     </row>
     <row r="303" ht="15.75" customHeight="1">
       <c r="A303" s="2"/>
@@ -3081,6 +3397,7 @@
       <c r="E303" s="2"/>
       <c r="F303" s="2"/>
       <c r="G303" s="2"/>
+      <c r="H303" s="4"/>
     </row>
     <row r="304" ht="15.75" customHeight="1">
       <c r="A304" s="2"/>
@@ -3090,6 +3407,7 @@
       <c r="E304" s="2"/>
       <c r="F304" s="2"/>
       <c r="G304" s="2"/>
+      <c r="H304" s="4"/>
     </row>
     <row r="305" ht="15.75" customHeight="1">
       <c r="A305" s="2"/>
@@ -3099,6 +3417,7 @@
       <c r="E305" s="2"/>
       <c r="F305" s="2"/>
       <c r="G305" s="2"/>
+      <c r="H305" s="4"/>
     </row>
     <row r="306" ht="15.75" customHeight="1">
       <c r="A306" s="2"/>
@@ -3108,6 +3427,7 @@
       <c r="E306" s="2"/>
       <c r="F306" s="2"/>
       <c r="G306" s="2"/>
+      <c r="H306" s="4"/>
     </row>
     <row r="307" ht="15.75" customHeight="1">
       <c r="A307" s="2"/>
@@ -3117,6 +3437,7 @@
       <c r="E307" s="2"/>
       <c r="F307" s="2"/>
       <c r="G307" s="2"/>
+      <c r="H307" s="4"/>
     </row>
     <row r="308" ht="15.75" customHeight="1">
       <c r="A308" s="2"/>
@@ -3126,6 +3447,7 @@
       <c r="E308" s="2"/>
       <c r="F308" s="2"/>
       <c r="G308" s="2"/>
+      <c r="H308" s="4"/>
     </row>
     <row r="309" ht="15.75" customHeight="1">
       <c r="A309" s="2"/>
@@ -3135,6 +3457,7 @@
       <c r="E309" s="2"/>
       <c r="F309" s="2"/>
       <c r="G309" s="2"/>
+      <c r="H309" s="4"/>
     </row>
     <row r="310" ht="15.75" customHeight="1">
       <c r="A310" s="2"/>
@@ -3144,6 +3467,7 @@
       <c r="E310" s="2"/>
       <c r="F310" s="2"/>
       <c r="G310" s="2"/>
+      <c r="H310" s="4"/>
     </row>
     <row r="311" ht="15.75" customHeight="1">
       <c r="A311" s="2"/>
@@ -3153,6 +3477,7 @@
       <c r="E311" s="2"/>
       <c r="F311" s="2"/>
       <c r="G311" s="2"/>
+      <c r="H311" s="4"/>
     </row>
     <row r="312" ht="15.75" customHeight="1">
       <c r="A312" s="2"/>
@@ -3162,6 +3487,7 @@
       <c r="E312" s="2"/>
       <c r="F312" s="2"/>
       <c r="G312" s="2"/>
+      <c r="H312" s="4"/>
     </row>
     <row r="313" ht="15.75" customHeight="1">
       <c r="A313" s="2"/>
@@ -3171,6 +3497,7 @@
       <c r="E313" s="2"/>
       <c r="F313" s="2"/>
       <c r="G313" s="2"/>
+      <c r="H313" s="4"/>
     </row>
     <row r="314" ht="15.75" customHeight="1">
       <c r="A314" s="2"/>
@@ -3180,6 +3507,7 @@
       <c r="E314" s="2"/>
       <c r="F314" s="2"/>
       <c r="G314" s="2"/>
+      <c r="H314" s="4"/>
     </row>
     <row r="315" ht="15.75" customHeight="1">
       <c r="A315" s="2"/>
@@ -3189,6 +3517,7 @@
       <c r="E315" s="2"/>
       <c r="F315" s="2"/>
       <c r="G315" s="2"/>
+      <c r="H315" s="4"/>
     </row>
     <row r="316" ht="15.75" customHeight="1">
       <c r="A316" s="2"/>
@@ -3198,6 +3527,7 @@
       <c r="E316" s="2"/>
       <c r="F316" s="2"/>
       <c r="G316" s="2"/>
+      <c r="H316" s="4"/>
     </row>
     <row r="317" ht="15.75" customHeight="1">
       <c r="A317" s="2"/>
@@ -3207,6 +3537,7 @@
       <c r="E317" s="2"/>
       <c r="F317" s="2"/>
       <c r="G317" s="2"/>
+      <c r="H317" s="4"/>
     </row>
     <row r="318" ht="15.75" customHeight="1">
       <c r="A318" s="2"/>
@@ -3216,6 +3547,7 @@
       <c r="E318" s="2"/>
       <c r="F318" s="2"/>
       <c r="G318" s="2"/>
+      <c r="H318" s="4"/>
     </row>
     <row r="319" ht="15.75" customHeight="1">
       <c r="A319" s="2"/>
@@ -3225,6 +3557,7 @@
       <c r="E319" s="2"/>
       <c r="F319" s="2"/>
       <c r="G319" s="2"/>
+      <c r="H319" s="4"/>
     </row>
     <row r="320" ht="15.75" customHeight="1">
       <c r="A320" s="2"/>
@@ -3234,6 +3567,7 @@
       <c r="E320" s="2"/>
       <c r="F320" s="2"/>
       <c r="G320" s="2"/>
+      <c r="H320" s="4"/>
     </row>
     <row r="321" ht="15.75" customHeight="1">
       <c r="A321" s="2"/>
@@ -3243,6 +3577,7 @@
       <c r="E321" s="2"/>
       <c r="F321" s="2"/>
       <c r="G321" s="2"/>
+      <c r="H321" s="4"/>
     </row>
     <row r="322" ht="15.75" customHeight="1">
       <c r="A322" s="2"/>
@@ -3252,6 +3587,7 @@
       <c r="E322" s="2"/>
       <c r="F322" s="2"/>
       <c r="G322" s="2"/>
+      <c r="H322" s="4"/>
     </row>
     <row r="323" ht="15.75" customHeight="1">
       <c r="A323" s="2"/>
@@ -3261,6 +3597,7 @@
       <c r="E323" s="2"/>
       <c r="F323" s="2"/>
       <c r="G323" s="2"/>
+      <c r="H323" s="4"/>
     </row>
     <row r="324" ht="15.75" customHeight="1">
       <c r="A324" s="2"/>
@@ -3270,6 +3607,7 @@
       <c r="E324" s="2"/>
       <c r="F324" s="2"/>
       <c r="G324" s="2"/>
+      <c r="H324" s="4"/>
     </row>
     <row r="325" ht="15.75" customHeight="1">
       <c r="A325" s="2"/>
@@ -3279,6 +3617,7 @@
       <c r="E325" s="2"/>
       <c r="F325" s="2"/>
       <c r="G325" s="2"/>
+      <c r="H325" s="4"/>
     </row>
     <row r="326" ht="15.75" customHeight="1">
       <c r="A326" s="2"/>
@@ -3288,6 +3627,7 @@
       <c r="E326" s="2"/>
       <c r="F326" s="2"/>
       <c r="G326" s="2"/>
+      <c r="H326" s="4"/>
     </row>
     <row r="327" ht="15.75" customHeight="1">
       <c r="A327" s="2"/>
@@ -3297,6 +3637,7 @@
       <c r="E327" s="2"/>
       <c r="F327" s="2"/>
       <c r="G327" s="2"/>
+      <c r="H327" s="4"/>
     </row>
     <row r="328" ht="15.75" customHeight="1">
       <c r="A328" s="2"/>
@@ -3306,6 +3647,7 @@
       <c r="E328" s="2"/>
       <c r="F328" s="2"/>
       <c r="G328" s="2"/>
+      <c r="H328" s="4"/>
     </row>
     <row r="329" ht="15.75" customHeight="1">
       <c r="A329" s="2"/>
@@ -3315,6 +3657,7 @@
       <c r="E329" s="2"/>
       <c r="F329" s="2"/>
       <c r="G329" s="2"/>
+      <c r="H329" s="4"/>
     </row>
     <row r="330" ht="15.75" customHeight="1">
       <c r="A330" s="2"/>
@@ -3324,6 +3667,7 @@
       <c r="E330" s="2"/>
       <c r="F330" s="2"/>
       <c r="G330" s="2"/>
+      <c r="H330" s="4"/>
     </row>
     <row r="331" ht="15.75" customHeight="1">
       <c r="A331" s="2"/>
@@ -3333,6 +3677,7 @@
       <c r="E331" s="2"/>
       <c r="F331" s="2"/>
       <c r="G331" s="2"/>
+      <c r="H331" s="4"/>
     </row>
     <row r="332" ht="15.75" customHeight="1">
       <c r="A332" s="2"/>
@@ -3342,6 +3687,7 @@
       <c r="E332" s="2"/>
       <c r="F332" s="2"/>
       <c r="G332" s="2"/>
+      <c r="H332" s="4"/>
     </row>
     <row r="333" ht="15.75" customHeight="1">
       <c r="A333" s="2"/>
@@ -3351,6 +3697,7 @@
       <c r="E333" s="2"/>
       <c r="F333" s="2"/>
       <c r="G333" s="2"/>
+      <c r="H333" s="4"/>
     </row>
     <row r="334" ht="15.75" customHeight="1">
       <c r="A334" s="2"/>
@@ -3360,6 +3707,7 @@
       <c r="E334" s="2"/>
       <c r="F334" s="2"/>
       <c r="G334" s="2"/>
+      <c r="H334" s="4"/>
     </row>
     <row r="335" ht="15.75" customHeight="1">
       <c r="A335" s="2"/>
@@ -3369,6 +3717,7 @@
       <c r="E335" s="2"/>
       <c r="F335" s="2"/>
       <c r="G335" s="2"/>
+      <c r="H335" s="4"/>
     </row>
     <row r="336" ht="15.75" customHeight="1">
       <c r="A336" s="2"/>
@@ -3378,6 +3727,7 @@
       <c r="E336" s="2"/>
       <c r="F336" s="2"/>
       <c r="G336" s="2"/>
+      <c r="H336" s="4"/>
     </row>
     <row r="337" ht="15.75" customHeight="1">
       <c r="A337" s="2"/>
@@ -3387,6 +3737,7 @@
       <c r="E337" s="2"/>
       <c r="F337" s="2"/>
       <c r="G337" s="2"/>
+      <c r="H337" s="4"/>
     </row>
     <row r="338" ht="15.75" customHeight="1">
       <c r="A338" s="2"/>
@@ -3396,6 +3747,7 @@
       <c r="E338" s="2"/>
       <c r="F338" s="2"/>
       <c r="G338" s="2"/>
+      <c r="H338" s="4"/>
     </row>
     <row r="339" ht="15.75" customHeight="1">
       <c r="A339" s="2"/>
@@ -3405,6 +3757,7 @@
       <c r="E339" s="2"/>
       <c r="F339" s="2"/>
       <c r="G339" s="2"/>
+      <c r="H339" s="4"/>
     </row>
     <row r="340" ht="15.75" customHeight="1">
       <c r="A340" s="2"/>
@@ -3414,6 +3767,7 @@
       <c r="E340" s="2"/>
       <c r="F340" s="2"/>
       <c r="G340" s="2"/>
+      <c r="H340" s="4"/>
     </row>
     <row r="341" ht="15.75" customHeight="1">
       <c r="A341" s="2"/>
@@ -3423,6 +3777,7 @@
       <c r="E341" s="2"/>
       <c r="F341" s="2"/>
       <c r="G341" s="2"/>
+      <c r="H341" s="4"/>
     </row>
     <row r="342" ht="15.75" customHeight="1">
       <c r="A342" s="2"/>
@@ -3432,6 +3787,7 @@
       <c r="E342" s="2"/>
       <c r="F342" s="2"/>
       <c r="G342" s="2"/>
+      <c r="H342" s="4"/>
     </row>
     <row r="343" ht="15.75" customHeight="1">
       <c r="A343" s="2"/>
@@ -3441,6 +3797,7 @@
       <c r="E343" s="2"/>
       <c r="F343" s="2"/>
       <c r="G343" s="2"/>
+      <c r="H343" s="4"/>
     </row>
     <row r="344" ht="15.75" customHeight="1">
       <c r="A344" s="2"/>
@@ -3450,6 +3807,7 @@
       <c r="E344" s="2"/>
       <c r="F344" s="2"/>
       <c r="G344" s="2"/>
+      <c r="H344" s="4"/>
     </row>
     <row r="345" ht="15.75" customHeight="1">
       <c r="A345" s="2"/>
@@ -3459,6 +3817,7 @@
       <c r="E345" s="2"/>
       <c r="F345" s="2"/>
       <c r="G345" s="2"/>
+      <c r="H345" s="4"/>
     </row>
     <row r="346" ht="15.75" customHeight="1">
       <c r="A346" s="2"/>
@@ -3468,6 +3827,7 @@
       <c r="E346" s="2"/>
       <c r="F346" s="2"/>
       <c r="G346" s="2"/>
+      <c r="H346" s="4"/>
     </row>
     <row r="347" ht="15.75" customHeight="1">
       <c r="A347" s="2"/>
@@ -3477,6 +3837,7 @@
       <c r="E347" s="2"/>
       <c r="F347" s="2"/>
       <c r="G347" s="2"/>
+      <c r="H347" s="4"/>
     </row>
     <row r="348" ht="15.75" customHeight="1">
       <c r="A348" s="2"/>
@@ -3486,6 +3847,7 @@
       <c r="E348" s="2"/>
       <c r="F348" s="2"/>
       <c r="G348" s="2"/>
+      <c r="H348" s="4"/>
     </row>
     <row r="349" ht="15.75" customHeight="1">
       <c r="A349" s="2"/>
@@ -3495,6 +3857,7 @@
       <c r="E349" s="2"/>
       <c r="F349" s="2"/>
       <c r="G349" s="2"/>
+      <c r="H349" s="4"/>
     </row>
     <row r="350" ht="15.75" customHeight="1">
       <c r="A350" s="2"/>
@@ -3504,6 +3867,7 @@
       <c r="E350" s="2"/>
       <c r="F350" s="2"/>
       <c r="G350" s="2"/>
+      <c r="H350" s="4"/>
     </row>
     <row r="351" ht="15.75" customHeight="1">
       <c r="A351" s="2"/>
@@ -3513,6 +3877,7 @@
       <c r="E351" s="2"/>
       <c r="F351" s="2"/>
       <c r="G351" s="2"/>
+      <c r="H351" s="4"/>
     </row>
     <row r="352" ht="15.75" customHeight="1">
       <c r="A352" s="2"/>
@@ -3522,6 +3887,7 @@
       <c r="E352" s="2"/>
       <c r="F352" s="2"/>
       <c r="G352" s="2"/>
+      <c r="H352" s="4"/>
     </row>
     <row r="353" ht="15.75" customHeight="1">
       <c r="A353" s="2"/>
@@ -3531,6 +3897,7 @@
       <c r="E353" s="2"/>
       <c r="F353" s="2"/>
       <c r="G353" s="2"/>
+      <c r="H353" s="4"/>
     </row>
     <row r="354" ht="15.75" customHeight="1">
       <c r="A354" s="2"/>
@@ -3540,6 +3907,7 @@
       <c r="E354" s="2"/>
       <c r="F354" s="2"/>
       <c r="G354" s="2"/>
+      <c r="H354" s="4"/>
     </row>
     <row r="355" ht="15.75" customHeight="1">
       <c r="A355" s="2"/>
@@ -3549,6 +3917,7 @@
       <c r="E355" s="2"/>
       <c r="F355" s="2"/>
       <c r="G355" s="2"/>
+      <c r="H355" s="4"/>
     </row>
     <row r="356" ht="15.75" customHeight="1">
       <c r="A356" s="2"/>
@@ -3558,6 +3927,7 @@
       <c r="E356" s="2"/>
       <c r="F356" s="2"/>
       <c r="G356" s="2"/>
+      <c r="H356" s="4"/>
     </row>
     <row r="357" ht="15.75" customHeight="1">
       <c r="A357" s="2"/>
@@ -3567,6 +3937,7 @@
       <c r="E357" s="2"/>
       <c r="F357" s="2"/>
       <c r="G357" s="2"/>
+      <c r="H357" s="4"/>
     </row>
     <row r="358" ht="15.75" customHeight="1">
       <c r="A358" s="2"/>
@@ -3576,6 +3947,7 @@
       <c r="E358" s="2"/>
       <c r="F358" s="2"/>
       <c r="G358" s="2"/>
+      <c r="H358" s="4"/>
     </row>
     <row r="359" ht="15.75" customHeight="1">
       <c r="A359" s="2"/>
@@ -3585,6 +3957,7 @@
       <c r="E359" s="2"/>
       <c r="F359" s="2"/>
       <c r="G359" s="2"/>
+      <c r="H359" s="4"/>
     </row>
     <row r="360" ht="15.75" customHeight="1">
       <c r="A360" s="2"/>
@@ -3594,6 +3967,7 @@
       <c r="E360" s="2"/>
       <c r="F360" s="2"/>
       <c r="G360" s="2"/>
+      <c r="H360" s="4"/>
     </row>
     <row r="361" ht="15.75" customHeight="1">
       <c r="A361" s="2"/>
@@ -3603,6 +3977,7 @@
       <c r="E361" s="2"/>
       <c r="F361" s="2"/>
       <c r="G361" s="2"/>
+      <c r="H361" s="4"/>
     </row>
     <row r="362" ht="15.75" customHeight="1">
       <c r="A362" s="2"/>
@@ -3612,6 +3987,7 @@
       <c r="E362" s="2"/>
       <c r="F362" s="2"/>
       <c r="G362" s="2"/>
+      <c r="H362" s="4"/>
     </row>
     <row r="363" ht="15.75" customHeight="1">
       <c r="A363" s="2"/>
@@ -3621,6 +3997,7 @@
       <c r="E363" s="2"/>
       <c r="F363" s="2"/>
       <c r="G363" s="2"/>
+      <c r="H363" s="4"/>
     </row>
     <row r="364" ht="15.75" customHeight="1">
       <c r="A364" s="2"/>
@@ -3630,6 +4007,7 @@
       <c r="E364" s="2"/>
       <c r="F364" s="2"/>
       <c r="G364" s="2"/>
+      <c r="H364" s="4"/>
     </row>
     <row r="365" ht="15.75" customHeight="1">
       <c r="A365" s="2"/>
@@ -3639,6 +4017,7 @@
       <c r="E365" s="2"/>
       <c r="F365" s="2"/>
       <c r="G365" s="2"/>
+      <c r="H365" s="4"/>
     </row>
     <row r="366" ht="15.75" customHeight="1">
       <c r="A366" s="2"/>
@@ -3648,6 +4027,7 @@
       <c r="E366" s="2"/>
       <c r="F366" s="2"/>
       <c r="G366" s="2"/>
+      <c r="H366" s="4"/>
     </row>
     <row r="367" ht="15.75" customHeight="1">
       <c r="A367" s="2"/>
@@ -3657,6 +4037,7 @@
       <c r="E367" s="2"/>
       <c r="F367" s="2"/>
       <c r="G367" s="2"/>
+      <c r="H367" s="4"/>
     </row>
     <row r="368" ht="15.75" customHeight="1">
       <c r="A368" s="2"/>
@@ -3666,6 +4047,7 @@
       <c r="E368" s="2"/>
       <c r="F368" s="2"/>
       <c r="G368" s="2"/>
+      <c r="H368" s="4"/>
     </row>
     <row r="369" ht="15.75" customHeight="1">
       <c r="A369" s="2"/>
@@ -3675,6 +4057,7 @@
       <c r="E369" s="2"/>
       <c r="F369" s="2"/>
       <c r="G369" s="2"/>
+      <c r="H369" s="4"/>
     </row>
     <row r="370" ht="15.75" customHeight="1">
       <c r="A370" s="2"/>
@@ -3684,6 +4067,7 @@
       <c r="E370" s="2"/>
       <c r="F370" s="2"/>
       <c r="G370" s="2"/>
+      <c r="H370" s="4"/>
     </row>
     <row r="371" ht="15.75" customHeight="1">
       <c r="A371" s="2"/>
@@ -3693,6 +4077,7 @@
       <c r="E371" s="2"/>
       <c r="F371" s="2"/>
       <c r="G371" s="2"/>
+      <c r="H371" s="4"/>
     </row>
     <row r="372" ht="15.75" customHeight="1">
       <c r="A372" s="2"/>
@@ -3702,6 +4087,7 @@
       <c r="E372" s="2"/>
       <c r="F372" s="2"/>
       <c r="G372" s="2"/>
+      <c r="H372" s="4"/>
     </row>
     <row r="373" ht="15.75" customHeight="1">
       <c r="A373" s="2"/>
@@ -3711,6 +4097,7 @@
       <c r="E373" s="2"/>
       <c r="F373" s="2"/>
       <c r="G373" s="2"/>
+      <c r="H373" s="4"/>
     </row>
     <row r="374" ht="15.75" customHeight="1">
       <c r="A374" s="2"/>
@@ -3720,6 +4107,7 @@
       <c r="E374" s="2"/>
       <c r="F374" s="2"/>
       <c r="G374" s="2"/>
+      <c r="H374" s="4"/>
     </row>
     <row r="375" ht="15.75" customHeight="1">
       <c r="A375" s="2"/>
@@ -3729,6 +4117,7 @@
       <c r="E375" s="2"/>
       <c r="F375" s="2"/>
       <c r="G375" s="2"/>
+      <c r="H375" s="4"/>
     </row>
     <row r="376" ht="15.75" customHeight="1">
       <c r="A376" s="2"/>
@@ -3738,6 +4127,7 @@
       <c r="E376" s="2"/>
       <c r="F376" s="2"/>
       <c r="G376" s="2"/>
+      <c r="H376" s="4"/>
     </row>
     <row r="377" ht="15.75" customHeight="1">
       <c r="A377" s="2"/>
@@ -3747,6 +4137,7 @@
       <c r="E377" s="2"/>
       <c r="F377" s="2"/>
       <c r="G377" s="2"/>
+      <c r="H377" s="4"/>
     </row>
     <row r="378" ht="15.75" customHeight="1">
       <c r="A378" s="2"/>
@@ -3756,6 +4147,7 @@
       <c r="E378" s="2"/>
       <c r="F378" s="2"/>
       <c r="G378" s="2"/>
+      <c r="H378" s="4"/>
     </row>
     <row r="379" ht="15.75" customHeight="1">
       <c r="A379" s="2"/>
@@ -3765,6 +4157,7 @@
       <c r="E379" s="2"/>
       <c r="F379" s="2"/>
       <c r="G379" s="2"/>
+      <c r="H379" s="4"/>
     </row>
     <row r="380" ht="15.75" customHeight="1">
       <c r="A380" s="2"/>
@@ -3774,6 +4167,7 @@
       <c r="E380" s="2"/>
       <c r="F380" s="2"/>
       <c r="G380" s="2"/>
+      <c r="H380" s="4"/>
     </row>
     <row r="381" ht="15.75" customHeight="1">
       <c r="A381" s="2"/>
@@ -3783,6 +4177,7 @@
       <c r="E381" s="2"/>
       <c r="F381" s="2"/>
       <c r="G381" s="2"/>
+      <c r="H381" s="4"/>
     </row>
     <row r="382" ht="15.75" customHeight="1">
       <c r="A382" s="2"/>
@@ -3792,6 +4187,7 @@
       <c r="E382" s="2"/>
       <c r="F382" s="2"/>
       <c r="G382" s="2"/>
+      <c r="H382" s="4"/>
     </row>
     <row r="383" ht="15.75" customHeight="1">
       <c r="A383" s="2"/>
@@ -3801,6 +4197,7 @@
       <c r="E383" s="2"/>
       <c r="F383" s="2"/>
       <c r="G383" s="2"/>
+      <c r="H383" s="4"/>
     </row>
     <row r="384" ht="15.75" customHeight="1">
       <c r="A384" s="2"/>
@@ -3810,6 +4207,7 @@
       <c r="E384" s="2"/>
       <c r="F384" s="2"/>
       <c r="G384" s="2"/>
+      <c r="H384" s="4"/>
     </row>
     <row r="385" ht="15.75" customHeight="1">
       <c r="A385" s="2"/>
@@ -3819,6 +4217,7 @@
       <c r="E385" s="2"/>
       <c r="F385" s="2"/>
       <c r="G385" s="2"/>
+      <c r="H385" s="4"/>
     </row>
     <row r="386" ht="15.75" customHeight="1">
       <c r="A386" s="2"/>
@@ -3828,6 +4227,7 @@
       <c r="E386" s="2"/>
       <c r="F386" s="2"/>
       <c r="G386" s="2"/>
+      <c r="H386" s="4"/>
     </row>
     <row r="387" ht="15.75" customHeight="1">
       <c r="A387" s="2"/>
@@ -3837,6 +4237,7 @@
       <c r="E387" s="2"/>
       <c r="F387" s="2"/>
       <c r="G387" s="2"/>
+      <c r="H387" s="4"/>
     </row>
     <row r="388" ht="15.75" customHeight="1">
       <c r="A388" s="2"/>
@@ -3846,6 +4247,7 @@
       <c r="E388" s="2"/>
       <c r="F388" s="2"/>
       <c r="G388" s="2"/>
+      <c r="H388" s="4"/>
     </row>
     <row r="389" ht="15.75" customHeight="1">
       <c r="A389" s="2"/>
@@ -3855,6 +4257,7 @@
       <c r="E389" s="2"/>
       <c r="F389" s="2"/>
       <c r="G389" s="2"/>
+      <c r="H389" s="4"/>
     </row>
     <row r="390" ht="15.75" customHeight="1">
       <c r="A390" s="2"/>
@@ -3864,6 +4267,7 @@
       <c r="E390" s="2"/>
       <c r="F390" s="2"/>
       <c r="G390" s="2"/>
+      <c r="H390" s="4"/>
     </row>
     <row r="391" ht="15.75" customHeight="1">
       <c r="A391" s="2"/>
@@ -3873,6 +4277,7 @@
       <c r="E391" s="2"/>
       <c r="F391" s="2"/>
       <c r="G391" s="2"/>
+      <c r="H391" s="4"/>
     </row>
     <row r="392" ht="15.75" customHeight="1">
       <c r="A392" s="2"/>
@@ -3882,6 +4287,7 @@
       <c r="E392" s="2"/>
       <c r="F392" s="2"/>
       <c r="G392" s="2"/>
+      <c r="H392" s="4"/>
     </row>
     <row r="393" ht="15.75" customHeight="1">
       <c r="A393" s="2"/>
@@ -3891,6 +4297,7 @@
       <c r="E393" s="2"/>
       <c r="F393" s="2"/>
       <c r="G393" s="2"/>
+      <c r="H393" s="4"/>
     </row>
     <row r="394" ht="15.75" customHeight="1">
       <c r="A394" s="2"/>
@@ -3900,6 +4307,7 @@
       <c r="E394" s="2"/>
       <c r="F394" s="2"/>
       <c r="G394" s="2"/>
+      <c r="H394" s="4"/>
     </row>
     <row r="395" ht="15.75" customHeight="1">
       <c r="A395" s="2"/>
@@ -3909,6 +4317,7 @@
       <c r="E395" s="2"/>
       <c r="F395" s="2"/>
       <c r="G395" s="2"/>
+      <c r="H395" s="4"/>
     </row>
     <row r="396" ht="15.75" customHeight="1">
       <c r="A396" s="2"/>
@@ -3918,6 +4327,7 @@
       <c r="E396" s="2"/>
       <c r="F396" s="2"/>
       <c r="G396" s="2"/>
+      <c r="H396" s="4"/>
     </row>
     <row r="397" ht="15.75" customHeight="1">
       <c r="A397" s="2"/>
@@ -3927,6 +4337,7 @@
       <c r="E397" s="2"/>
       <c r="F397" s="2"/>
       <c r="G397" s="2"/>
+      <c r="H397" s="4"/>
     </row>
     <row r="398" ht="15.75" customHeight="1">
       <c r="A398" s="2"/>
@@ -3936,6 +4347,7 @@
       <c r="E398" s="2"/>
       <c r="F398" s="2"/>
       <c r="G398" s="2"/>
+      <c r="H398" s="4"/>
     </row>
     <row r="399" ht="15.75" customHeight="1">
       <c r="A399" s="2"/>
@@ -3945,6 +4357,7 @@
       <c r="E399" s="2"/>
       <c r="F399" s="2"/>
       <c r="G399" s="2"/>
+      <c r="H399" s="4"/>
     </row>
     <row r="400" ht="15.75" customHeight="1">
       <c r="A400" s="2"/>
@@ -3954,6 +4367,7 @@
       <c r="E400" s="2"/>
       <c r="F400" s="2"/>
       <c r="G400" s="2"/>
+      <c r="H400" s="4"/>
     </row>
     <row r="401" ht="15.75" customHeight="1">
       <c r="A401" s="2"/>
@@ -3963,6 +4377,7 @@
       <c r="E401" s="2"/>
       <c r="F401" s="2"/>
       <c r="G401" s="2"/>
+      <c r="H401" s="4"/>
     </row>
     <row r="402" ht="15.75" customHeight="1">
       <c r="A402" s="2"/>
@@ -3972,6 +4387,7 @@
       <c r="E402" s="2"/>
       <c r="F402" s="2"/>
       <c r="G402" s="2"/>
+      <c r="H402" s="4"/>
     </row>
     <row r="403" ht="15.75" customHeight="1">
       <c r="A403" s="2"/>
@@ -3981,6 +4397,7 @@
       <c r="E403" s="2"/>
       <c r="F403" s="2"/>
       <c r="G403" s="2"/>
+      <c r="H403" s="4"/>
     </row>
     <row r="404" ht="15.75" customHeight="1">
       <c r="A404" s="2"/>
@@ -3990,6 +4407,7 @@
       <c r="E404" s="2"/>
       <c r="F404" s="2"/>
       <c r="G404" s="2"/>
+      <c r="H404" s="4"/>
     </row>
     <row r="405" ht="15.75" customHeight="1">
       <c r="A405" s="2"/>
@@ -3999,6 +4417,7 @@
       <c r="E405" s="2"/>
       <c r="F405" s="2"/>
       <c r="G405" s="2"/>
+      <c r="H405" s="4"/>
     </row>
     <row r="406" ht="15.75" customHeight="1">
       <c r="A406" s="2"/>
@@ -4008,6 +4427,7 @@
       <c r="E406" s="2"/>
       <c r="F406" s="2"/>
       <c r="G406" s="2"/>
+      <c r="H406" s="4"/>
     </row>
     <row r="407" ht="15.75" customHeight="1">
       <c r="A407" s="2"/>
@@ -4017,6 +4437,7 @@
       <c r="E407" s="2"/>
       <c r="F407" s="2"/>
       <c r="G407" s="2"/>
+      <c r="H407" s="4"/>
     </row>
     <row r="408" ht="15.75" customHeight="1">
       <c r="A408" s="2"/>
@@ -4026,6 +4447,7 @@
       <c r="E408" s="2"/>
       <c r="F408" s="2"/>
       <c r="G408" s="2"/>
+      <c r="H408" s="4"/>
     </row>
     <row r="409" ht="15.75" customHeight="1">
       <c r="A409" s="2"/>
@@ -4035,6 +4457,7 @@
       <c r="E409" s="2"/>
       <c r="F409" s="2"/>
       <c r="G409" s="2"/>
+      <c r="H409" s="4"/>
     </row>
     <row r="410" ht="15.75" customHeight="1">
       <c r="A410" s="2"/>
@@ -4044,6 +4467,7 @@
       <c r="E410" s="2"/>
       <c r="F410" s="2"/>
       <c r="G410" s="2"/>
+      <c r="H410" s="4"/>
     </row>
     <row r="411" ht="15.75" customHeight="1">
       <c r="A411" s="2"/>
@@ -4053,6 +4477,7 @@
       <c r="E411" s="2"/>
       <c r="F411" s="2"/>
       <c r="G411" s="2"/>
+      <c r="H411" s="4"/>
     </row>
     <row r="412" ht="15.75" customHeight="1">
       <c r="A412" s="2"/>
@@ -4062,6 +4487,7 @@
       <c r="E412" s="2"/>
       <c r="F412" s="2"/>
       <c r="G412" s="2"/>
+      <c r="H412" s="4"/>
     </row>
     <row r="413" ht="15.75" customHeight="1">
       <c r="A413" s="2"/>
@@ -4071,6 +4497,7 @@
       <c r="E413" s="2"/>
       <c r="F413" s="2"/>
       <c r="G413" s="2"/>
+      <c r="H413" s="4"/>
     </row>
     <row r="414" ht="15.75" customHeight="1">
       <c r="A414" s="2"/>
@@ -4080,6 +4507,7 @@
       <c r="E414" s="2"/>
       <c r="F414" s="2"/>
       <c r="G414" s="2"/>
+      <c r="H414" s="4"/>
     </row>
     <row r="415" ht="15.75" customHeight="1">
       <c r="A415" s="2"/>
@@ -4089,6 +4517,7 @@
       <c r="E415" s="2"/>
       <c r="F415" s="2"/>
       <c r="G415" s="2"/>
+      <c r="H415" s="4"/>
     </row>
     <row r="416" ht="15.75" customHeight="1">
       <c r="A416" s="2"/>
@@ -4098,6 +4527,7 @@
       <c r="E416" s="2"/>
       <c r="F416" s="2"/>
       <c r="G416" s="2"/>
+      <c r="H416" s="4"/>
     </row>
     <row r="417" ht="15.75" customHeight="1">
       <c r="A417" s="2"/>
@@ -4107,6 +4537,7 @@
       <c r="E417" s="2"/>
       <c r="F417" s="2"/>
       <c r="G417" s="2"/>
+      <c r="H417" s="4"/>
     </row>
     <row r="418" ht="15.75" customHeight="1">
       <c r="A418" s="2"/>
@@ -4116,6 +4547,7 @@
       <c r="E418" s="2"/>
       <c r="F418" s="2"/>
       <c r="G418" s="2"/>
+      <c r="H418" s="4"/>
     </row>
     <row r="419" ht="15.75" customHeight="1">
       <c r="A419" s="2"/>
@@ -4125,6 +4557,7 @@
       <c r="E419" s="2"/>
       <c r="F419" s="2"/>
       <c r="G419" s="2"/>
+      <c r="H419" s="4"/>
     </row>
     <row r="420" ht="15.75" customHeight="1">
       <c r="A420" s="2"/>
@@ -4134,6 +4567,7 @@
       <c r="E420" s="2"/>
       <c r="F420" s="2"/>
       <c r="G420" s="2"/>
+      <c r="H420" s="4"/>
     </row>
     <row r="421" ht="15.75" customHeight="1">
       <c r="A421" s="2"/>
@@ -4143,6 +4577,7 @@
       <c r="E421" s="2"/>
       <c r="F421" s="2"/>
       <c r="G421" s="2"/>
+      <c r="H421" s="4"/>
     </row>
     <row r="422" ht="15.75" customHeight="1">
       <c r="A422" s="2"/>
@@ -4152,6 +4587,7 @@
       <c r="E422" s="2"/>
       <c r="F422" s="2"/>
       <c r="G422" s="2"/>
+      <c r="H422" s="4"/>
     </row>
     <row r="423" ht="15.75" customHeight="1">
       <c r="A423" s="2"/>
@@ -4161,6 +4597,7 @@
       <c r="E423" s="2"/>
       <c r="F423" s="2"/>
       <c r="G423" s="2"/>
+      <c r="H423" s="4"/>
     </row>
     <row r="424" ht="15.75" customHeight="1">
       <c r="A424" s="2"/>
@@ -4170,6 +4607,7 @@
       <c r="E424" s="2"/>
       <c r="F424" s="2"/>
       <c r="G424" s="2"/>
+      <c r="H424" s="4"/>
     </row>
     <row r="425" ht="15.75" customHeight="1">
       <c r="A425" s="2"/>
@@ -4179,6 +4617,7 @@
       <c r="E425" s="2"/>
       <c r="F425" s="2"/>
       <c r="G425" s="2"/>
+      <c r="H425" s="4"/>
     </row>
     <row r="426" ht="15.75" customHeight="1">
       <c r="A426" s="2"/>
@@ -4188,6 +4627,7 @@
       <c r="E426" s="2"/>
       <c r="F426" s="2"/>
       <c r="G426" s="2"/>
+      <c r="H426" s="4"/>
     </row>
     <row r="427" ht="15.75" customHeight="1">
       <c r="A427" s="2"/>
@@ -4197,6 +4637,7 @@
       <c r="E427" s="2"/>
       <c r="F427" s="2"/>
       <c r="G427" s="2"/>
+      <c r="H427" s="4"/>
     </row>
     <row r="428" ht="15.75" customHeight="1">
       <c r="A428" s="2"/>
@@ -4206,6 +4647,7 @@
       <c r="E428" s="2"/>
       <c r="F428" s="2"/>
       <c r="G428" s="2"/>
+      <c r="H428" s="4"/>
     </row>
     <row r="429" ht="15.75" customHeight="1">
       <c r="A429" s="2"/>
@@ -4215,6 +4657,7 @@
       <c r="E429" s="2"/>
       <c r="F429" s="2"/>
       <c r="G429" s="2"/>
+      <c r="H429" s="4"/>
     </row>
     <row r="430" ht="15.75" customHeight="1">
       <c r="A430" s="2"/>
@@ -4224,6 +4667,7 @@
       <c r="E430" s="2"/>
       <c r="F430" s="2"/>
       <c r="G430" s="2"/>
+      <c r="H430" s="4"/>
     </row>
     <row r="431" ht="15.75" customHeight="1">
       <c r="A431" s="2"/>
@@ -4233,6 +4677,7 @@
       <c r="E431" s="2"/>
       <c r="F431" s="2"/>
       <c r="G431" s="2"/>
+      <c r="H431" s="4"/>
     </row>
     <row r="432" ht="15.75" customHeight="1">
       <c r="A432" s="2"/>
@@ -4242,6 +4687,7 @@
       <c r="E432" s="2"/>
       <c r="F432" s="2"/>
       <c r="G432" s="2"/>
+      <c r="H432" s="4"/>
     </row>
     <row r="433" ht="15.75" customHeight="1">
       <c r="A433" s="2"/>
@@ -4251,6 +4697,7 @@
       <c r="E433" s="2"/>
       <c r="F433" s="2"/>
       <c r="G433" s="2"/>
+      <c r="H433" s="4"/>
     </row>
     <row r="434" ht="15.75" customHeight="1">
       <c r="A434" s="2"/>
@@ -4260,6 +4707,7 @@
       <c r="E434" s="2"/>
       <c r="F434" s="2"/>
       <c r="G434" s="2"/>
+      <c r="H434" s="4"/>
     </row>
     <row r="435" ht="15.75" customHeight="1">
       <c r="A435" s="2"/>
@@ -4269,6 +4717,7 @@
       <c r="E435" s="2"/>
       <c r="F435" s="2"/>
       <c r="G435" s="2"/>
+      <c r="H435" s="4"/>
     </row>
     <row r="436" ht="15.75" customHeight="1">
       <c r="A436" s="2"/>
@@ -4278,6 +4727,7 @@
       <c r="E436" s="2"/>
       <c r="F436" s="2"/>
       <c r="G436" s="2"/>
+      <c r="H436" s="4"/>
     </row>
     <row r="437" ht="15.75" customHeight="1">
       <c r="A437" s="2"/>
@@ -4287,6 +4737,7 @@
       <c r="E437" s="2"/>
       <c r="F437" s="2"/>
       <c r="G437" s="2"/>
+      <c r="H437" s="4"/>
     </row>
     <row r="438" ht="15.75" customHeight="1">
       <c r="A438" s="2"/>
@@ -4296,6 +4747,7 @@
       <c r="E438" s="2"/>
       <c r="F438" s="2"/>
       <c r="G438" s="2"/>
+      <c r="H438" s="4"/>
     </row>
     <row r="439" ht="15.75" customHeight="1">
       <c r="A439" s="2"/>
@@ -4305,6 +4757,7 @@
       <c r="E439" s="2"/>
       <c r="F439" s="2"/>
       <c r="G439" s="2"/>
+      <c r="H439" s="4"/>
     </row>
     <row r="440" ht="15.75" customHeight="1">
       <c r="A440" s="2"/>
@@ -4314,6 +4767,7 @@
       <c r="E440" s="2"/>
       <c r="F440" s="2"/>
       <c r="G440" s="2"/>
+      <c r="H440" s="4"/>
     </row>
     <row r="441" ht="15.75" customHeight="1">
       <c r="A441" s="2"/>
@@ -4323,6 +4777,7 @@
       <c r="E441" s="2"/>
       <c r="F441" s="2"/>
       <c r="G441" s="2"/>
+      <c r="H441" s="4"/>
     </row>
     <row r="442" ht="15.75" customHeight="1">
       <c r="A442" s="2"/>
@@ -4332,6 +4787,7 @@
       <c r="E442" s="2"/>
       <c r="F442" s="2"/>
       <c r="G442" s="2"/>
+      <c r="H442" s="4"/>
     </row>
     <row r="443" ht="15.75" customHeight="1">
       <c r="A443" s="2"/>
@@ -4341,6 +4797,7 @@
       <c r="E443" s="2"/>
       <c r="F443" s="2"/>
       <c r="G443" s="2"/>
+      <c r="H443" s="4"/>
     </row>
     <row r="444" ht="15.75" customHeight="1">
       <c r="A444" s="2"/>
@@ -4350,6 +4807,7 @@
       <c r="E444" s="2"/>
       <c r="F444" s="2"/>
       <c r="G444" s="2"/>
+      <c r="H444" s="4"/>
     </row>
     <row r="445" ht="15.75" customHeight="1">
       <c r="A445" s="2"/>
@@ -4359,6 +4817,7 @@
       <c r="E445" s="2"/>
       <c r="F445" s="2"/>
       <c r="G445" s="2"/>
+      <c r="H445" s="4"/>
     </row>
     <row r="446" ht="15.75" customHeight="1">
       <c r="A446" s="2"/>
@@ -4368,6 +4827,7 @@
       <c r="E446" s="2"/>
       <c r="F446" s="2"/>
       <c r="G446" s="2"/>
+      <c r="H446" s="4"/>
     </row>
     <row r="447" ht="15.75" customHeight="1">
       <c r="A447" s="2"/>
@@ -4377,6 +4837,7 @@
       <c r="E447" s="2"/>
       <c r="F447" s="2"/>
       <c r="G447" s="2"/>
+      <c r="H447" s="4"/>
     </row>
     <row r="448" ht="15.75" customHeight="1">
       <c r="A448" s="2"/>
@@ -4386,6 +4847,7 @@
       <c r="E448" s="2"/>
       <c r="F448" s="2"/>
       <c r="G448" s="2"/>
+      <c r="H448" s="4"/>
     </row>
     <row r="449" ht="15.75" customHeight="1">
       <c r="A449" s="2"/>
@@ -4395,6 +4857,7 @@
       <c r="E449" s="2"/>
       <c r="F449" s="2"/>
       <c r="G449" s="2"/>
+      <c r="H449" s="4"/>
     </row>
     <row r="450" ht="15.75" customHeight="1">
       <c r="A450" s="2"/>
@@ -4404,6 +4867,7 @@
       <c r="E450" s="2"/>
       <c r="F450" s="2"/>
       <c r="G450" s="2"/>
+      <c r="H450" s="4"/>
     </row>
     <row r="451" ht="15.75" customHeight="1">
       <c r="A451" s="2"/>
@@ -4413,6 +4877,7 @@
       <c r="E451" s="2"/>
       <c r="F451" s="2"/>
       <c r="G451" s="2"/>
+      <c r="H451" s="4"/>
     </row>
     <row r="452" ht="15.75" customHeight="1">
       <c r="A452" s="2"/>
@@ -4422,6 +4887,7 @@
       <c r="E452" s="2"/>
       <c r="F452" s="2"/>
       <c r="G452" s="2"/>
+      <c r="H452" s="4"/>
     </row>
     <row r="453" ht="15.75" customHeight="1">
       <c r="A453" s="2"/>
@@ -4431,6 +4897,7 @@
       <c r="E453" s="2"/>
       <c r="F453" s="2"/>
       <c r="G453" s="2"/>
+      <c r="H453" s="4"/>
     </row>
     <row r="454" ht="15.75" customHeight="1">
       <c r="A454" s="2"/>
@@ -4440,6 +4907,7 @@
       <c r="E454" s="2"/>
       <c r="F454" s="2"/>
       <c r="G454" s="2"/>
+      <c r="H454" s="4"/>
     </row>
     <row r="455" ht="15.75" customHeight="1">
       <c r="A455" s="2"/>
@@ -4449,6 +4917,7 @@
       <c r="E455" s="2"/>
       <c r="F455" s="2"/>
       <c r="G455" s="2"/>
+      <c r="H455" s="4"/>
     </row>
     <row r="456" ht="15.75" customHeight="1">
       <c r="A456" s="2"/>
@@ -4458,6 +4927,7 @@
       <c r="E456" s="2"/>
       <c r="F456" s="2"/>
       <c r="G456" s="2"/>
+      <c r="H456" s="4"/>
     </row>
     <row r="457" ht="15.75" customHeight="1">
       <c r="A457" s="2"/>
@@ -4467,6 +4937,7 @@
       <c r="E457" s="2"/>
       <c r="F457" s="2"/>
       <c r="G457" s="2"/>
+      <c r="H457" s="4"/>
     </row>
     <row r="458" ht="15.75" customHeight="1">
       <c r="A458" s="2"/>
@@ -4476,6 +4947,7 @@
       <c r="E458" s="2"/>
       <c r="F458" s="2"/>
       <c r="G458" s="2"/>
+      <c r="H458" s="4"/>
     </row>
     <row r="459" ht="15.75" customHeight="1">
       <c r="A459" s="2"/>
@@ -4485,6 +4957,7 @@
       <c r="E459" s="2"/>
       <c r="F459" s="2"/>
       <c r="G459" s="2"/>
+      <c r="H459" s="4"/>
     </row>
     <row r="460" ht="15.75" customHeight="1">
       <c r="A460" s="2"/>
@@ -4494,6 +4967,7 @@
       <c r="E460" s="2"/>
       <c r="F460" s="2"/>
       <c r="G460" s="2"/>
+      <c r="H460" s="4"/>
     </row>
     <row r="461" ht="15.75" customHeight="1">
       <c r="A461" s="2"/>
@@ -4503,6 +4977,7 @@
       <c r="E461" s="2"/>
       <c r="F461" s="2"/>
       <c r="G461" s="2"/>
+      <c r="H461" s="4"/>
     </row>
     <row r="462" ht="15.75" customHeight="1">
       <c r="A462" s="2"/>
@@ -4512,6 +4987,7 @@
       <c r="E462" s="2"/>
       <c r="F462" s="2"/>
       <c r="G462" s="2"/>
+      <c r="H462" s="4"/>
     </row>
     <row r="463" ht="15.75" customHeight="1">
       <c r="A463" s="2"/>
@@ -4521,6 +4997,7 @@
       <c r="E463" s="2"/>
       <c r="F463" s="2"/>
       <c r="G463" s="2"/>
+      <c r="H463" s="4"/>
     </row>
     <row r="464" ht="15.75" customHeight="1">
       <c r="A464" s="2"/>
@@ -4530,6 +5007,7 @@
       <c r="E464" s="2"/>
       <c r="F464" s="2"/>
       <c r="G464" s="2"/>
+      <c r="H464" s="4"/>
     </row>
     <row r="465" ht="15.75" customHeight="1">
       <c r="A465" s="2"/>
@@ -4539,6 +5017,7 @@
       <c r="E465" s="2"/>
       <c r="F465" s="2"/>
       <c r="G465" s="2"/>
+      <c r="H465" s="4"/>
     </row>
     <row r="466" ht="15.75" customHeight="1">
       <c r="A466" s="2"/>
@@ -4548,6 +5027,7 @@
       <c r="E466" s="2"/>
       <c r="F466" s="2"/>
       <c r="G466" s="2"/>
+      <c r="H466" s="4"/>
     </row>
     <row r="467" ht="15.75" customHeight="1">
       <c r="A467" s="2"/>
@@ -4557,6 +5037,7 @@
       <c r="E467" s="2"/>
       <c r="F467" s="2"/>
       <c r="G467" s="2"/>
+      <c r="H467" s="4"/>
     </row>
     <row r="468" ht="15.75" customHeight="1">
       <c r="A468" s="2"/>
@@ -4566,6 +5047,7 @@
       <c r="E468" s="2"/>
       <c r="F468" s="2"/>
       <c r="G468" s="2"/>
+      <c r="H468" s="4"/>
     </row>
     <row r="469" ht="15.75" customHeight="1">
       <c r="A469" s="2"/>
@@ -4575,6 +5057,7 @@
       <c r="E469" s="2"/>
       <c r="F469" s="2"/>
       <c r="G469" s="2"/>
+      <c r="H469" s="4"/>
     </row>
     <row r="470" ht="15.75" customHeight="1">
       <c r="A470" s="2"/>
@@ -4584,6 +5067,7 @@
       <c r="E470" s="2"/>
       <c r="F470" s="2"/>
       <c r="G470" s="2"/>
+      <c r="H470" s="4"/>
     </row>
     <row r="471" ht="15.75" customHeight="1">
       <c r="A471" s="2"/>
@@ -4593,6 +5077,7 @@
       <c r="E471" s="2"/>
       <c r="F471" s="2"/>
       <c r="G471" s="2"/>
+      <c r="H471" s="4"/>
     </row>
     <row r="472" ht="15.75" customHeight="1">
       <c r="A472" s="2"/>
@@ -4602,6 +5087,7 @@
       <c r="E472" s="2"/>
       <c r="F472" s="2"/>
       <c r="G472" s="2"/>
+      <c r="H472" s="4"/>
     </row>
     <row r="473" ht="15.75" customHeight="1">
       <c r="A473" s="2"/>
@@ -4611,6 +5097,7 @@
       <c r="E473" s="2"/>
       <c r="F473" s="2"/>
       <c r="G473" s="2"/>
+      <c r="H473" s="4"/>
     </row>
     <row r="474" ht="15.75" customHeight="1">
       <c r="A474" s="2"/>
@@ -4620,6 +5107,7 @@
       <c r="E474" s="2"/>
       <c r="F474" s="2"/>
       <c r="G474" s="2"/>
+      <c r="H474" s="4"/>
     </row>
     <row r="475" ht="15.75" customHeight="1">
       <c r="A475" s="2"/>
@@ -4629,6 +5117,7 @@
       <c r="E475" s="2"/>
       <c r="F475" s="2"/>
       <c r="G475" s="2"/>
+      <c r="H475" s="4"/>
     </row>
     <row r="476" ht="15.75" customHeight="1">
       <c r="A476" s="2"/>
@@ -4638,6 +5127,7 @@
       <c r="E476" s="2"/>
       <c r="F476" s="2"/>
       <c r="G476" s="2"/>
+      <c r="H476" s="4"/>
     </row>
     <row r="477" ht="15.75" customHeight="1">
       <c r="A477" s="2"/>
@@ -4647,6 +5137,7 @@
       <c r="E477" s="2"/>
       <c r="F477" s="2"/>
       <c r="G477" s="2"/>
+      <c r="H477" s="4"/>
     </row>
     <row r="478" ht="15.75" customHeight="1">
       <c r="A478" s="2"/>
@@ -4656,6 +5147,7 @@
       <c r="E478" s="2"/>
       <c r="F478" s="2"/>
       <c r="G478" s="2"/>
+      <c r="H478" s="4"/>
     </row>
     <row r="479" ht="15.75" customHeight="1">
       <c r="A479" s="2"/>
@@ -4665,6 +5157,7 @@
       <c r="E479" s="2"/>
       <c r="F479" s="2"/>
       <c r="G479" s="2"/>
+      <c r="H479" s="4"/>
     </row>
     <row r="480" ht="15.75" customHeight="1">
       <c r="A480" s="2"/>
@@ -4674,6 +5167,7 @@
       <c r="E480" s="2"/>
       <c r="F480" s="2"/>
       <c r="G480" s="2"/>
+      <c r="H480" s="4"/>
     </row>
     <row r="481" ht="15.75" customHeight="1">
       <c r="A481" s="2"/>
@@ -4683,6 +5177,7 @@
       <c r="E481" s="2"/>
       <c r="F481" s="2"/>
       <c r="G481" s="2"/>
+      <c r="H481" s="4"/>
     </row>
     <row r="482" ht="15.75" customHeight="1">
       <c r="A482" s="2"/>
@@ -4692,6 +5187,7 @@
       <c r="E482" s="2"/>
       <c r="F482" s="2"/>
       <c r="G482" s="2"/>
+      <c r="H482" s="4"/>
     </row>
     <row r="483" ht="15.75" customHeight="1">
       <c r="A483" s="2"/>
@@ -4701,6 +5197,7 @@
       <c r="E483" s="2"/>
       <c r="F483" s="2"/>
       <c r="G483" s="2"/>
+      <c r="H483" s="4"/>
     </row>
     <row r="484" ht="15.75" customHeight="1">
       <c r="A484" s="2"/>
@@ -4710,6 +5207,7 @@
       <c r="E484" s="2"/>
       <c r="F484" s="2"/>
       <c r="G484" s="2"/>
+      <c r="H484" s="4"/>
     </row>
     <row r="485" ht="15.75" customHeight="1">
       <c r="A485" s="2"/>
@@ -4719,6 +5217,7 @@
       <c r="E485" s="2"/>
       <c r="F485" s="2"/>
       <c r="G485" s="2"/>
+      <c r="H485" s="4"/>
     </row>
     <row r="486" ht="15.75" customHeight="1">
       <c r="A486" s="2"/>
@@ -4728,6 +5227,7 @@
       <c r="E486" s="2"/>
       <c r="F486" s="2"/>
       <c r="G486" s="2"/>
+      <c r="H486" s="4"/>
     </row>
     <row r="487" ht="15.75" customHeight="1">
       <c r="A487" s="2"/>
@@ -4737,6 +5237,7 @@
       <c r="E487" s="2"/>
       <c r="F487" s="2"/>
       <c r="G487" s="2"/>
+      <c r="H487" s="4"/>
     </row>
     <row r="488" ht="15.75" customHeight="1">
       <c r="A488" s="2"/>
@@ -4746,6 +5247,7 @@
       <c r="E488" s="2"/>
       <c r="F488" s="2"/>
       <c r="G488" s="2"/>
+      <c r="H488" s="4"/>
     </row>
     <row r="489" ht="15.75" customHeight="1">
       <c r="A489" s="2"/>
@@ -4755,6 +5257,7 @@
       <c r="E489" s="2"/>
       <c r="F489" s="2"/>
       <c r="G489" s="2"/>
+      <c r="H489" s="4"/>
     </row>
     <row r="490" ht="15.75" customHeight="1">
       <c r="A490" s="2"/>
@@ -4764,6 +5267,7 @@
       <c r="E490" s="2"/>
       <c r="F490" s="2"/>
       <c r="G490" s="2"/>
+      <c r="H490" s="4"/>
     </row>
     <row r="491" ht="15.75" customHeight="1">
       <c r="A491" s="2"/>
@@ -4773,6 +5277,7 @@
       <c r="E491" s="2"/>
       <c r="F491" s="2"/>
       <c r="G491" s="2"/>
+      <c r="H491" s="4"/>
     </row>
     <row r="492" ht="15.75" customHeight="1">
       <c r="A492" s="2"/>
@@ -4782,6 +5287,7 @@
       <c r="E492" s="2"/>
       <c r="F492" s="2"/>
       <c r="G492" s="2"/>
+      <c r="H492" s="4"/>
     </row>
     <row r="493" ht="15.75" customHeight="1">
       <c r="A493" s="2"/>
@@ -4791,6 +5297,7 @@
       <c r="E493" s="2"/>
       <c r="F493" s="2"/>
       <c r="G493" s="2"/>
+      <c r="H493" s="4"/>
     </row>
     <row r="494" ht="15.75" customHeight="1">
       <c r="A494" s="2"/>
@@ -4800,6 +5307,7 @@
       <c r="E494" s="2"/>
       <c r="F494" s="2"/>
       <c r="G494" s="2"/>
+      <c r="H494" s="4"/>
     </row>
     <row r="495" ht="15.75" customHeight="1">
       <c r="A495" s="2"/>
@@ -4809,6 +5317,7 @@
       <c r="E495" s="2"/>
       <c r="F495" s="2"/>
       <c r="G495" s="2"/>
+      <c r="H495" s="4"/>
     </row>
     <row r="496" ht="15.75" customHeight="1">
       <c r="A496" s="2"/>
@@ -4818,6 +5327,7 @@
       <c r="E496" s="2"/>
       <c r="F496" s="2"/>
       <c r="G496" s="2"/>
+      <c r="H496" s="4"/>
     </row>
     <row r="497" ht="15.75" customHeight="1">
       <c r="A497" s="2"/>
@@ -4827,6 +5337,7 @@
       <c r="E497" s="2"/>
       <c r="F497" s="2"/>
       <c r="G497" s="2"/>
+      <c r="H497" s="4"/>
     </row>
     <row r="498" ht="15.75" customHeight="1">
       <c r="A498" s="2"/>
@@ -4836,6 +5347,7 @@
       <c r="E498" s="2"/>
       <c r="F498" s="2"/>
       <c r="G498" s="2"/>
+      <c r="H498" s="4"/>
     </row>
     <row r="499" ht="15.75" customHeight="1">
       <c r="A499" s="2"/>
@@ -4845,6 +5357,7 @@
       <c r="E499" s="2"/>
       <c r="F499" s="2"/>
       <c r="G499" s="2"/>
+      <c r="H499" s="4"/>
     </row>
     <row r="500" ht="15.75" customHeight="1">
       <c r="A500" s="2"/>
@@ -4854,6 +5367,7 @@
       <c r="E500" s="2"/>
       <c r="F500" s="2"/>
       <c r="G500" s="2"/>
+      <c r="H500" s="4"/>
     </row>
     <row r="501" ht="15.75" customHeight="1">
       <c r="A501" s="2"/>
@@ -4863,6 +5377,7 @@
       <c r="E501" s="2"/>
       <c r="F501" s="2"/>
       <c r="G501" s="2"/>
+      <c r="H501" s="4"/>
     </row>
     <row r="502" ht="15.75" customHeight="1">
       <c r="A502" s="2"/>
@@ -4872,6 +5387,7 @@
       <c r="E502" s="2"/>
       <c r="F502" s="2"/>
       <c r="G502" s="2"/>
+      <c r="H502" s="4"/>
     </row>
     <row r="503" ht="15.75" customHeight="1">
       <c r="A503" s="2"/>
@@ -4881,6 +5397,7 @@
       <c r="E503" s="2"/>
       <c r="F503" s="2"/>
       <c r="G503" s="2"/>
+      <c r="H503" s="4"/>
     </row>
     <row r="504" ht="15.75" customHeight="1">
       <c r="A504" s="2"/>
@@ -4890,6 +5407,7 @@
       <c r="E504" s="2"/>
       <c r="F504" s="2"/>
       <c r="G504" s="2"/>
+      <c r="H504" s="4"/>
     </row>
     <row r="505" ht="15.75" customHeight="1">
       <c r="A505" s="2"/>
@@ -4899,6 +5417,7 @@
       <c r="E505" s="2"/>
       <c r="F505" s="2"/>
       <c r="G505" s="2"/>
+      <c r="H505" s="4"/>
     </row>
     <row r="506" ht="15.75" customHeight="1">
       <c r="A506" s="2"/>
@@ -4908,6 +5427,7 @@
       <c r="E506" s="2"/>
       <c r="F506" s="2"/>
       <c r="G506" s="2"/>
+      <c r="H506" s="4"/>
     </row>
     <row r="507" ht="15.75" customHeight="1">
       <c r="A507" s="2"/>
@@ -4917,6 +5437,7 @@
       <c r="E507" s="2"/>
       <c r="F507" s="2"/>
       <c r="G507" s="2"/>
+      <c r="H507" s="4"/>
     </row>
     <row r="508" ht="15.75" customHeight="1">
       <c r="A508" s="2"/>
@@ -4926,6 +5447,7 @@
       <c r="E508" s="2"/>
       <c r="F508" s="2"/>
       <c r="G508" s="2"/>
+      <c r="H508" s="4"/>
     </row>
     <row r="509" ht="15.75" customHeight="1">
       <c r="A509" s="2"/>
@@ -4935,6 +5457,7 @@
       <c r="E509" s="2"/>
       <c r="F509" s="2"/>
       <c r="G509" s="2"/>
+      <c r="H509" s="4"/>
     </row>
     <row r="510" ht="15.75" customHeight="1">
       <c r="A510" s="2"/>
@@ -4944,6 +5467,7 @@
       <c r="E510" s="2"/>
       <c r="F510" s="2"/>
       <c r="G510" s="2"/>
+      <c r="H510" s="4"/>
     </row>
     <row r="511" ht="15.75" customHeight="1">
       <c r="A511" s="2"/>
@@ -4953,6 +5477,7 @@
       <c r="E511" s="2"/>
       <c r="F511" s="2"/>
       <c r="G511" s="2"/>
+      <c r="H511" s="4"/>
     </row>
     <row r="512" ht="15.75" customHeight="1">
       <c r="A512" s="2"/>
@@ -4962,6 +5487,7 @@
       <c r="E512" s="2"/>
       <c r="F512" s="2"/>
       <c r="G512" s="2"/>
+      <c r="H512" s="4"/>
     </row>
     <row r="513" ht="15.75" customHeight="1">
       <c r="A513" s="2"/>
@@ -4971,6 +5497,7 @@
       <c r="E513" s="2"/>
       <c r="F513" s="2"/>
       <c r="G513" s="2"/>
+      <c r="H513" s="4"/>
     </row>
     <row r="514" ht="15.75" customHeight="1">
       <c r="A514" s="2"/>
@@ -4980,6 +5507,7 @@
       <c r="E514" s="2"/>
       <c r="F514" s="2"/>
       <c r="G514" s="2"/>
+      <c r="H514" s="4"/>
     </row>
     <row r="515" ht="15.75" customHeight="1">
       <c r="A515" s="2"/>
@@ -4989,6 +5517,7 @@
       <c r="E515" s="2"/>
       <c r="F515" s="2"/>
       <c r="G515" s="2"/>
+      <c r="H515" s="4"/>
     </row>
     <row r="516" ht="15.75" customHeight="1">
       <c r="A516" s="2"/>
@@ -4998,6 +5527,7 @@
       <c r="E516" s="2"/>
       <c r="F516" s="2"/>
       <c r="G516" s="2"/>
+      <c r="H516" s="4"/>
     </row>
     <row r="517" ht="15.75" customHeight="1">
       <c r="A517" s="2"/>
@@ -5007,6 +5537,7 @@
       <c r="E517" s="2"/>
       <c r="F517" s="2"/>
       <c r="G517" s="2"/>
+      <c r="H517" s="4"/>
     </row>
     <row r="518" ht="15.75" customHeight="1">
       <c r="A518" s="2"/>
@@ -5016,6 +5547,7 @@
       <c r="E518" s="2"/>
       <c r="F518" s="2"/>
       <c r="G518" s="2"/>
+      <c r="H518" s="4"/>
     </row>
     <row r="519" ht="15.75" customHeight="1">
       <c r="A519" s="2"/>
@@ -5025,6 +5557,7 @@
       <c r="E519" s="2"/>
       <c r="F519" s="2"/>
       <c r="G519" s="2"/>
+      <c r="H519" s="4"/>
     </row>
     <row r="520" ht="15.75" customHeight="1">
       <c r="A520" s="2"/>
@@ -5034,6 +5567,7 @@
       <c r="E520" s="2"/>
       <c r="F520" s="2"/>
       <c r="G520" s="2"/>
+      <c r="H520" s="4"/>
     </row>
     <row r="521" ht="15.75" customHeight="1">
       <c r="A521" s="2"/>
@@ -5043,6 +5577,7 @@
       <c r="E521" s="2"/>
       <c r="F521" s="2"/>
       <c r="G521" s="2"/>
+      <c r="H521" s="4"/>
     </row>
     <row r="522" ht="15.75" customHeight="1">
       <c r="A522" s="2"/>
@@ -5052,6 +5587,7 @@
       <c r="E522" s="2"/>
       <c r="F522" s="2"/>
       <c r="G522" s="2"/>
+      <c r="H522" s="4"/>
     </row>
     <row r="523" ht="15.75" customHeight="1">
       <c r="A523" s="2"/>
@@ -5061,6 +5597,7 @@
       <c r="E523" s="2"/>
       <c r="F523" s="2"/>
       <c r="G523" s="2"/>
+      <c r="H523" s="4"/>
     </row>
     <row r="524" ht="15.75" customHeight="1">
       <c r="A524" s="2"/>
@@ -5070,6 +5607,7 @@
       <c r="E524" s="2"/>
       <c r="F524" s="2"/>
       <c r="G524" s="2"/>
+      <c r="H524" s="4"/>
     </row>
     <row r="525" ht="15.75" customHeight="1">
       <c r="A525" s="2"/>
@@ -5079,6 +5617,7 @@
       <c r="E525" s="2"/>
       <c r="F525" s="2"/>
       <c r="G525" s="2"/>
+      <c r="H525" s="4"/>
     </row>
     <row r="526" ht="15.75" customHeight="1">
       <c r="A526" s="2"/>
@@ -5088,6 +5627,7 @@
       <c r="E526" s="2"/>
       <c r="F526" s="2"/>
       <c r="G526" s="2"/>
+      <c r="H526" s="4"/>
     </row>
     <row r="527" ht="15.75" customHeight="1">
       <c r="A527" s="2"/>
@@ -5097,6 +5637,7 @@
       <c r="E527" s="2"/>
       <c r="F527" s="2"/>
       <c r="G527" s="2"/>
+      <c r="H527" s="4"/>
     </row>
     <row r="528" ht="15.75" customHeight="1">
       <c r="A528" s="2"/>
@@ -5106,6 +5647,7 @@
       <c r="E528" s="2"/>
       <c r="F528" s="2"/>
       <c r="G528" s="2"/>
+      <c r="H528" s="4"/>
     </row>
     <row r="529" ht="15.75" customHeight="1">
       <c r="A529" s="2"/>
@@ -5115,6 +5657,7 @@
       <c r="E529" s="2"/>
       <c r="F529" s="2"/>
       <c r="G529" s="2"/>
+      <c r="H529" s="4"/>
     </row>
     <row r="530" ht="15.75" customHeight="1">
       <c r="A530" s="2"/>
@@ -5124,6 +5667,7 @@
       <c r="E530" s="2"/>
       <c r="F530" s="2"/>
       <c r="G530" s="2"/>
+      <c r="H530" s="4"/>
     </row>
     <row r="531" ht="15.75" customHeight="1">
       <c r="A531" s="2"/>
@@ -5133,6 +5677,7 @@
       <c r="E531" s="2"/>
       <c r="F531" s="2"/>
       <c r="G531" s="2"/>
+      <c r="H531" s="4"/>
     </row>
     <row r="532" ht="15.75" customHeight="1">
       <c r="A532" s="2"/>
@@ -5142,6 +5687,7 @@
       <c r="E532" s="2"/>
       <c r="F532" s="2"/>
       <c r="G532" s="2"/>
+      <c r="H532" s="4"/>
     </row>
     <row r="533" ht="15.75" customHeight="1">
       <c r="A533" s="2"/>
@@ -5151,6 +5697,7 @@
       <c r="E533" s="2"/>
       <c r="F533" s="2"/>
       <c r="G533" s="2"/>
+      <c r="H533" s="4"/>
     </row>
     <row r="534" ht="15.75" customHeight="1">
       <c r="A534" s="2"/>
@@ -5160,6 +5707,7 @@
       <c r="E534" s="2"/>
       <c r="F534" s="2"/>
       <c r="G534" s="2"/>
+      <c r="H534" s="4"/>
     </row>
     <row r="535" ht="15.75" customHeight="1">
       <c r="A535" s="2"/>
@@ -5169,6 +5717,7 @@
       <c r="E535" s="2"/>
       <c r="F535" s="2"/>
       <c r="G535" s="2"/>
+      <c r="H535" s="4"/>
     </row>
     <row r="536" ht="15.75" customHeight="1">
       <c r="A536" s="2"/>
@@ -5178,6 +5727,7 @@
       <c r="E536" s="2"/>
       <c r="F536" s="2"/>
       <c r="G536" s="2"/>
+      <c r="H536" s="4"/>
     </row>
     <row r="537" ht="15.75" customHeight="1">
       <c r="A537" s="2"/>
@@ -5187,6 +5737,7 @@
       <c r="E537" s="2"/>
       <c r="F537" s="2"/>
       <c r="G537" s="2"/>
+      <c r="H537" s="4"/>
     </row>
     <row r="538" ht="15.75" customHeight="1">
       <c r="A538" s="2"/>
@@ -5196,6 +5747,7 @@
       <c r="E538" s="2"/>
       <c r="F538" s="2"/>
       <c r="G538" s="2"/>
+      <c r="H538" s="4"/>
     </row>
     <row r="539" ht="15.75" customHeight="1">
       <c r="A539" s="2"/>
@@ -5205,6 +5757,7 @@
       <c r="E539" s="2"/>
       <c r="F539" s="2"/>
       <c r="G539" s="2"/>
+      <c r="H539" s="4"/>
     </row>
     <row r="540" ht="15.75" customHeight="1">
       <c r="A540" s="2"/>
@@ -5214,6 +5767,7 @@
       <c r="E540" s="2"/>
       <c r="F540" s="2"/>
       <c r="G540" s="2"/>
+      <c r="H540" s="4"/>
     </row>
     <row r="541" ht="15.75" customHeight="1">
       <c r="A541" s="2"/>
@@ -5223,6 +5777,7 @@
       <c r="E541" s="2"/>
       <c r="F541" s="2"/>
       <c r="G541" s="2"/>
+      <c r="H541" s="4"/>
     </row>
     <row r="542" ht="15.75" customHeight="1">
       <c r="A542" s="2"/>
@@ -5232,6 +5787,7 @@
       <c r="E542" s="2"/>
       <c r="F542" s="2"/>
       <c r="G542" s="2"/>
+      <c r="H542" s="4"/>
     </row>
     <row r="543" ht="15.75" customHeight="1">
       <c r="A543" s="2"/>
@@ -5241,6 +5797,7 @@
       <c r="E543" s="2"/>
       <c r="F543" s="2"/>
       <c r="G543" s="2"/>
+      <c r="H543" s="4"/>
     </row>
     <row r="544" ht="15.75" customHeight="1">
       <c r="A544" s="2"/>
@@ -5250,6 +5807,7 @@
       <c r="E544" s="2"/>
       <c r="F544" s="2"/>
       <c r="G544" s="2"/>
+      <c r="H544" s="4"/>
     </row>
     <row r="545" ht="15.75" customHeight="1">
       <c r="A545" s="2"/>
@@ -5259,6 +5817,7 @@
       <c r="E545" s="2"/>
       <c r="F545" s="2"/>
       <c r="G545" s="2"/>
+      <c r="H545" s="4"/>
     </row>
     <row r="546" ht="15.75" customHeight="1">
       <c r="A546" s="2"/>
@@ -5268,6 +5827,7 @@
       <c r="E546" s="2"/>
       <c r="F546" s="2"/>
       <c r="G546" s="2"/>
+      <c r="H546" s="4"/>
     </row>
     <row r="547" ht="15.75" customHeight="1">
       <c r="A547" s="2"/>
@@ -5277,6 +5837,7 @@
       <c r="E547" s="2"/>
       <c r="F547" s="2"/>
       <c r="G547" s="2"/>
+      <c r="H547" s="4"/>
     </row>
     <row r="548" ht="15.75" customHeight="1">
       <c r="A548" s="2"/>
@@ -5286,6 +5847,7 @@
       <c r="E548" s="2"/>
       <c r="F548" s="2"/>
       <c r="G548" s="2"/>
+      <c r="H548" s="4"/>
     </row>
     <row r="549" ht="15.75" customHeight="1">
       <c r="A549" s="2"/>
@@ -5295,6 +5857,7 @@
       <c r="E549" s="2"/>
       <c r="F549" s="2"/>
       <c r="G549" s="2"/>
+      <c r="H549" s="4"/>
     </row>
     <row r="550" ht="15.75" customHeight="1">
       <c r="A550" s="2"/>
@@ -5304,6 +5867,7 @@
       <c r="E550" s="2"/>
       <c r="F550" s="2"/>
       <c r="G550" s="2"/>
+      <c r="H550" s="4"/>
     </row>
     <row r="551" ht="15.75" customHeight="1">
       <c r="A551" s="2"/>
@@ -5313,6 +5877,7 @@
       <c r="E551" s="2"/>
       <c r="F551" s="2"/>
       <c r="G551" s="2"/>
+      <c r="H551" s="4"/>
     </row>
     <row r="552" ht="15.75" customHeight="1">
       <c r="A552" s="2"/>
@@ -5322,6 +5887,7 @@
       <c r="E552" s="2"/>
       <c r="F552" s="2"/>
       <c r="G552" s="2"/>
+      <c r="H552" s="4"/>
     </row>
     <row r="553" ht="15.75" customHeight="1">
       <c r="A553" s="2"/>
@@ -5331,6 +5897,7 @@
       <c r="E553" s="2"/>
       <c r="F553" s="2"/>
       <c r="G553" s="2"/>
+      <c r="H553" s="4"/>
     </row>
     <row r="554" ht="15.75" customHeight="1">
       <c r="A554" s="2"/>
@@ -5340,6 +5907,7 @@
       <c r="E554" s="2"/>
       <c r="F554" s="2"/>
       <c r="G554" s="2"/>
+      <c r="H554" s="4"/>
     </row>
     <row r="555" ht="15.75" customHeight="1">
       <c r="A555" s="2"/>
@@ -5349,6 +5917,7 @@
       <c r="E555" s="2"/>
       <c r="F555" s="2"/>
       <c r="G555" s="2"/>
+      <c r="H555" s="4"/>
     </row>
     <row r="556" ht="15.75" customHeight="1">
       <c r="A556" s="2"/>
@@ -5358,6 +5927,7 @@
       <c r="E556" s="2"/>
       <c r="F556" s="2"/>
       <c r="G556" s="2"/>
+      <c r="H556" s="4"/>
     </row>
     <row r="557" ht="15.75" customHeight="1">
       <c r="A557" s="2"/>
@@ -5367,6 +5937,7 @@
       <c r="E557" s="2"/>
       <c r="F557" s="2"/>
       <c r="G557" s="2"/>
+      <c r="H557" s="4"/>
     </row>
     <row r="558" ht="15.75" customHeight="1">
       <c r="A558" s="2"/>
@@ -5376,6 +5947,7 @@
       <c r="E558" s="2"/>
       <c r="F558" s="2"/>
       <c r="G558" s="2"/>
+      <c r="H558" s="4"/>
     </row>
     <row r="559" ht="15.75" customHeight="1">
       <c r="A559" s="2"/>
@@ -5385,6 +5957,7 @@
       <c r="E559" s="2"/>
       <c r="F559" s="2"/>
       <c r="G559" s="2"/>
+      <c r="H559" s="4"/>
     </row>
     <row r="560" ht="15.75" customHeight="1">
       <c r="A560" s="2"/>
@@ -5394,6 +5967,7 @@
       <c r="E560" s="2"/>
       <c r="F560" s="2"/>
       <c r="G560" s="2"/>
+      <c r="H560" s="4"/>
     </row>
     <row r="561" ht="15.75" customHeight="1">
       <c r="A561" s="2"/>
@@ -5403,6 +5977,7 @@
       <c r="E561" s="2"/>
       <c r="F561" s="2"/>
       <c r="G561" s="2"/>
+      <c r="H561" s="4"/>
     </row>
     <row r="562" ht="15.75" customHeight="1">
       <c r="A562" s="2"/>
@@ -5412,6 +5987,7 @@
       <c r="E562" s="2"/>
       <c r="F562" s="2"/>
       <c r="G562" s="2"/>
+      <c r="H562" s="4"/>
     </row>
     <row r="563" ht="15.75" customHeight="1">
       <c r="A563" s="2"/>
@@ -5421,6 +5997,7 @@
       <c r="E563" s="2"/>
       <c r="F563" s="2"/>
       <c r="G563" s="2"/>
+      <c r="H563" s="4"/>
     </row>
     <row r="564" ht="15.75" customHeight="1">
       <c r="A564" s="2"/>
@@ -5430,6 +6007,7 @@
       <c r="E564" s="2"/>
       <c r="F564" s="2"/>
       <c r="G564" s="2"/>
+      <c r="H564" s="4"/>
     </row>
     <row r="565" ht="15.75" customHeight="1">
       <c r="A565" s="2"/>
@@ -5439,6 +6017,7 @@
       <c r="E565" s="2"/>
       <c r="F565" s="2"/>
       <c r="G565" s="2"/>
+      <c r="H565" s="4"/>
     </row>
     <row r="566" ht="15.75" customHeight="1">
       <c r="A566" s="2"/>
@@ -5448,6 +6027,7 @@
       <c r="E566" s="2"/>
       <c r="F566" s="2"/>
       <c r="G566" s="2"/>
+      <c r="H566" s="4"/>
     </row>
     <row r="567" ht="15.75" customHeight="1">
       <c r="A567" s="2"/>
@@ -5457,6 +6037,7 @@
       <c r="E567" s="2"/>
       <c r="F567" s="2"/>
       <c r="G567" s="2"/>
+      <c r="H567" s="4"/>
     </row>
     <row r="568" ht="15.75" customHeight="1">
       <c r="A568" s="2"/>
@@ -5466,6 +6047,7 @@
       <c r="E568" s="2"/>
       <c r="F568" s="2"/>
       <c r="G568" s="2"/>
+      <c r="H568" s="4"/>
     </row>
     <row r="569" ht="15.75" customHeight="1">
       <c r="A569" s="2"/>
@@ -5475,6 +6057,7 @@
       <c r="E569" s="2"/>
       <c r="F569" s="2"/>
       <c r="G569" s="2"/>
+      <c r="H569" s="4"/>
     </row>
     <row r="570" ht="15.75" customHeight="1">
       <c r="A570" s="2"/>
@@ -5484,6 +6067,7 @@
       <c r="E570" s="2"/>
       <c r="F570" s="2"/>
       <c r="G570" s="2"/>
+      <c r="H570" s="4"/>
     </row>
     <row r="571" ht="15.75" customHeight="1">
       <c r="A571" s="2"/>
@@ -5493,6 +6077,7 @@
       <c r="E571" s="2"/>
       <c r="F571" s="2"/>
       <c r="G571" s="2"/>
+      <c r="H571" s="4"/>
     </row>
     <row r="572" ht="15.75" customHeight="1">
       <c r="A572" s="2"/>
@@ -5502,6 +6087,7 @@
       <c r="E572" s="2"/>
       <c r="F572" s="2"/>
       <c r="G572" s="2"/>
+      <c r="H572" s="4"/>
     </row>
     <row r="573" ht="15.75" customHeight="1">
       <c r="A573" s="2"/>
@@ -5511,6 +6097,7 @@
       <c r="E573" s="2"/>
       <c r="F573" s="2"/>
       <c r="G573" s="2"/>
+      <c r="H573" s="4"/>
     </row>
     <row r="574" ht="15.75" customHeight="1">
       <c r="A574" s="2"/>
@@ -5520,6 +6107,7 @@
       <c r="E574" s="2"/>
       <c r="F574" s="2"/>
       <c r="G574" s="2"/>
+      <c r="H574" s="4"/>
     </row>
     <row r="575" ht="15.75" customHeight="1">
       <c r="A575" s="2"/>
@@ -5529,6 +6117,7 @@
       <c r="E575" s="2"/>
       <c r="F575" s="2"/>
       <c r="G575" s="2"/>
+      <c r="H575" s="4"/>
     </row>
     <row r="576" ht="15.75" customHeight="1">
       <c r="A576" s="2"/>
@@ -5538,6 +6127,7 @@
       <c r="E576" s="2"/>
       <c r="F576" s="2"/>
       <c r="G576" s="2"/>
+      <c r="H576" s="4"/>
     </row>
     <row r="577" ht="15.75" customHeight="1">
       <c r="A577" s="2"/>
@@ -5547,6 +6137,7 @@
       <c r="E577" s="2"/>
       <c r="F577" s="2"/>
       <c r="G577" s="2"/>
+      <c r="H577" s="4"/>
     </row>
     <row r="578" ht="15.75" customHeight="1">
       <c r="A578" s="2"/>
@@ -5556,6 +6147,7 @@
       <c r="E578" s="2"/>
       <c r="F578" s="2"/>
       <c r="G578" s="2"/>
+      <c r="H578" s="4"/>
     </row>
     <row r="579" ht="15.75" customHeight="1">
       <c r="A579" s="2"/>
@@ -5565,6 +6157,7 @@
       <c r="E579" s="2"/>
       <c r="F579" s="2"/>
       <c r="G579" s="2"/>
+      <c r="H579" s="4"/>
     </row>
     <row r="580" ht="15.75" customHeight="1">
       <c r="A580" s="2"/>
@@ -5574,6 +6167,7 @@
       <c r="E580" s="2"/>
       <c r="F580" s="2"/>
       <c r="G580" s="2"/>
+      <c r="H580" s="4"/>
     </row>
     <row r="581" ht="15.75" customHeight="1">
       <c r="A581" s="2"/>
@@ -5583,6 +6177,7 @@
       <c r="E581" s="2"/>
       <c r="F581" s="2"/>
       <c r="G581" s="2"/>
+      <c r="H581" s="4"/>
     </row>
     <row r="582" ht="15.75" customHeight="1">
       <c r="A582" s="2"/>
@@ -5592,6 +6187,7 @@
       <c r="E582" s="2"/>
       <c r="F582" s="2"/>
       <c r="G582" s="2"/>
+      <c r="H582" s="4"/>
     </row>
     <row r="583" ht="15.75" customHeight="1">
       <c r="A583" s="2"/>
@@ -5601,6 +6197,7 @@
       <c r="E583" s="2"/>
       <c r="F583" s="2"/>
       <c r="G583" s="2"/>
+      <c r="H583" s="4"/>
     </row>
     <row r="584" ht="15.75" customHeight="1">
       <c r="A584" s="2"/>
@@ -5610,6 +6207,7 @@
       <c r="E584" s="2"/>
       <c r="F584" s="2"/>
       <c r="G584" s="2"/>
+      <c r="H584" s="4"/>
     </row>
     <row r="585" ht="15.75" customHeight="1">
       <c r="A585" s="2"/>
@@ -5619,6 +6217,7 @@
       <c r="E585" s="2"/>
       <c r="F585" s="2"/>
       <c r="G585" s="2"/>
+      <c r="H585" s="4"/>
     </row>
     <row r="586" ht="15.75" customHeight="1">
       <c r="A586" s="2"/>
@@ -5628,6 +6227,7 @@
       <c r="E586" s="2"/>
       <c r="F586" s="2"/>
       <c r="G586" s="2"/>
+      <c r="H586" s="4"/>
     </row>
     <row r="587" ht="15.75" customHeight="1">
       <c r="A587" s="2"/>
@@ -5637,6 +6237,7 @@
       <c r="E587" s="2"/>
       <c r="F587" s="2"/>
       <c r="G587" s="2"/>
+      <c r="H587" s="4"/>
     </row>
     <row r="588" ht="15.75" customHeight="1">
       <c r="A588" s="2"/>
@@ -5646,6 +6247,7 @@
       <c r="E588" s="2"/>
       <c r="F588" s="2"/>
       <c r="G588" s="2"/>
+      <c r="H588" s="4"/>
     </row>
     <row r="589" ht="15.75" customHeight="1">
       <c r="A589" s="2"/>
@@ -5655,6 +6257,7 @@
       <c r="E589" s="2"/>
       <c r="F589" s="2"/>
       <c r="G589" s="2"/>
+      <c r="H589" s="4"/>
     </row>
     <row r="590" ht="15.75" customHeight="1">
       <c r="A590" s="2"/>
@@ -5664,6 +6267,7 @@
       <c r="E590" s="2"/>
       <c r="F590" s="2"/>
       <c r="G590" s="2"/>
+      <c r="H590" s="4"/>
     </row>
     <row r="591" ht="15.75" customHeight="1">
       <c r="A591" s="2"/>
@@ -5673,6 +6277,7 @@
       <c r="E591" s="2"/>
       <c r="F591" s="2"/>
       <c r="G591" s="2"/>
+      <c r="H591" s="4"/>
     </row>
     <row r="592" ht="15.75" customHeight="1">
       <c r="A592" s="2"/>
@@ -5682,6 +6287,7 @@
       <c r="E592" s="2"/>
       <c r="F592" s="2"/>
       <c r="G592" s="2"/>
+      <c r="H592" s="4"/>
     </row>
     <row r="593" ht="15.75" customHeight="1">
       <c r="A593" s="2"/>
@@ -5691,6 +6297,7 @@
       <c r="E593" s="2"/>
       <c r="F593" s="2"/>
       <c r="G593" s="2"/>
+      <c r="H593" s="4"/>
     </row>
     <row r="594" ht="15.75" customHeight="1">
       <c r="A594" s="2"/>
@@ -5700,6 +6307,7 @@
       <c r="E594" s="2"/>
       <c r="F594" s="2"/>
       <c r="G594" s="2"/>
+      <c r="H594" s="4"/>
     </row>
     <row r="595" ht="15.75" customHeight="1">
       <c r="A595" s="2"/>
@@ -5709,6 +6317,7 @@
       <c r="E595" s="2"/>
       <c r="F595" s="2"/>
       <c r="G595" s="2"/>
+      <c r="H595" s="4"/>
     </row>
     <row r="596" ht="15.75" customHeight="1">
       <c r="A596" s="2"/>
@@ -5718,6 +6327,7 @@
       <c r="E596" s="2"/>
       <c r="F596" s="2"/>
       <c r="G596" s="2"/>
+      <c r="H596" s="4"/>
     </row>
     <row r="597" ht="15.75" customHeight="1">
       <c r="A597" s="2"/>
@@ -5727,6 +6337,7 @@
       <c r="E597" s="2"/>
       <c r="F597" s="2"/>
       <c r="G597" s="2"/>
+      <c r="H597" s="4"/>
     </row>
     <row r="598" ht="15.75" customHeight="1">
       <c r="A598" s="2"/>
@@ -5736,6 +6347,7 @@
       <c r="E598" s="2"/>
       <c r="F598" s="2"/>
       <c r="G598" s="2"/>
+      <c r="H598" s="4"/>
     </row>
     <row r="599" ht="15.75" customHeight="1">
       <c r="A599" s="2"/>
@@ -5745,6 +6357,7 @@
       <c r="E599" s="2"/>
       <c r="F599" s="2"/>
       <c r="G599" s="2"/>
+      <c r="H599" s="4"/>
     </row>
     <row r="600" ht="15.75" customHeight="1">
       <c r="A600" s="2"/>
@@ -5754,6 +6367,7 @@
       <c r="E600" s="2"/>
       <c r="F600" s="2"/>
       <c r="G600" s="2"/>
+      <c r="H600" s="4"/>
     </row>
     <row r="601" ht="15.75" customHeight="1">
       <c r="A601" s="2"/>
@@ -5763,6 +6377,7 @@
       <c r="E601" s="2"/>
       <c r="F601" s="2"/>
       <c r="G601" s="2"/>
+      <c r="H601" s="4"/>
     </row>
     <row r="602" ht="15.75" customHeight="1">
       <c r="A602" s="2"/>
@@ -5772,6 +6387,7 @@
       <c r="E602" s="2"/>
       <c r="F602" s="2"/>
       <c r="G602" s="2"/>
+      <c r="H602" s="4"/>
     </row>
     <row r="603" ht="15.75" customHeight="1">
       <c r="A603" s="2"/>
@@ -5781,6 +6397,7 @@
       <c r="E603" s="2"/>
       <c r="F603" s="2"/>
       <c r="G603" s="2"/>
+      <c r="H603" s="4"/>
     </row>
     <row r="604" ht="15.75" customHeight="1">
       <c r="A604" s="2"/>
@@ -5790,6 +6407,7 @@
       <c r="E604" s="2"/>
       <c r="F604" s="2"/>
       <c r="G604" s="2"/>
+      <c r="H604" s="4"/>
     </row>
     <row r="605" ht="15.75" customHeight="1">
       <c r="A605" s="2"/>
@@ -5799,6 +6417,7 @@
       <c r="E605" s="2"/>
       <c r="F605" s="2"/>
       <c r="G605" s="2"/>
+      <c r="H605" s="4"/>
     </row>
     <row r="606" ht="15.75" customHeight="1">
       <c r="A606" s="2"/>
@@ -5808,6 +6427,7 @@
       <c r="E606" s="2"/>
       <c r="F606" s="2"/>
       <c r="G606" s="2"/>
+      <c r="H606" s="4"/>
     </row>
     <row r="607" ht="15.75" customHeight="1">
       <c r="A607" s="2"/>
@@ -5817,6 +6437,7 @@
       <c r="E607" s="2"/>
       <c r="F607" s="2"/>
       <c r="G607" s="2"/>
+      <c r="H607" s="4"/>
     </row>
     <row r="608" ht="15.75" customHeight="1">
       <c r="A608" s="2"/>
@@ -5826,6 +6447,7 @@
       <c r="E608" s="2"/>
       <c r="F608" s="2"/>
       <c r="G608" s="2"/>
+      <c r="H608" s="4"/>
     </row>
     <row r="609" ht="15.75" customHeight="1">
       <c r="A609" s="2"/>
@@ -5835,6 +6457,7 @@
       <c r="E609" s="2"/>
       <c r="F609" s="2"/>
       <c r="G609" s="2"/>
+      <c r="H609" s="4"/>
     </row>
     <row r="610" ht="15.75" customHeight="1">
       <c r="A610" s="2"/>
@@ -5844,6 +6467,7 @@
       <c r="E610" s="2"/>
       <c r="F610" s="2"/>
       <c r="G610" s="2"/>
+      <c r="H610" s="4"/>
     </row>
     <row r="611" ht="15.75" customHeight="1">
       <c r="A611" s="2"/>
@@ -5853,6 +6477,7 @@
       <c r="E611" s="2"/>
       <c r="F611" s="2"/>
       <c r="G611" s="2"/>
+      <c r="H611" s="4"/>
     </row>
     <row r="612" ht="15.75" customHeight="1">
       <c r="A612" s="2"/>
@@ -5862,6 +6487,7 @@
       <c r="E612" s="2"/>
       <c r="F612" s="2"/>
       <c r="G612" s="2"/>
+      <c r="H612" s="4"/>
     </row>
     <row r="613" ht="15.75" customHeight="1">
       <c r="A613" s="2"/>
@@ -5871,6 +6497,7 @@
       <c r="E613" s="2"/>
       <c r="F613" s="2"/>
       <c r="G613" s="2"/>
+      <c r="H613" s="4"/>
     </row>
     <row r="614" ht="15.75" customHeight="1">
       <c r="A614" s="2"/>
@@ -5880,6 +6507,7 @@
       <c r="E614" s="2"/>
       <c r="F614" s="2"/>
       <c r="G614" s="2"/>
+      <c r="H614" s="4"/>
     </row>
     <row r="615" ht="15.75" customHeight="1">
       <c r="A615" s="2"/>
@@ -5889,6 +6517,7 @@
       <c r="E615" s="2"/>
       <c r="F615" s="2"/>
       <c r="G615" s="2"/>
+      <c r="H615" s="4"/>
     </row>
     <row r="616" ht="15.75" customHeight="1">
       <c r="A616" s="2"/>
@@ -5898,6 +6527,7 @@
       <c r="E616" s="2"/>
       <c r="F616" s="2"/>
       <c r="G616" s="2"/>
+      <c r="H616" s="4"/>
     </row>
     <row r="617" ht="15.75" customHeight="1">
       <c r="A617" s="2"/>
@@ -5907,6 +6537,7 @@
       <c r="E617" s="2"/>
       <c r="F617" s="2"/>
       <c r="G617" s="2"/>
+      <c r="H617" s="4"/>
     </row>
     <row r="618" ht="15.75" customHeight="1">
       <c r="A618" s="2"/>
@@ -5916,6 +6547,7 @@
       <c r="E618" s="2"/>
       <c r="F618" s="2"/>
       <c r="G618" s="2"/>
+      <c r="H618" s="4"/>
     </row>
     <row r="619" ht="15.75" customHeight="1">
       <c r="A619" s="2"/>
@@ -5925,6 +6557,7 @@
       <c r="E619" s="2"/>
       <c r="F619" s="2"/>
       <c r="G619" s="2"/>
+      <c r="H619" s="4"/>
     </row>
     <row r="620" ht="15.75" customHeight="1">
       <c r="A620" s="2"/>
@@ -5934,6 +6567,7 @@
       <c r="E620" s="2"/>
       <c r="F620" s="2"/>
       <c r="G620" s="2"/>
+      <c r="H620" s="4"/>
     </row>
     <row r="621" ht="15.75" customHeight="1">
       <c r="A621" s="2"/>
@@ -5943,6 +6577,7 @@
       <c r="E621" s="2"/>
       <c r="F621" s="2"/>
       <c r="G621" s="2"/>
+      <c r="H621" s="4"/>
     </row>
     <row r="622" ht="15.75" customHeight="1">
       <c r="A622" s="2"/>
@@ -5952,6 +6587,7 @@
       <c r="E622" s="2"/>
       <c r="F622" s="2"/>
       <c r="G622" s="2"/>
+      <c r="H622" s="4"/>
     </row>
     <row r="623" ht="15.75" customHeight="1">
       <c r="A623" s="2"/>
@@ -5961,6 +6597,7 @@
       <c r="E623" s="2"/>
       <c r="F623" s="2"/>
       <c r="G623" s="2"/>
+      <c r="H623" s="4"/>
     </row>
     <row r="624" ht="15.75" customHeight="1">
       <c r="A624" s="2"/>
@@ -5970,6 +6607,7 @@
       <c r="E624" s="2"/>
       <c r="F624" s="2"/>
       <c r="G624" s="2"/>
+      <c r="H624" s="4"/>
     </row>
     <row r="625" ht="15.75" customHeight="1">
       <c r="A625" s="2"/>
@@ -5979,6 +6617,7 @@
       <c r="E625" s="2"/>
       <c r="F625" s="2"/>
       <c r="G625" s="2"/>
+      <c r="H625" s="4"/>
     </row>
     <row r="626" ht="15.75" customHeight="1">
       <c r="A626" s="2"/>
@@ -5988,6 +6627,7 @@
       <c r="E626" s="2"/>
       <c r="F626" s="2"/>
       <c r="G626" s="2"/>
+      <c r="H626" s="4"/>
     </row>
     <row r="627" ht="15.75" customHeight="1">
       <c r="A627" s="2"/>
@@ -5997,6 +6637,7 @@
       <c r="E627" s="2"/>
       <c r="F627" s="2"/>
       <c r="G627" s="2"/>
+      <c r="H627" s="4"/>
     </row>
     <row r="628" ht="15.75" customHeight="1">
       <c r="A628" s="2"/>
@@ -6006,6 +6647,7 @@
       <c r="E628" s="2"/>
       <c r="F628" s="2"/>
       <c r="G628" s="2"/>
+      <c r="H628" s="4"/>
     </row>
     <row r="629" ht="15.75" customHeight="1">
       <c r="A629" s="2"/>
@@ -6015,6 +6657,7 @@
       <c r="E629" s="2"/>
       <c r="F629" s="2"/>
       <c r="G629" s="2"/>
+      <c r="H629" s="4"/>
     </row>
     <row r="630" ht="15.75" customHeight="1">
       <c r="A630" s="2"/>
@@ -6024,6 +6667,7 @@
       <c r="E630" s="2"/>
       <c r="F630" s="2"/>
       <c r="G630" s="2"/>
+      <c r="H630" s="4"/>
     </row>
     <row r="631" ht="15.75" customHeight="1">
       <c r="A631" s="2"/>
@@ -6033,6 +6677,7 @@
       <c r="E631" s="2"/>
       <c r="F631" s="2"/>
       <c r="G631" s="2"/>
+      <c r="H631" s="4"/>
     </row>
     <row r="632" ht="15.75" customHeight="1">
       <c r="A632" s="2"/>
@@ -6042,6 +6687,7 @@
       <c r="E632" s="2"/>
       <c r="F632" s="2"/>
       <c r="G632" s="2"/>
+      <c r="H632" s="4"/>
     </row>
     <row r="633" ht="15.75" customHeight="1">
       <c r="A633" s="2"/>
@@ -6051,6 +6697,7 @@
       <c r="E633" s="2"/>
       <c r="F633" s="2"/>
       <c r="G633" s="2"/>
+      <c r="H633" s="4"/>
     </row>
     <row r="634" ht="15.75" customHeight="1">
       <c r="A634" s="2"/>
@@ -6060,6 +6707,7 @@
       <c r="E634" s="2"/>
       <c r="F634" s="2"/>
       <c r="G634" s="2"/>
+      <c r="H634" s="4"/>
     </row>
     <row r="635" ht="15.75" customHeight="1">
       <c r="A635" s="2"/>
@@ -6069,6 +6717,7 @@
       <c r="E635" s="2"/>
       <c r="F635" s="2"/>
       <c r="G635" s="2"/>
+      <c r="H635" s="4"/>
     </row>
     <row r="636" ht="15.75" customHeight="1">
       <c r="A636" s="2"/>
@@ -6078,6 +6727,7 @@
       <c r="E636" s="2"/>
       <c r="F636" s="2"/>
       <c r="G636" s="2"/>
+      <c r="H636" s="4"/>
     </row>
     <row r="637" ht="15.75" customHeight="1">
       <c r="A637" s="2"/>
@@ -6087,6 +6737,7 @@
       <c r="E637" s="2"/>
       <c r="F637" s="2"/>
       <c r="G637" s="2"/>
+      <c r="H637" s="4"/>
     </row>
     <row r="638" ht="15.75" customHeight="1">
       <c r="A638" s="2"/>
@@ -6096,6 +6747,7 @@
       <c r="E638" s="2"/>
       <c r="F638" s="2"/>
       <c r="G638" s="2"/>
+      <c r="H638" s="4"/>
     </row>
     <row r="639" ht="15.75" customHeight="1">
       <c r="A639" s="2"/>
@@ -6105,6 +6757,7 @@
       <c r="E639" s="2"/>
       <c r="F639" s="2"/>
       <c r="G639" s="2"/>
+      <c r="H639" s="4"/>
     </row>
     <row r="640" ht="15.75" customHeight="1">
       <c r="A640" s="2"/>
@@ -6114,6 +6767,7 @@
       <c r="E640" s="2"/>
       <c r="F640" s="2"/>
       <c r="G640" s="2"/>
+      <c r="H640" s="4"/>
     </row>
     <row r="641" ht="15.75" customHeight="1">
       <c r="A641" s="2"/>
@@ -6123,6 +6777,7 @@
       <c r="E641" s="2"/>
       <c r="F641" s="2"/>
       <c r="G641" s="2"/>
+      <c r="H641" s="4"/>
     </row>
     <row r="642" ht="15.75" customHeight="1">
       <c r="A642" s="2"/>
@@ -6132,6 +6787,7 @@
       <c r="E642" s="2"/>
       <c r="F642" s="2"/>
       <c r="G642" s="2"/>
+      <c r="H642" s="4"/>
     </row>
     <row r="643" ht="15.75" customHeight="1">
       <c r="A643" s="2"/>
@@ -6141,6 +6797,7 @@
       <c r="E643" s="2"/>
       <c r="F643" s="2"/>
       <c r="G643" s="2"/>
+      <c r="H643" s="4"/>
     </row>
     <row r="644" ht="15.75" customHeight="1">
       <c r="A644" s="2"/>
@@ -6150,6 +6807,7 @@
       <c r="E644" s="2"/>
       <c r="F644" s="2"/>
       <c r="G644" s="2"/>
+      <c r="H644" s="4"/>
     </row>
     <row r="645" ht="15.75" customHeight="1">
       <c r="A645" s="2"/>
@@ -6159,6 +6817,7 @@
       <c r="E645" s="2"/>
       <c r="F645" s="2"/>
       <c r="G645" s="2"/>
+      <c r="H645" s="4"/>
     </row>
     <row r="646" ht="15.75" customHeight="1">
       <c r="A646" s="2"/>
@@ -6168,6 +6827,7 @@
       <c r="E646" s="2"/>
       <c r="F646" s="2"/>
       <c r="G646" s="2"/>
+      <c r="H646" s="4"/>
     </row>
     <row r="647" ht="15.75" customHeight="1">
       <c r="A647" s="2"/>
@@ -6177,6 +6837,7 @@
       <c r="E647" s="2"/>
       <c r="F647" s="2"/>
       <c r="G647" s="2"/>
+      <c r="H647" s="4"/>
     </row>
     <row r="648" ht="15.75" customHeight="1">
       <c r="A648" s="2"/>
@@ -6186,6 +6847,7 @@
       <c r="E648" s="2"/>
       <c r="F648" s="2"/>
       <c r="G648" s="2"/>
+      <c r="H648" s="4"/>
     </row>
     <row r="649" ht="15.75" customHeight="1">
       <c r="A649" s="2"/>
@@ -6195,6 +6857,7 @@
       <c r="E649" s="2"/>
       <c r="F649" s="2"/>
       <c r="G649" s="2"/>
+      <c r="H649" s="4"/>
     </row>
     <row r="650" ht="15.75" customHeight="1">
       <c r="A650" s="2"/>
@@ -6204,6 +6867,7 @@
       <c r="E650" s="2"/>
       <c r="F650" s="2"/>
       <c r="G650" s="2"/>
+      <c r="H650" s="4"/>
     </row>
     <row r="651" ht="15.75" customHeight="1">
       <c r="A651" s="2"/>
@@ -6213,6 +6877,7 @@
       <c r="E651" s="2"/>
       <c r="F651" s="2"/>
       <c r="G651" s="2"/>
+      <c r="H651" s="4"/>
     </row>
     <row r="652" ht="15.75" customHeight="1">
       <c r="A652" s="2"/>
@@ -6222,6 +6887,7 @@
       <c r="E652" s="2"/>
       <c r="F652" s="2"/>
       <c r="G652" s="2"/>
+      <c r="H652" s="4"/>
     </row>
     <row r="653" ht="15.75" customHeight="1">
       <c r="A653" s="2"/>
@@ -6231,6 +6897,7 @@
       <c r="E653" s="2"/>
       <c r="F653" s="2"/>
       <c r="G653" s="2"/>
+      <c r="H653" s="4"/>
     </row>
     <row r="654" ht="15.75" customHeight="1">
       <c r="A654" s="2"/>
@@ -6240,6 +6907,7 @@
       <c r="E654" s="2"/>
       <c r="F654" s="2"/>
       <c r="G654" s="2"/>
+      <c r="H654" s="4"/>
     </row>
     <row r="655" ht="15.75" customHeight="1">
       <c r="A655" s="2"/>
@@ -6249,6 +6917,7 @@
       <c r="E655" s="2"/>
       <c r="F655" s="2"/>
       <c r="G655" s="2"/>
+      <c r="H655" s="4"/>
     </row>
     <row r="656" ht="15.75" customHeight="1">
       <c r="A656" s="2"/>
@@ -6258,6 +6927,7 @@
       <c r="E656" s="2"/>
       <c r="F656" s="2"/>
       <c r="G656" s="2"/>
+      <c r="H656" s="4"/>
     </row>
     <row r="657" ht="15.75" customHeight="1">
       <c r="A657" s="2"/>
@@ -6267,6 +6937,7 @@
       <c r="E657" s="2"/>
       <c r="F657" s="2"/>
       <c r="G657" s="2"/>
+      <c r="H657" s="4"/>
     </row>
     <row r="658" ht="15.75" customHeight="1">
       <c r="A658" s="2"/>
@@ -6276,6 +6947,7 @@
       <c r="E658" s="2"/>
       <c r="F658" s="2"/>
       <c r="G658" s="2"/>
+      <c r="H658" s="4"/>
     </row>
     <row r="659" ht="15.75" customHeight="1">
       <c r="A659" s="2"/>
@@ -6285,6 +6957,7 @@
       <c r="E659" s="2"/>
       <c r="F659" s="2"/>
       <c r="G659" s="2"/>
+      <c r="H659" s="4"/>
     </row>
     <row r="660" ht="15.75" customHeight="1">
       <c r="A660" s="2"/>
@@ -6294,6 +6967,7 @@
       <c r="E660" s="2"/>
       <c r="F660" s="2"/>
       <c r="G660" s="2"/>
+      <c r="H660" s="4"/>
     </row>
     <row r="661" ht="15.75" customHeight="1">
       <c r="A661" s="2"/>
@@ -6303,6 +6977,7 @@
       <c r="E661" s="2"/>
       <c r="F661" s="2"/>
       <c r="G661" s="2"/>
+      <c r="H661" s="4"/>
     </row>
     <row r="662" ht="15.75" customHeight="1">
       <c r="A662" s="2"/>
@@ -6312,6 +6987,7 @@
       <c r="E662" s="2"/>
       <c r="F662" s="2"/>
       <c r="G662" s="2"/>
+      <c r="H662" s="4"/>
     </row>
     <row r="663" ht="15.75" customHeight="1">
       <c r="A663" s="2"/>
@@ -6321,6 +6997,7 @@
       <c r="E663" s="2"/>
       <c r="F663" s="2"/>
       <c r="G663" s="2"/>
+      <c r="H663" s="4"/>
     </row>
     <row r="664" ht="15.75" customHeight="1">
       <c r="A664" s="2"/>
@@ -6330,6 +7007,7 @@
       <c r="E664" s="2"/>
       <c r="F664" s="2"/>
       <c r="G664" s="2"/>
+      <c r="H664" s="4"/>
     </row>
     <row r="665" ht="15.75" customHeight="1">
       <c r="A665" s="2"/>
@@ -6339,6 +7017,7 @@
       <c r="E665" s="2"/>
       <c r="F665" s="2"/>
       <c r="G665" s="2"/>
+      <c r="H665" s="4"/>
     </row>
     <row r="666" ht="15.75" customHeight="1">
       <c r="A666" s="2"/>
@@ -6348,6 +7027,7 @@
       <c r="E666" s="2"/>
       <c r="F666" s="2"/>
       <c r="G666" s="2"/>
+      <c r="H666" s="4"/>
     </row>
     <row r="667" ht="15.75" customHeight="1">
       <c r="A667" s="2"/>
@@ -6357,6 +7037,7 @@
       <c r="E667" s="2"/>
       <c r="F667" s="2"/>
       <c r="G667" s="2"/>
+      <c r="H667" s="4"/>
     </row>
     <row r="668" ht="15.75" customHeight="1">
       <c r="A668" s="2"/>
@@ -6366,6 +7047,7 @@
       <c r="E668" s="2"/>
       <c r="F668" s="2"/>
       <c r="G668" s="2"/>
+      <c r="H668" s="4"/>
     </row>
     <row r="669" ht="15.75" customHeight="1">
       <c r="A669" s="2"/>
@@ -6375,6 +7057,7 @@
       <c r="E669" s="2"/>
       <c r="F669" s="2"/>
       <c r="G669" s="2"/>
+      <c r="H669" s="4"/>
     </row>
     <row r="670" ht="15.75" customHeight="1">
       <c r="A670" s="2"/>
@@ -6384,6 +7067,7 @@
       <c r="E670" s="2"/>
       <c r="F670" s="2"/>
       <c r="G670" s="2"/>
+      <c r="H670" s="4"/>
     </row>
     <row r="671" ht="15.75" customHeight="1">
       <c r="A671" s="2"/>
@@ -6393,6 +7077,7 @@
       <c r="E671" s="2"/>
       <c r="F671" s="2"/>
       <c r="G671" s="2"/>
+      <c r="H671" s="4"/>
     </row>
     <row r="672" ht="15.75" customHeight="1">
       <c r="A672" s="2"/>
@@ -6402,6 +7087,7 @@
       <c r="E672" s="2"/>
       <c r="F672" s="2"/>
       <c r="G672" s="2"/>
+      <c r="H672" s="4"/>
     </row>
     <row r="673" ht="15.75" customHeight="1">
       <c r="A673" s="2"/>
@@ -6411,6 +7097,7 @@
       <c r="E673" s="2"/>
       <c r="F673" s="2"/>
       <c r="G673" s="2"/>
+      <c r="H673" s="4"/>
     </row>
     <row r="674" ht="15.75" customHeight="1">
       <c r="A674" s="2"/>
@@ -6420,6 +7107,7 @@
       <c r="E674" s="2"/>
       <c r="F674" s="2"/>
       <c r="G674" s="2"/>
+      <c r="H674" s="4"/>
     </row>
     <row r="675" ht="15.75" customHeight="1">
       <c r="A675" s="2"/>
@@ -6429,6 +7117,7 @@
       <c r="E675" s="2"/>
       <c r="F675" s="2"/>
       <c r="G675" s="2"/>
+      <c r="H675" s="4"/>
     </row>
     <row r="676" ht="15.75" customHeight="1">
       <c r="A676" s="2"/>
@@ -6438,6 +7127,7 @@
       <c r="E676" s="2"/>
       <c r="F676" s="2"/>
       <c r="G676" s="2"/>
+      <c r="H676" s="4"/>
     </row>
     <row r="677" ht="15.75" customHeight="1">
       <c r="A677" s="2"/>
@@ -6447,6 +7137,7 @@
       <c r="E677" s="2"/>
       <c r="F677" s="2"/>
       <c r="G677" s="2"/>
+      <c r="H677" s="4"/>
     </row>
     <row r="678" ht="15.75" customHeight="1">
       <c r="A678" s="2"/>
@@ -6456,6 +7147,7 @@
       <c r="E678" s="2"/>
       <c r="F678" s="2"/>
       <c r="G678" s="2"/>
+      <c r="H678" s="4"/>
     </row>
     <row r="679" ht="15.75" customHeight="1">
       <c r="A679" s="2"/>
@@ -6465,6 +7157,7 @@
       <c r="E679" s="2"/>
       <c r="F679" s="2"/>
       <c r="G679" s="2"/>
+      <c r="H679" s="4"/>
     </row>
     <row r="680" ht="15.75" customHeight="1">
       <c r="A680" s="2"/>
@@ -6474,6 +7167,7 @@
       <c r="E680" s="2"/>
       <c r="F680" s="2"/>
       <c r="G680" s="2"/>
+      <c r="H680" s="4"/>
     </row>
     <row r="681" ht="15.75" customHeight="1">
       <c r="A681" s="2"/>
@@ -6483,6 +7177,7 @@
       <c r="E681" s="2"/>
       <c r="F681" s="2"/>
       <c r="G681" s="2"/>
+      <c r="H681" s="4"/>
     </row>
     <row r="682" ht="15.75" customHeight="1">
       <c r="A682" s="2"/>
@@ -6492,6 +7187,7 @@
       <c r="E682" s="2"/>
       <c r="F682" s="2"/>
       <c r="G682" s="2"/>
+      <c r="H682" s="4"/>
     </row>
     <row r="683" ht="15.75" customHeight="1">
       <c r="A683" s="2"/>
@@ -6501,6 +7197,7 @@
       <c r="E683" s="2"/>
       <c r="F683" s="2"/>
       <c r="G683" s="2"/>
+      <c r="H683" s="4"/>
     </row>
     <row r="684" ht="15.75" customHeight="1">
       <c r="A684" s="2"/>
@@ -6510,6 +7207,7 @@
       <c r="E684" s="2"/>
       <c r="F684" s="2"/>
       <c r="G684" s="2"/>
+      <c r="H684" s="4"/>
     </row>
     <row r="685" ht="15.75" customHeight="1">
       <c r="A685" s="2"/>
@@ -6519,6 +7217,7 @@
       <c r="E685" s="2"/>
       <c r="F685" s="2"/>
       <c r="G685" s="2"/>
+      <c r="H685" s="4"/>
     </row>
     <row r="686" ht="15.75" customHeight="1">
       <c r="A686" s="2"/>
@@ -6528,6 +7227,7 @@
       <c r="E686" s="2"/>
       <c r="F686" s="2"/>
       <c r="G686" s="2"/>
+      <c r="H686" s="4"/>
     </row>
     <row r="687" ht="15.75" customHeight="1">
       <c r="A687" s="2"/>
@@ -6537,6 +7237,7 @@
       <c r="E687" s="2"/>
       <c r="F687" s="2"/>
       <c r="G687" s="2"/>
+      <c r="H687" s="4"/>
     </row>
     <row r="688" ht="15.75" customHeight="1">
       <c r="A688" s="2"/>
@@ -6546,6 +7247,7 @@
       <c r="E688" s="2"/>
       <c r="F688" s="2"/>
       <c r="G688" s="2"/>
+      <c r="H688" s="4"/>
     </row>
     <row r="689" ht="15.75" customHeight="1">
       <c r="A689" s="2"/>
@@ -6555,6 +7257,7 @@
       <c r="E689" s="2"/>
       <c r="F689" s="2"/>
       <c r="G689" s="2"/>
+      <c r="H689" s="4"/>
     </row>
     <row r="690" ht="15.75" customHeight="1">
       <c r="A690" s="2"/>
@@ -6564,6 +7267,7 @@
       <c r="E690" s="2"/>
       <c r="F690" s="2"/>
       <c r="G690" s="2"/>
+      <c r="H690" s="4"/>
     </row>
     <row r="691" ht="15.75" customHeight="1">
       <c r="A691" s="2"/>
@@ -6573,6 +7277,7 @@
       <c r="E691" s="2"/>
       <c r="F691" s="2"/>
       <c r="G691" s="2"/>
+      <c r="H691" s="4"/>
     </row>
     <row r="692" ht="15.75" customHeight="1">
       <c r="A692" s="2"/>
@@ -6582,6 +7287,7 @@
       <c r="E692" s="2"/>
       <c r="F692" s="2"/>
       <c r="G692" s="2"/>
+      <c r="H692" s="4"/>
     </row>
     <row r="693" ht="15.75" customHeight="1">
       <c r="A693" s="2"/>
@@ -6591,6 +7297,7 @@
       <c r="E693" s="2"/>
       <c r="F693" s="2"/>
       <c r="G693" s="2"/>
+      <c r="H693" s="4"/>
     </row>
     <row r="694" ht="15.75" customHeight="1">
       <c r="A694" s="2"/>
@@ -6600,6 +7307,7 @@
       <c r="E694" s="2"/>
       <c r="F694" s="2"/>
       <c r="G694" s="2"/>
+      <c r="H694" s="4"/>
     </row>
     <row r="695" ht="15.75" customHeight="1">
       <c r="A695" s="2"/>
@@ -6609,6 +7317,7 @@
       <c r="E695" s="2"/>
       <c r="F695" s="2"/>
       <c r="G695" s="2"/>
+      <c r="H695" s="4"/>
     </row>
     <row r="696" ht="15.75" customHeight="1">
       <c r="A696" s="2"/>
@@ -6618,6 +7327,7 @@
       <c r="E696" s="2"/>
       <c r="F696" s="2"/>
       <c r="G696" s="2"/>
+      <c r="H696" s="4"/>
     </row>
     <row r="697" ht="15.75" customHeight="1">
       <c r="A697" s="2"/>
@@ -6627,6 +7337,7 @@
       <c r="E697" s="2"/>
       <c r="F697" s="2"/>
       <c r="G697" s="2"/>
+      <c r="H697" s="4"/>
     </row>
     <row r="698" ht="15.75" customHeight="1">
       <c r="A698" s="2"/>
@@ -6636,6 +7347,7 @@
       <c r="E698" s="2"/>
       <c r="F698" s="2"/>
       <c r="G698" s="2"/>
+      <c r="H698" s="4"/>
     </row>
     <row r="699" ht="15.75" customHeight="1">
       <c r="A699" s="2"/>
@@ -6645,6 +7357,7 @@
       <c r="E699" s="2"/>
       <c r="F699" s="2"/>
       <c r="G699" s="2"/>
+      <c r="H699" s="4"/>
     </row>
     <row r="700" ht="15.75" customHeight="1">
       <c r="A700" s="2"/>
@@ -6654,6 +7367,7 @@
       <c r="E700" s="2"/>
       <c r="F700" s="2"/>
       <c r="G700" s="2"/>
+      <c r="H700" s="4"/>
     </row>
     <row r="701" ht="15.75" customHeight="1">
       <c r="A701" s="2"/>
@@ -6663,6 +7377,7 @@
       <c r="E701" s="2"/>
       <c r="F701" s="2"/>
       <c r="G701" s="2"/>
+      <c r="H701" s="4"/>
     </row>
     <row r="702" ht="15.75" customHeight="1">
       <c r="A702" s="2"/>
@@ -6672,6 +7387,7 @@
       <c r="E702" s="2"/>
       <c r="F702" s="2"/>
       <c r="G702" s="2"/>
+      <c r="H702" s="4"/>
     </row>
     <row r="703" ht="15.75" customHeight="1">
       <c r="A703" s="2"/>
@@ -6681,6 +7397,7 @@
       <c r="E703" s="2"/>
       <c r="F703" s="2"/>
       <c r="G703" s="2"/>
+      <c r="H703" s="4"/>
     </row>
     <row r="704" ht="15.75" customHeight="1">
       <c r="A704" s="2"/>
@@ -6690,6 +7407,7 @@
       <c r="E704" s="2"/>
       <c r="F704" s="2"/>
       <c r="G704" s="2"/>
+      <c r="H704" s="4"/>
     </row>
     <row r="705" ht="15.75" customHeight="1">
       <c r="A705" s="2"/>
@@ -6699,6 +7417,7 @@
       <c r="E705" s="2"/>
       <c r="F705" s="2"/>
       <c r="G705" s="2"/>
+      <c r="H705" s="4"/>
     </row>
     <row r="706" ht="15.75" customHeight="1">
       <c r="A706" s="2"/>
@@ -6708,6 +7427,7 @@
       <c r="E706" s="2"/>
       <c r="F706" s="2"/>
       <c r="G706" s="2"/>
+      <c r="H706" s="4"/>
     </row>
     <row r="707" ht="15.75" customHeight="1">
       <c r="A707" s="2"/>
@@ -6717,6 +7437,7 @@
       <c r="E707" s="2"/>
       <c r="F707" s="2"/>
       <c r="G707" s="2"/>
+      <c r="H707" s="4"/>
     </row>
     <row r="708" ht="15.75" customHeight="1">
       <c r="A708" s="2"/>
@@ -6726,6 +7447,7 @@
       <c r="E708" s="2"/>
       <c r="F708" s="2"/>
       <c r="G708" s="2"/>
+      <c r="H708" s="4"/>
     </row>
     <row r="709" ht="15.75" customHeight="1">
       <c r="A709" s="2"/>
@@ -6735,6 +7457,7 @@
       <c r="E709" s="2"/>
       <c r="F709" s="2"/>
       <c r="G709" s="2"/>
+      <c r="H709" s="4"/>
     </row>
     <row r="710" ht="15.75" customHeight="1">
       <c r="A710" s="2"/>
@@ -6744,6 +7467,7 @@
       <c r="E710" s="2"/>
       <c r="F710" s="2"/>
       <c r="G710" s="2"/>
+      <c r="H710" s="4"/>
     </row>
     <row r="711" ht="15.75" customHeight="1">
       <c r="A711" s="2"/>
@@ -6753,6 +7477,7 @@
       <c r="E711" s="2"/>
       <c r="F711" s="2"/>
       <c r="G711" s="2"/>
+      <c r="H711" s="4"/>
     </row>
     <row r="712" ht="15.75" customHeight="1">
       <c r="A712" s="2"/>
@@ -6762,6 +7487,7 @@
       <c r="E712" s="2"/>
       <c r="F712" s="2"/>
       <c r="G712" s="2"/>
+      <c r="H712" s="4"/>
     </row>
     <row r="713" ht="15.75" customHeight="1">
       <c r="A713" s="2"/>
@@ -6771,6 +7497,7 @@
       <c r="E713" s="2"/>
       <c r="F713" s="2"/>
       <c r="G713" s="2"/>
+      <c r="H713" s="4"/>
     </row>
     <row r="714" ht="15.75" customHeight="1">
       <c r="A714" s="2"/>
@@ -6780,6 +7507,7 @@
       <c r="E714" s="2"/>
       <c r="F714" s="2"/>
       <c r="G714" s="2"/>
+      <c r="H714" s="4"/>
     </row>
     <row r="715" ht="15.75" customHeight="1">
       <c r="A715" s="2"/>
@@ -6789,6 +7517,7 @@
       <c r="E715" s="2"/>
       <c r="F715" s="2"/>
       <c r="G715" s="2"/>
+      <c r="H715" s="4"/>
     </row>
     <row r="716" ht="15.75" customHeight="1">
       <c r="A716" s="2"/>
@@ -6798,6 +7527,7 @@
       <c r="E716" s="2"/>
       <c r="F716" s="2"/>
       <c r="G716" s="2"/>
+      <c r="H716" s="4"/>
     </row>
     <row r="717" ht="15.75" customHeight="1">
       <c r="A717" s="2"/>
@@ -6807,6 +7537,7 @@
       <c r="E717" s="2"/>
       <c r="F717" s="2"/>
       <c r="G717" s="2"/>
+      <c r="H717" s="4"/>
     </row>
     <row r="718" ht="15.75" customHeight="1">
       <c r="A718" s="2"/>
@@ -6816,6 +7547,7 @@
       <c r="E718" s="2"/>
       <c r="F718" s="2"/>
       <c r="G718" s="2"/>
+      <c r="H718" s="4"/>
     </row>
     <row r="719" ht="15.75" customHeight="1">
       <c r="A719" s="2"/>
@@ -6825,6 +7557,7 @@
       <c r="E719" s="2"/>
       <c r="F719" s="2"/>
       <c r="G719" s="2"/>
+      <c r="H719" s="4"/>
     </row>
     <row r="720" ht="15.75" customHeight="1">
       <c r="A720" s="2"/>
@@ -6834,6 +7567,7 @@
       <c r="E720" s="2"/>
       <c r="F720" s="2"/>
       <c r="G720" s="2"/>
+      <c r="H720" s="4"/>
     </row>
     <row r="721" ht="15.75" customHeight="1">
       <c r="A721" s="2"/>
@@ -6843,6 +7577,7 @@
       <c r="E721" s="2"/>
       <c r="F721" s="2"/>
       <c r="G721" s="2"/>
+      <c r="H721" s="4"/>
     </row>
     <row r="722" ht="15.75" customHeight="1">
       <c r="A722" s="2"/>
@@ -6852,6 +7587,7 @@
       <c r="E722" s="2"/>
       <c r="F722" s="2"/>
       <c r="G722" s="2"/>
+      <c r="H722" s="4"/>
     </row>
     <row r="723" ht="15.75" customHeight="1">
       <c r="A723" s="2"/>
@@ -6861,6 +7597,7 @@
       <c r="E723" s="2"/>
       <c r="F723" s="2"/>
       <c r="G723" s="2"/>
+      <c r="H723" s="4"/>
     </row>
     <row r="724" ht="15.75" customHeight="1">
       <c r="A724" s="2"/>
@@ -6870,6 +7607,7 @@
       <c r="E724" s="2"/>
       <c r="F724" s="2"/>
       <c r="G724" s="2"/>
+      <c r="H724" s="4"/>
     </row>
     <row r="725" ht="15.75" customHeight="1">
       <c r="A725" s="2"/>
@@ -6879,6 +7617,7 @@
       <c r="E725" s="2"/>
       <c r="F725" s="2"/>
       <c r="G725" s="2"/>
+      <c r="H725" s="4"/>
     </row>
     <row r="726" ht="15.75" customHeight="1">
       <c r="A726" s="2"/>
@@ -6888,6 +7627,7 @@
       <c r="E726" s="2"/>
       <c r="F726" s="2"/>
       <c r="G726" s="2"/>
+      <c r="H726" s="4"/>
     </row>
     <row r="727" ht="15.75" customHeight="1">
       <c r="A727" s="2"/>
@@ -6897,6 +7637,7 @@
       <c r="E727" s="2"/>
       <c r="F727" s="2"/>
       <c r="G727" s="2"/>
+      <c r="H727" s="4"/>
     </row>
     <row r="728" ht="15.75" customHeight="1">
       <c r="A728" s="2"/>
@@ -6906,6 +7647,7 @@
       <c r="E728" s="2"/>
       <c r="F728" s="2"/>
       <c r="G728" s="2"/>
+      <c r="H728" s="4"/>
     </row>
     <row r="729" ht="15.75" customHeight="1">
       <c r="A729" s="2"/>
@@ -6915,6 +7657,7 @@
       <c r="E729" s="2"/>
       <c r="F729" s="2"/>
       <c r="G729" s="2"/>
+      <c r="H729" s="4"/>
     </row>
     <row r="730" ht="15.75" customHeight="1">
       <c r="A730" s="2"/>
@@ -6924,6 +7667,7 @@
       <c r="E730" s="2"/>
       <c r="F730" s="2"/>
       <c r="G730" s="2"/>
+      <c r="H730" s="4"/>
     </row>
     <row r="731" ht="15.75" customHeight="1">
       <c r="A731" s="2"/>
@@ -6933,6 +7677,7 @@
       <c r="E731" s="2"/>
       <c r="F731" s="2"/>
       <c r="G731" s="2"/>
+      <c r="H731" s="4"/>
     </row>
     <row r="732" ht="15.75" customHeight="1">
       <c r="A732" s="2"/>
@@ -6942,6 +7687,7 @@
       <c r="E732" s="2"/>
       <c r="F732" s="2"/>
       <c r="G732" s="2"/>
+      <c r="H732" s="4"/>
     </row>
     <row r="733" ht="15.75" customHeight="1">
       <c r="A733" s="2"/>
@@ -6951,6 +7697,7 @@
       <c r="E733" s="2"/>
       <c r="F733" s="2"/>
       <c r="G733" s="2"/>
+      <c r="H733" s="4"/>
     </row>
     <row r="734" ht="15.75" customHeight="1">
       <c r="A734" s="2"/>
@@ -6960,6 +7707,7 @@
       <c r="E734" s="2"/>
       <c r="F734" s="2"/>
       <c r="G734" s="2"/>
+      <c r="H734" s="4"/>
     </row>
     <row r="735" ht="15.75" customHeight="1">
       <c r="A735" s="2"/>
@@ -6969,6 +7717,7 @@
       <c r="E735" s="2"/>
       <c r="F735" s="2"/>
       <c r="G735" s="2"/>
+      <c r="H735" s="4"/>
     </row>
     <row r="736" ht="15.75" customHeight="1">
       <c r="A736" s="2"/>
@@ -6978,6 +7727,7 @@
       <c r="E736" s="2"/>
       <c r="F736" s="2"/>
       <c r="G736" s="2"/>
+      <c r="H736" s="4"/>
     </row>
     <row r="737" ht="15.75" customHeight="1">
       <c r="A737" s="2"/>
@@ -6987,6 +7737,7 @@
       <c r="E737" s="2"/>
       <c r="F737" s="2"/>
       <c r="G737" s="2"/>
+      <c r="H737" s="4"/>
     </row>
     <row r="738" ht="15.75" customHeight="1">
       <c r="A738" s="2"/>
@@ -6996,6 +7747,7 @@
       <c r="E738" s="2"/>
       <c r="F738" s="2"/>
       <c r="G738" s="2"/>
+      <c r="H738" s="4"/>
     </row>
     <row r="739" ht="15.75" customHeight="1">
       <c r="A739" s="2"/>
@@ -7005,6 +7757,7 @@
       <c r="E739" s="2"/>
       <c r="F739" s="2"/>
       <c r="G739" s="2"/>
+      <c r="H739" s="4"/>
     </row>
     <row r="740" ht="15.75" customHeight="1">
       <c r="A740" s="2"/>
@@ -7014,6 +7767,7 @@
       <c r="E740" s="2"/>
       <c r="F740" s="2"/>
       <c r="G740" s="2"/>
+      <c r="H740" s="4"/>
     </row>
     <row r="741" ht="15.75" customHeight="1">
       <c r="A741" s="2"/>
@@ -7023,6 +7777,7 @@
       <c r="E741" s="2"/>
       <c r="F741" s="2"/>
       <c r="G741" s="2"/>
+      <c r="H741" s="4"/>
     </row>
     <row r="742" ht="15.75" customHeight="1">
       <c r="A742" s="2"/>
@@ -7032,6 +7787,7 @@
       <c r="E742" s="2"/>
       <c r="F742" s="2"/>
       <c r="G742" s="2"/>
+      <c r="H742" s="4"/>
     </row>
     <row r="743" ht="15.75" customHeight="1">
       <c r="A743" s="2"/>
@@ -7041,6 +7797,7 @@
       <c r="E743" s="2"/>
       <c r="F743" s="2"/>
       <c r="G743" s="2"/>
+      <c r="H743" s="4"/>
     </row>
     <row r="744" ht="15.75" customHeight="1">
       <c r="A744" s="2"/>
@@ -7050,6 +7807,7 @@
       <c r="E744" s="2"/>
       <c r="F744" s="2"/>
       <c r="G744" s="2"/>
+      <c r="H744" s="4"/>
     </row>
     <row r="745" ht="15.75" customHeight="1">
       <c r="A745" s="2"/>
@@ -7059,6 +7817,7 @@
       <c r="E745" s="2"/>
       <c r="F745" s="2"/>
       <c r="G745" s="2"/>
+      <c r="H745" s="4"/>
     </row>
     <row r="746" ht="15.75" customHeight="1">
       <c r="A746" s="2"/>
@@ -7068,6 +7827,7 @@
       <c r="E746" s="2"/>
       <c r="F746" s="2"/>
       <c r="G746" s="2"/>
+      <c r="H746" s="4"/>
     </row>
     <row r="747" ht="15.75" customHeight="1">
       <c r="A747" s="2"/>
@@ -7077,6 +7837,7 @@
       <c r="E747" s="2"/>
       <c r="F747" s="2"/>
       <c r="G747" s="2"/>
+      <c r="H747" s="4"/>
     </row>
     <row r="748" ht="15.75" customHeight="1">
       <c r="A748" s="2"/>
@@ -7086,6 +7847,7 @@
       <c r="E748" s="2"/>
       <c r="F748" s="2"/>
       <c r="G748" s="2"/>
+      <c r="H748" s="4"/>
     </row>
     <row r="749" ht="15.75" customHeight="1">
       <c r="A749" s="2"/>
@@ -7095,6 +7857,7 @@
       <c r="E749" s="2"/>
       <c r="F749" s="2"/>
       <c r="G749" s="2"/>
+      <c r="H749" s="4"/>
     </row>
     <row r="750" ht="15.75" customHeight="1">
       <c r="A750" s="2"/>
@@ -7104,6 +7867,7 @@
       <c r="E750" s="2"/>
       <c r="F750" s="2"/>
       <c r="G750" s="2"/>
+      <c r="H750" s="4"/>
     </row>
     <row r="751" ht="15.75" customHeight="1">
       <c r="A751" s="2"/>
@@ -7113,6 +7877,7 @@
       <c r="E751" s="2"/>
       <c r="F751" s="2"/>
       <c r="G751" s="2"/>
+      <c r="H751" s="4"/>
     </row>
     <row r="752" ht="15.75" customHeight="1">
       <c r="A752" s="2"/>
@@ -7122,6 +7887,7 @@
       <c r="E752" s="2"/>
       <c r="F752" s="2"/>
       <c r="G752" s="2"/>
+      <c r="H752" s="4"/>
     </row>
     <row r="753" ht="15.75" customHeight="1">
       <c r="A753" s="2"/>
@@ -7131,6 +7897,7 @@
       <c r="E753" s="2"/>
       <c r="F753" s="2"/>
       <c r="G753" s="2"/>
+      <c r="H753" s="4"/>
     </row>
     <row r="754" ht="15.75" customHeight="1">
       <c r="A754" s="2"/>
@@ -7140,6 +7907,7 @@
       <c r="E754" s="2"/>
       <c r="F754" s="2"/>
       <c r="G754" s="2"/>
+      <c r="H754" s="4"/>
     </row>
     <row r="755" ht="15.75" customHeight="1">
       <c r="A755" s="2"/>
@@ -7149,6 +7917,7 @@
       <c r="E755" s="2"/>
       <c r="F755" s="2"/>
       <c r="G755" s="2"/>
+      <c r="H755" s="4"/>
     </row>
     <row r="756" ht="15.75" customHeight="1">
       <c r="A756" s="2"/>
@@ -7158,6 +7927,7 @@
       <c r="E756" s="2"/>
       <c r="F756" s="2"/>
       <c r="G756" s="2"/>
+      <c r="H756" s="4"/>
     </row>
     <row r="757" ht="15.75" customHeight="1">
       <c r="A757" s="2"/>
@@ -7167,6 +7937,7 @@
       <c r="E757" s="2"/>
       <c r="F757" s="2"/>
       <c r="G757" s="2"/>
+      <c r="H757" s="4"/>
     </row>
     <row r="758" ht="15.75" customHeight="1">
       <c r="A758" s="2"/>
@@ -7176,6 +7947,7 @@
       <c r="E758" s="2"/>
       <c r="F758" s="2"/>
       <c r="G758" s="2"/>
+      <c r="H758" s="4"/>
     </row>
     <row r="759" ht="15.75" customHeight="1">
       <c r="A759" s="2"/>
@@ -7185,6 +7957,7 @@
       <c r="E759" s="2"/>
       <c r="F759" s="2"/>
       <c r="G759" s="2"/>
+      <c r="H759" s="4"/>
     </row>
     <row r="760" ht="15.75" customHeight="1">
       <c r="A760" s="2"/>
@@ -7194,6 +7967,7 @@
       <c r="E760" s="2"/>
       <c r="F760" s="2"/>
       <c r="G760" s="2"/>
+      <c r="H760" s="4"/>
     </row>
     <row r="761" ht="15.75" customHeight="1">
       <c r="A761" s="2"/>
@@ -7203,6 +7977,7 @@
       <c r="E761" s="2"/>
       <c r="F761" s="2"/>
       <c r="G761" s="2"/>
+      <c r="H761" s="4"/>
     </row>
     <row r="762" ht="15.75" customHeight="1">
       <c r="A762" s="2"/>
@@ -7212,6 +7987,7 @@
       <c r="E762" s="2"/>
       <c r="F762" s="2"/>
       <c r="G762" s="2"/>
+      <c r="H762" s="4"/>
     </row>
     <row r="763" ht="15.75" customHeight="1">
       <c r="A763" s="2"/>
@@ -7221,6 +7997,7 @@
       <c r="E763" s="2"/>
       <c r="F763" s="2"/>
       <c r="G763" s="2"/>
+      <c r="H763" s="4"/>
     </row>
     <row r="764" ht="15.75" customHeight="1">
       <c r="A764" s="2"/>
@@ -7230,6 +8007,7 @@
       <c r="E764" s="2"/>
       <c r="F764" s="2"/>
       <c r="G764" s="2"/>
+      <c r="H764" s="4"/>
     </row>
     <row r="765" ht="15.75" customHeight="1">
       <c r="A765" s="2"/>
@@ -7239,6 +8017,7 @@
       <c r="E765" s="2"/>
       <c r="F765" s="2"/>
       <c r="G765" s="2"/>
+      <c r="H765" s="4"/>
     </row>
     <row r="766" ht="15.75" customHeight="1">
       <c r="A766" s="2"/>
@@ -7248,6 +8027,7 @@
       <c r="E766" s="2"/>
       <c r="F766" s="2"/>
       <c r="G766" s="2"/>
+      <c r="H766" s="4"/>
     </row>
     <row r="767" ht="15.75" customHeight="1">
       <c r="A767" s="2"/>
@@ -7257,6 +8037,7 @@
       <c r="E767" s="2"/>
       <c r="F767" s="2"/>
       <c r="G767" s="2"/>
+      <c r="H767" s="4"/>
     </row>
     <row r="768" ht="15.75" customHeight="1">
       <c r="A768" s="2"/>
@@ -7266,6 +8047,7 @@
       <c r="E768" s="2"/>
       <c r="F768" s="2"/>
       <c r="G768" s="2"/>
+      <c r="H768" s="4"/>
     </row>
     <row r="769" ht="15.75" customHeight="1">
       <c r="A769" s="2"/>
@@ -7275,6 +8057,7 @@
       <c r="E769" s="2"/>
       <c r="F769" s="2"/>
       <c r="G769" s="2"/>
+      <c r="H769" s="4"/>
     </row>
     <row r="770" ht="15.75" customHeight="1">
       <c r="A770" s="2"/>
@@ -7284,6 +8067,7 @@
       <c r="E770" s="2"/>
       <c r="F770" s="2"/>
       <c r="G770" s="2"/>
+      <c r="H770" s="4"/>
     </row>
     <row r="771" ht="15.75" customHeight="1">
       <c r="A771" s="2"/>
@@ -7293,6 +8077,7 @@
       <c r="E771" s="2"/>
       <c r="F771" s="2"/>
       <c r="G771" s="2"/>
+      <c r="H771" s="4"/>
     </row>
     <row r="772" ht="15.75" customHeight="1">
       <c r="A772" s="2"/>
@@ -7302,6 +8087,7 @@
       <c r="E772" s="2"/>
       <c r="F772" s="2"/>
       <c r="G772" s="2"/>
+      <c r="H772" s="4"/>
     </row>
     <row r="773" ht="15.75" customHeight="1">
       <c r="A773" s="2"/>
@@ -7311,6 +8097,7 @@
       <c r="E773" s="2"/>
       <c r="F773" s="2"/>
       <c r="G773" s="2"/>
+      <c r="H773" s="4"/>
     </row>
     <row r="774" ht="15.75" customHeight="1">
       <c r="A774" s="2"/>
@@ -7320,6 +8107,7 @@
       <c r="E774" s="2"/>
       <c r="F774" s="2"/>
       <c r="G774" s="2"/>
+      <c r="H774" s="4"/>
     </row>
     <row r="775" ht="15.75" customHeight="1">
       <c r="A775" s="2"/>
@@ -7329,6 +8117,7 @@
       <c r="E775" s="2"/>
       <c r="F775" s="2"/>
       <c r="G775" s="2"/>
+      <c r="H775" s="4"/>
     </row>
     <row r="776" ht="15.75" customHeight="1">
       <c r="A776" s="2"/>
@@ -7338,6 +8127,7 @@
       <c r="E776" s="2"/>
       <c r="F776" s="2"/>
       <c r="G776" s="2"/>
+      <c r="H776" s="4"/>
     </row>
     <row r="777" ht="15.75" customHeight="1">
       <c r="A777" s="2"/>
@@ -7347,6 +8137,7 @@
       <c r="E777" s="2"/>
       <c r="F777" s="2"/>
       <c r="G777" s="2"/>
+      <c r="H777" s="4"/>
     </row>
     <row r="778" ht="15.75" customHeight="1">
       <c r="A778" s="2"/>
@@ -7356,6 +8147,7 @@
       <c r="E778" s="2"/>
       <c r="F778" s="2"/>
       <c r="G778" s="2"/>
+      <c r="H778" s="4"/>
     </row>
     <row r="779" ht="15.75" customHeight="1">
       <c r="A779" s="2"/>
@@ -7365,6 +8157,7 @@
       <c r="E779" s="2"/>
       <c r="F779" s="2"/>
       <c r="G779" s="2"/>
+      <c r="H779" s="4"/>
     </row>
     <row r="780" ht="15.75" customHeight="1">
       <c r="A780" s="2"/>
@@ -7374,6 +8167,7 @@
       <c r="E780" s="2"/>
       <c r="F780" s="2"/>
       <c r="G780" s="2"/>
+      <c r="H780" s="4"/>
     </row>
     <row r="781" ht="15.75" customHeight="1">
       <c r="A781" s="2"/>
@@ -7383,6 +8177,7 @@
       <c r="E781" s="2"/>
       <c r="F781" s="2"/>
       <c r="G781" s="2"/>
+      <c r="H781" s="4"/>
     </row>
     <row r="782" ht="15.75" customHeight="1">
       <c r="A782" s="2"/>
@@ -7392,6 +8187,7 @@
       <c r="E782" s="2"/>
       <c r="F782" s="2"/>
       <c r="G782" s="2"/>
+      <c r="H782" s="4"/>
     </row>
     <row r="783" ht="15.75" customHeight="1">
       <c r="A783" s="2"/>
@@ -7401,6 +8197,7 @@
       <c r="E783" s="2"/>
       <c r="F783" s="2"/>
       <c r="G783" s="2"/>
+      <c r="H783" s="4"/>
     </row>
     <row r="784" ht="15.75" customHeight="1">
       <c r="A784" s="2"/>
@@ -7410,6 +8207,7 @@
       <c r="E784" s="2"/>
       <c r="F784" s="2"/>
       <c r="G784" s="2"/>
+      <c r="H784" s="4"/>
     </row>
     <row r="785" ht="15.75" customHeight="1">
       <c r="A785" s="2"/>
@@ -7419,6 +8217,7 @@
       <c r="E785" s="2"/>
       <c r="F785" s="2"/>
       <c r="G785" s="2"/>
+      <c r="H785" s="4"/>
     </row>
     <row r="786" ht="15.75" customHeight="1">
       <c r="A786" s="2"/>
@@ -7428,6 +8227,7 @@
       <c r="E786" s="2"/>
       <c r="F786" s="2"/>
       <c r="G786" s="2"/>
+      <c r="H786" s="4"/>
     </row>
     <row r="787" ht="15.75" customHeight="1">
       <c r="A787" s="2"/>
@@ -7437,6 +8237,7 @@
       <c r="E787" s="2"/>
       <c r="F787" s="2"/>
       <c r="G787" s="2"/>
+      <c r="H787" s="4"/>
     </row>
     <row r="788" ht="15.75" customHeight="1">
       <c r="A788" s="2"/>
@@ -7446,6 +8247,7 @@
       <c r="E788" s="2"/>
       <c r="F788" s="2"/>
       <c r="G788" s="2"/>
+      <c r="H788" s="4"/>
     </row>
     <row r="789" ht="15.75" customHeight="1">
       <c r="A789" s="2"/>
@@ -7455,6 +8257,7 @@
       <c r="E789" s="2"/>
       <c r="F789" s="2"/>
       <c r="G789" s="2"/>
+      <c r="H789" s="4"/>
     </row>
     <row r="790" ht="15.75" customHeight="1">
       <c r="A790" s="2"/>
@@ -7464,6 +8267,7 @@
       <c r="E790" s="2"/>
       <c r="F790" s="2"/>
       <c r="G790" s="2"/>
+      <c r="H790" s="4"/>
     </row>
     <row r="791" ht="15.75" customHeight="1">
       <c r="A791" s="2"/>
@@ -7473,6 +8277,7 @@
       <c r="E791" s="2"/>
       <c r="F791" s="2"/>
       <c r="G791" s="2"/>
+      <c r="H791" s="4"/>
     </row>
     <row r="792" ht="15.75" customHeight="1">
       <c r="A792" s="2"/>
@@ -7482,6 +8287,7 @@
       <c r="E792" s="2"/>
       <c r="F792" s="2"/>
       <c r="G792" s="2"/>
+      <c r="H792" s="4"/>
     </row>
     <row r="793" ht="15.75" customHeight="1">
       <c r="A793" s="2"/>
@@ -7491,6 +8297,7 @@
       <c r="E793" s="2"/>
       <c r="F793" s="2"/>
       <c r="G793" s="2"/>
+      <c r="H793" s="4"/>
     </row>
     <row r="794" ht="15.75" customHeight="1">
       <c r="A794" s="2"/>
@@ -7500,6 +8307,7 @@
       <c r="E794" s="2"/>
       <c r="F794" s="2"/>
       <c r="G794" s="2"/>
+      <c r="H794" s="4"/>
     </row>
     <row r="795" ht="15.75" customHeight="1">
       <c r="A795" s="2"/>
@@ -7509,6 +8317,7 @@
       <c r="E795" s="2"/>
       <c r="F795" s="2"/>
       <c r="G795" s="2"/>
+      <c r="H795" s="4"/>
     </row>
     <row r="796" ht="15.75" customHeight="1">
       <c r="A796" s="2"/>
@@ -7518,6 +8327,7 @@
       <c r="E796" s="2"/>
       <c r="F796" s="2"/>
       <c r="G796" s="2"/>
+      <c r="H796" s="4"/>
     </row>
     <row r="797" ht="15.75" customHeight="1">
       <c r="A797" s="2"/>
@@ -7527,6 +8337,7 @@
       <c r="E797" s="2"/>
       <c r="F797" s="2"/>
       <c r="G797" s="2"/>
+      <c r="H797" s="4"/>
     </row>
     <row r="798" ht="15.75" customHeight="1">
       <c r="A798" s="2"/>
@@ -7536,6 +8347,7 @@
       <c r="E798" s="2"/>
       <c r="F798" s="2"/>
       <c r="G798" s="2"/>
+      <c r="H798" s="4"/>
     </row>
     <row r="799" ht="15.75" customHeight="1">
       <c r="A799" s="2"/>
@@ -7545,6 +8357,7 @@
       <c r="E799" s="2"/>
       <c r="F799" s="2"/>
       <c r="G799" s="2"/>
+      <c r="H799" s="4"/>
     </row>
     <row r="800" ht="15.75" customHeight="1">
       <c r="A800" s="2"/>
@@ -7554,6 +8367,7 @@
       <c r="E800" s="2"/>
       <c r="F800" s="2"/>
       <c r="G800" s="2"/>
+      <c r="H800" s="4"/>
     </row>
     <row r="801" ht="15.75" customHeight="1">
       <c r="A801" s="2"/>
@@ -7563,6 +8377,7 @@
       <c r="E801" s="2"/>
       <c r="F801" s="2"/>
       <c r="G801" s="2"/>
+      <c r="H801" s="4"/>
     </row>
     <row r="802" ht="15.75" customHeight="1">
       <c r="A802" s="2"/>
@@ -7572,6 +8387,7 @@
       <c r="E802" s="2"/>
       <c r="F802" s="2"/>
       <c r="G802" s="2"/>
+      <c r="H802" s="4"/>
     </row>
     <row r="803" ht="15.75" customHeight="1">
       <c r="A803" s="2"/>
@@ -7581,6 +8397,7 @@
       <c r="E803" s="2"/>
       <c r="F803" s="2"/>
       <c r="G803" s="2"/>
+      <c r="H803" s="4"/>
     </row>
     <row r="804" ht="15.75" customHeight="1">
       <c r="A804" s="2"/>
@@ -7590,6 +8407,7 @@
       <c r="E804" s="2"/>
       <c r="F804" s="2"/>
       <c r="G804" s="2"/>
+      <c r="H804" s="4"/>
     </row>
     <row r="805" ht="15.75" customHeight="1">
       <c r="A805" s="2"/>
@@ -7599,6 +8417,7 @@
       <c r="E805" s="2"/>
       <c r="F805" s="2"/>
       <c r="G805" s="2"/>
+      <c r="H805" s="4"/>
     </row>
     <row r="806" ht="15.75" customHeight="1">
       <c r="A806" s="2"/>
@@ -7608,6 +8427,7 @@
       <c r="E806" s="2"/>
       <c r="F806" s="2"/>
       <c r="G806" s="2"/>
+      <c r="H806" s="4"/>
     </row>
     <row r="807" ht="15.75" customHeight="1">
       <c r="A807" s="2"/>
@@ -7617,6 +8437,7 @@
       <c r="E807" s="2"/>
       <c r="F807" s="2"/>
       <c r="G807" s="2"/>
+      <c r="H807" s="4"/>
     </row>
     <row r="808" ht="15.75" customHeight="1">
       <c r="A808" s="2"/>
@@ -7626,6 +8447,7 @@
       <c r="E808" s="2"/>
       <c r="F808" s="2"/>
       <c r="G808" s="2"/>
+      <c r="H808" s="4"/>
     </row>
     <row r="809" ht="15.75" customHeight="1">
       <c r="A809" s="2"/>
@@ -7635,6 +8457,7 @@
       <c r="E809" s="2"/>
       <c r="F809" s="2"/>
       <c r="G809" s="2"/>
+      <c r="H809" s="4"/>
     </row>
     <row r="810" ht="15.75" customHeight="1">
       <c r="A810" s="2"/>
@@ -7644,6 +8467,7 @@
       <c r="E810" s="2"/>
       <c r="F810" s="2"/>
       <c r="G810" s="2"/>
+      <c r="H810" s="4"/>
     </row>
     <row r="811" ht="15.75" customHeight="1">
       <c r="A811" s="2"/>
@@ -7653,6 +8477,7 @@
       <c r="E811" s="2"/>
       <c r="F811" s="2"/>
       <c r="G811" s="2"/>
+      <c r="H811" s="4"/>
     </row>
     <row r="812" ht="15.75" customHeight="1">
       <c r="A812" s="2"/>
@@ -7662,6 +8487,7 @@
       <c r="E812" s="2"/>
       <c r="F812" s="2"/>
       <c r="G812" s="2"/>
+      <c r="H812" s="4"/>
     </row>
     <row r="813" ht="15.75" customHeight="1">
       <c r="A813" s="2"/>
@@ -7671,6 +8497,7 @@
       <c r="E813" s="2"/>
       <c r="F813" s="2"/>
       <c r="G813" s="2"/>
+      <c r="H813" s="4"/>
     </row>
     <row r="814" ht="15.75" customHeight="1">
       <c r="A814" s="2"/>
@@ -7680,6 +8507,7 @@
       <c r="E814" s="2"/>
       <c r="F814" s="2"/>
       <c r="G814" s="2"/>
+      <c r="H814" s="4"/>
     </row>
     <row r="815" ht="15.75" customHeight="1">
       <c r="A815" s="2"/>
@@ -7689,6 +8517,7 @@
       <c r="E815" s="2"/>
       <c r="F815" s="2"/>
       <c r="G815" s="2"/>
+      <c r="H815" s="4"/>
     </row>
     <row r="816" ht="15.75" customHeight="1">
       <c r="A816" s="2"/>
@@ -7698,6 +8527,7 @@
       <c r="E816" s="2"/>
       <c r="F816" s="2"/>
       <c r="G816" s="2"/>
+      <c r="H816" s="4"/>
     </row>
     <row r="817" ht="15.75" customHeight="1">
       <c r="A817" s="2"/>
@@ -7707,6 +8537,7 @@
       <c r="E817" s="2"/>
       <c r="F817" s="2"/>
       <c r="G817" s="2"/>
+      <c r="H817" s="4"/>
     </row>
     <row r="818" ht="15.75" customHeight="1">
       <c r="A818" s="2"/>
@@ -7716,6 +8547,7 @@
       <c r="E818" s="2"/>
       <c r="F818" s="2"/>
       <c r="G818" s="2"/>
+      <c r="H818" s="4"/>
     </row>
     <row r="819" ht="15.75" customHeight="1">
       <c r="A819" s="2"/>
@@ -7725,6 +8557,7 @@
       <c r="E819" s="2"/>
       <c r="F819" s="2"/>
       <c r="G819" s="2"/>
+      <c r="H819" s="4"/>
     </row>
     <row r="820" ht="15.75" customHeight="1">
       <c r="A820" s="2"/>
@@ -7734,6 +8567,7 @@
       <c r="E820" s="2"/>
       <c r="F820" s="2"/>
       <c r="G820" s="2"/>
+      <c r="H820" s="4"/>
     </row>
     <row r="821" ht="15.75" customHeight="1">
       <c r="A821" s="2"/>
@@ -7743,6 +8577,7 @@
       <c r="E821" s="2"/>
       <c r="F821" s="2"/>
       <c r="G821" s="2"/>
+      <c r="H821" s="4"/>
     </row>
     <row r="822" ht="15.75" customHeight="1">
       <c r="A822" s="2"/>
@@ -7752,6 +8587,7 @@
       <c r="E822" s="2"/>
       <c r="F822" s="2"/>
       <c r="G822" s="2"/>
+      <c r="H822" s="4"/>
     </row>
     <row r="823" ht="15.75" customHeight="1">
       <c r="A823" s="2"/>
@@ -7761,6 +8597,7 @@
       <c r="E823" s="2"/>
       <c r="F823" s="2"/>
       <c r="G823" s="2"/>
+      <c r="H823" s="4"/>
     </row>
     <row r="824" ht="15.75" customHeight="1">
       <c r="A824" s="2"/>
@@ -7770,6 +8607,7 @@
       <c r="E824" s="2"/>
       <c r="F824" s="2"/>
       <c r="G824" s="2"/>
+      <c r="H824" s="4"/>
     </row>
     <row r="825" ht="15.75" customHeight="1">
       <c r="A825" s="2"/>
@@ -7779,6 +8617,7 @@
       <c r="E825" s="2"/>
       <c r="F825" s="2"/>
       <c r="G825" s="2"/>
+      <c r="H825" s="4"/>
     </row>
     <row r="826" ht="15.75" customHeight="1">
       <c r="A826" s="2"/>
@@ -7788,6 +8627,7 @@
       <c r="E826" s="2"/>
       <c r="F826" s="2"/>
       <c r="G826" s="2"/>
+      <c r="H826" s="4"/>
     </row>
     <row r="827" ht="15.75" customHeight="1">
       <c r="A827" s="2"/>
@@ -7797,6 +8637,7 @@
       <c r="E827" s="2"/>
       <c r="F827" s="2"/>
       <c r="G827" s="2"/>
+      <c r="H827" s="4"/>
     </row>
     <row r="828" ht="15.75" customHeight="1">
       <c r="A828" s="2"/>
@@ -7806,6 +8647,7 @@
       <c r="E828" s="2"/>
       <c r="F828" s="2"/>
       <c r="G828" s="2"/>
+      <c r="H828" s="4"/>
     </row>
     <row r="829" ht="15.75" customHeight="1">
       <c r="A829" s="2"/>
@@ -7815,6 +8657,7 @@
       <c r="E829" s="2"/>
       <c r="F829" s="2"/>
       <c r="G829" s="2"/>
+      <c r="H829" s="4"/>
     </row>
     <row r="830" ht="15.75" customHeight="1">
       <c r="A830" s="2"/>
@@ -7824,6 +8667,7 @@
       <c r="E830" s="2"/>
       <c r="F830" s="2"/>
       <c r="G830" s="2"/>
+      <c r="H830" s="4"/>
     </row>
     <row r="831" ht="15.75" customHeight="1">
       <c r="A831" s="2"/>
@@ -7833,6 +8677,7 @@
       <c r="E831" s="2"/>
       <c r="F831" s="2"/>
       <c r="G831" s="2"/>
+      <c r="H831" s="4"/>
     </row>
     <row r="832" ht="15.75" customHeight="1">
       <c r="A832" s="2"/>
@@ -7842,6 +8687,7 @@
       <c r="E832" s="2"/>
       <c r="F832" s="2"/>
       <c r="G832" s="2"/>
+      <c r="H832" s="4"/>
     </row>
     <row r="833" ht="15.75" customHeight="1">
       <c r="A833" s="2"/>
@@ -7851,6 +8697,7 @@
       <c r="E833" s="2"/>
       <c r="F833" s="2"/>
       <c r="G833" s="2"/>
+      <c r="H833" s="4"/>
     </row>
     <row r="834" ht="15.75" customHeight="1">
       <c r="A834" s="2"/>
@@ -7860,6 +8707,7 @@
       <c r="E834" s="2"/>
       <c r="F834" s="2"/>
       <c r="G834" s="2"/>
+      <c r="H834" s="4"/>
     </row>
     <row r="835" ht="15.75" customHeight="1">
       <c r="A835" s="2"/>
@@ -7869,6 +8717,7 @@
       <c r="E835" s="2"/>
       <c r="F835" s="2"/>
       <c r="G835" s="2"/>
+      <c r="H835" s="4"/>
     </row>
     <row r="836" ht="15.75" customHeight="1">
       <c r="A836" s="2"/>
@@ -7878,6 +8727,7 @@
       <c r="E836" s="2"/>
       <c r="F836" s="2"/>
       <c r="G836" s="2"/>
+      <c r="H836" s="4"/>
     </row>
     <row r="837" ht="15.75" customHeight="1">
       <c r="A837" s="2"/>
@@ -7887,6 +8737,7 @@
       <c r="E837" s="2"/>
       <c r="F837" s="2"/>
       <c r="G837" s="2"/>
+      <c r="H837" s="4"/>
     </row>
     <row r="838" ht="15.75" customHeight="1">
       <c r="A838" s="2"/>
@@ -7896,6 +8747,7 @@
       <c r="E838" s="2"/>
       <c r="F838" s="2"/>
       <c r="G838" s="2"/>
+      <c r="H838" s="4"/>
     </row>
     <row r="839" ht="15.75" customHeight="1">
       <c r="A839" s="2"/>
@@ -7905,6 +8757,7 @@
       <c r="E839" s="2"/>
       <c r="F839" s="2"/>
       <c r="G839" s="2"/>
+      <c r="H839" s="4"/>
     </row>
     <row r="840" ht="15.75" customHeight="1">
       <c r="A840" s="2"/>
@@ -7914,6 +8767,7 @@
       <c r="E840" s="2"/>
       <c r="F840" s="2"/>
       <c r="G840" s="2"/>
+      <c r="H840" s="4"/>
     </row>
     <row r="841" ht="15.75" customHeight="1">
       <c r="A841" s="2"/>
@@ -7923,6 +8777,7 @@
       <c r="E841" s="2"/>
       <c r="F841" s="2"/>
       <c r="G841" s="2"/>
+      <c r="H841" s="4"/>
     </row>
     <row r="842" ht="15.75" customHeight="1">
       <c r="A842" s="2"/>
@@ -7932,6 +8787,7 @@
       <c r="E842" s="2"/>
       <c r="F842" s="2"/>
       <c r="G842" s="2"/>
+      <c r="H842" s="4"/>
     </row>
     <row r="843" ht="15.75" customHeight="1">
       <c r="A843" s="2"/>
@@ -7941,6 +8797,7 @@
       <c r="E843" s="2"/>
       <c r="F843" s="2"/>
       <c r="G843" s="2"/>
+      <c r="H843" s="4"/>
     </row>
     <row r="844" ht="15.75" customHeight="1">
       <c r="A844" s="2"/>
@@ -7950,6 +8807,7 @@
       <c r="E844" s="2"/>
       <c r="F844" s="2"/>
       <c r="G844" s="2"/>
+      <c r="H844" s="4"/>
     </row>
     <row r="845" ht="15.75" customHeight="1">
       <c r="A845" s="2"/>
@@ -7959,6 +8817,7 @@
       <c r="E845" s="2"/>
       <c r="F845" s="2"/>
       <c r="G845" s="2"/>
+      <c r="H845" s="4"/>
     </row>
     <row r="846" ht="15.75" customHeight="1">
       <c r="A846" s="2"/>
@@ -7968,6 +8827,7 @@
       <c r="E846" s="2"/>
       <c r="F846" s="2"/>
       <c r="G846" s="2"/>
+      <c r="H846" s="4"/>
     </row>
     <row r="847" ht="15.75" customHeight="1">
       <c r="A847" s="2"/>
@@ -7977,6 +8837,7 @@
       <c r="E847" s="2"/>
       <c r="F847" s="2"/>
       <c r="G847" s="2"/>
+      <c r="H847" s="4"/>
     </row>
     <row r="848" ht="15.75" customHeight="1">
       <c r="A848" s="2"/>
@@ -7986,6 +8847,7 @@
       <c r="E848" s="2"/>
       <c r="F848" s="2"/>
       <c r="G848" s="2"/>
+      <c r="H848" s="4"/>
     </row>
     <row r="849" ht="15.75" customHeight="1">
       <c r="A849" s="2"/>
@@ -7995,6 +8857,7 @@
       <c r="E849" s="2"/>
       <c r="F849" s="2"/>
       <c r="G849" s="2"/>
+      <c r="H849" s="4"/>
     </row>
     <row r="850" ht="15.75" customHeight="1">
       <c r="A850" s="2"/>
@@ -8004,6 +8867,7 @@
       <c r="E850" s="2"/>
       <c r="F850" s="2"/>
       <c r="G850" s="2"/>
+      <c r="H850" s="4"/>
     </row>
     <row r="851" ht="15.75" customHeight="1">
       <c r="A851" s="2"/>
@@ -8013,6 +8877,7 @@
       <c r="E851" s="2"/>
       <c r="F851" s="2"/>
       <c r="G851" s="2"/>
+      <c r="H851" s="4"/>
     </row>
     <row r="852" ht="15.75" customHeight="1">
       <c r="A852" s="2"/>
@@ -8022,6 +8887,7 @@
       <c r="E852" s="2"/>
       <c r="F852" s="2"/>
       <c r="G852" s="2"/>
+      <c r="H852" s="4"/>
     </row>
     <row r="853" ht="15.75" customHeight="1">
       <c r="A853" s="2"/>
@@ -8031,6 +8897,7 @@
       <c r="E853" s="2"/>
       <c r="F853" s="2"/>
       <c r="G853" s="2"/>
+      <c r="H853" s="4"/>
     </row>
     <row r="854" ht="15.75" customHeight="1">
       <c r="A854" s="2"/>
@@ -8040,6 +8907,7 @@
       <c r="E854" s="2"/>
       <c r="F854" s="2"/>
       <c r="G854" s="2"/>
+      <c r="H854" s="4"/>
     </row>
     <row r="855" ht="15.75" customHeight="1">
       <c r="A855" s="2"/>
@@ -8049,6 +8917,7 @@
       <c r="E855" s="2"/>
       <c r="F855" s="2"/>
       <c r="G855" s="2"/>
+      <c r="H855" s="4"/>
     </row>
     <row r="856" ht="15.75" customHeight="1">
       <c r="A856" s="2"/>
@@ -8058,6 +8927,7 @@
       <c r="E856" s="2"/>
       <c r="F856" s="2"/>
       <c r="G856" s="2"/>
+      <c r="H856" s="4"/>
     </row>
     <row r="857" ht="15.75" customHeight="1">
       <c r="A857" s="2"/>
@@ -8067,6 +8937,7 @@
       <c r="E857" s="2"/>
       <c r="F857" s="2"/>
       <c r="G857" s="2"/>
+      <c r="H857" s="4"/>
     </row>
     <row r="858" ht="15.75" customHeight="1">
       <c r="A858" s="2"/>
@@ -8076,6 +8947,7 @@
       <c r="E858" s="2"/>
       <c r="F858" s="2"/>
       <c r="G858" s="2"/>
+      <c r="H858" s="4"/>
     </row>
     <row r="859" ht="15.75" customHeight="1">
       <c r="A859" s="2"/>
@@ -8085,6 +8957,7 @@
       <c r="E859" s="2"/>
       <c r="F859" s="2"/>
       <c r="G859" s="2"/>
+      <c r="H859" s="4"/>
     </row>
     <row r="860" ht="15.75" customHeight="1">
       <c r="A860" s="2"/>
@@ -8094,6 +8967,7 @@
       <c r="E860" s="2"/>
       <c r="F860" s="2"/>
       <c r="G860" s="2"/>
+      <c r="H860" s="4"/>
     </row>
     <row r="861" ht="15.75" customHeight="1">
       <c r="A861" s="2"/>
@@ -8103,6 +8977,7 @@
       <c r="E861" s="2"/>
       <c r="F861" s="2"/>
       <c r="G861" s="2"/>
+      <c r="H861" s="4"/>
     </row>
     <row r="862" ht="15.75" customHeight="1">
       <c r="A862" s="2"/>
@@ -8112,6 +8987,7 @@
       <c r="E862" s="2"/>
       <c r="F862" s="2"/>
       <c r="G862" s="2"/>
+      <c r="H862" s="4"/>
     </row>
     <row r="863" ht="15.75" customHeight="1">
       <c r="A863" s="2"/>
@@ -8121,6 +8997,7 @@
       <c r="E863" s="2"/>
       <c r="F863" s="2"/>
       <c r="G863" s="2"/>
+      <c r="H863" s="4"/>
     </row>
     <row r="864" ht="15.75" customHeight="1">
       <c r="A864" s="2"/>
@@ -8130,6 +9007,7 @@
       <c r="E864" s="2"/>
       <c r="F864" s="2"/>
       <c r="G864" s="2"/>
+      <c r="H864" s="4"/>
     </row>
     <row r="865" ht="15.75" customHeight="1">
       <c r="A865" s="2"/>
@@ -8139,6 +9017,7 @@
       <c r="E865" s="2"/>
       <c r="F865" s="2"/>
       <c r="G865" s="2"/>
+      <c r="H865" s="4"/>
     </row>
     <row r="866" ht="15.75" customHeight="1">
       <c r="A866" s="2"/>
@@ -8148,6 +9027,7 @@
       <c r="E866" s="2"/>
       <c r="F866" s="2"/>
       <c r="G866" s="2"/>
+      <c r="H866" s="4"/>
     </row>
     <row r="867" ht="15.75" customHeight="1">
       <c r="A867" s="2"/>
@@ -8157,6 +9037,7 @@
       <c r="E867" s="2"/>
       <c r="F867" s="2"/>
       <c r="G867" s="2"/>
+      <c r="H867" s="4"/>
     </row>
     <row r="868" ht="15.75" customHeight="1">
       <c r="A868" s="2"/>
@@ -8166,6 +9047,7 @@
       <c r="E868" s="2"/>
       <c r="F868" s="2"/>
       <c r="G868" s="2"/>
+      <c r="H868" s="4"/>
     </row>
     <row r="869" ht="15.75" customHeight="1">
       <c r="A869" s="2"/>
@@ -8175,6 +9057,7 @@
       <c r="E869" s="2"/>
       <c r="F869" s="2"/>
       <c r="G869" s="2"/>
+      <c r="H869" s="4"/>
     </row>
     <row r="870" ht="15.75" customHeight="1">
       <c r="A870" s="2"/>
@@ -8184,6 +9067,7 @@
       <c r="E870" s="2"/>
       <c r="F870" s="2"/>
       <c r="G870" s="2"/>
+      <c r="H870" s="4"/>
     </row>
     <row r="871" ht="15.75" customHeight="1">
       <c r="A871" s="2"/>
@@ -8193,6 +9077,7 @@
       <c r="E871" s="2"/>
       <c r="F871" s="2"/>
       <c r="G871" s="2"/>
+      <c r="H871" s="4"/>
     </row>
     <row r="872" ht="15.75" customHeight="1">
       <c r="A872" s="2"/>
@@ -8202,6 +9087,7 @@
       <c r="E872" s="2"/>
       <c r="F872" s="2"/>
       <c r="G872" s="2"/>
+      <c r="H872" s="4"/>
     </row>
     <row r="873" ht="15.75" customHeight="1">
       <c r="A873" s="2"/>
@@ -8211,6 +9097,7 @@
       <c r="E873" s="2"/>
       <c r="F873" s="2"/>
       <c r="G873" s="2"/>
+      <c r="H873" s="4"/>
     </row>
     <row r="874" ht="15.75" customHeight="1">
       <c r="A874" s="2"/>
@@ -8220,6 +9107,7 @@
       <c r="E874" s="2"/>
       <c r="F874" s="2"/>
       <c r="G874" s="2"/>
+      <c r="H874" s="4"/>
     </row>
     <row r="875" ht="15.75" customHeight="1">
       <c r="A875" s="2"/>
@@ -8229,6 +9117,7 @@
       <c r="E875" s="2"/>
       <c r="F875" s="2"/>
       <c r="G875" s="2"/>
+      <c r="H875" s="4"/>
     </row>
     <row r="876" ht="15.75" customHeight="1">
       <c r="A876" s="2"/>
@@ -8238,6 +9127,7 @@
       <c r="E876" s="2"/>
       <c r="F876" s="2"/>
       <c r="G876" s="2"/>
+      <c r="H876" s="4"/>
     </row>
     <row r="877" ht="15.75" customHeight="1">
       <c r="A877" s="2"/>
@@ -8247,6 +9137,7 @@
       <c r="E877" s="2"/>
       <c r="F877" s="2"/>
       <c r="G877" s="2"/>
+      <c r="H877" s="4"/>
     </row>
     <row r="878" ht="15.75" customHeight="1">
       <c r="A878" s="2"/>
@@ -8256,6 +9147,7 @@
       <c r="E878" s="2"/>
       <c r="F878" s="2"/>
       <c r="G878" s="2"/>
+      <c r="H878" s="4"/>
     </row>
     <row r="879" ht="15.75" customHeight="1">
       <c r="A879" s="2"/>
@@ -8265,6 +9157,7 @@
       <c r="E879" s="2"/>
       <c r="F879" s="2"/>
       <c r="G879" s="2"/>
+      <c r="H879" s="4"/>
     </row>
     <row r="880" ht="15.75" customHeight="1">
       <c r="A880" s="2"/>
@@ -8274,6 +9167,7 @@
       <c r="E880" s="2"/>
       <c r="F880" s="2"/>
       <c r="G880" s="2"/>
+      <c r="H880" s="4"/>
     </row>
     <row r="881" ht="15.75" customHeight="1">
       <c r="A881" s="2"/>
@@ -8283,6 +9177,7 @@
       <c r="E881" s="2"/>
       <c r="F881" s="2"/>
       <c r="G881" s="2"/>
+      <c r="H881" s="4"/>
     </row>
     <row r="882" ht="15.75" customHeight="1">
       <c r="A882" s="2"/>
@@ -8292,6 +9187,7 @@
       <c r="E882" s="2"/>
       <c r="F882" s="2"/>
       <c r="G882" s="2"/>
+      <c r="H882" s="4"/>
     </row>
     <row r="883" ht="15.75" customHeight="1">
       <c r="A883" s="2"/>
@@ -8301,6 +9197,7 @@
       <c r="E883" s="2"/>
       <c r="F883" s="2"/>
       <c r="G883" s="2"/>
+      <c r="H883" s="4"/>
     </row>
     <row r="884" ht="15.75" customHeight="1">
       <c r="A884" s="2"/>
@@ -8310,6 +9207,7 @@
       <c r="E884" s="2"/>
       <c r="F884" s="2"/>
       <c r="G884" s="2"/>
+      <c r="H884" s="4"/>
     </row>
     <row r="885" ht="15.75" customHeight="1">
       <c r="A885" s="2"/>
@@ -8319,6 +9217,7 @@
       <c r="E885" s="2"/>
       <c r="F885" s="2"/>
       <c r="G885" s="2"/>
+      <c r="H885" s="4"/>
     </row>
     <row r="886" ht="15.75" customHeight="1">
       <c r="A886" s="2"/>
@@ -8328,6 +9227,7 @@
       <c r="E886" s="2"/>
       <c r="F886" s="2"/>
       <c r="G886" s="2"/>
+      <c r="H886" s="4"/>
     </row>
     <row r="887" ht="15.75" customHeight="1">
       <c r="A887" s="2"/>
@@ -8337,6 +9237,7 @@
       <c r="E887" s="2"/>
       <c r="F887" s="2"/>
       <c r="G887" s="2"/>
+      <c r="H887" s="4"/>
     </row>
     <row r="888" ht="15.75" customHeight="1">
       <c r="A888" s="2"/>
@@ -8346,6 +9247,7 @@
       <c r="E888" s="2"/>
       <c r="F888" s="2"/>
       <c r="G888" s="2"/>
+      <c r="H888" s="4"/>
     </row>
     <row r="889" ht="15.75" customHeight="1">
       <c r="A889" s="2"/>
@@ -8355,6 +9257,7 @@
       <c r="E889" s="2"/>
       <c r="F889" s="2"/>
       <c r="G889" s="2"/>
+      <c r="H889" s="4"/>
     </row>
     <row r="890" ht="15.75" customHeight="1">
       <c r="A890" s="2"/>
@@ -8364,6 +9267,7 @@
       <c r="E890" s="2"/>
       <c r="F890" s="2"/>
       <c r="G890" s="2"/>
+      <c r="H890" s="4"/>
     </row>
     <row r="891" ht="15.75" customHeight="1">
       <c r="A891" s="2"/>
@@ -8373,6 +9277,7 @@
       <c r="E891" s="2"/>
       <c r="F891" s="2"/>
       <c r="G891" s="2"/>
+      <c r="H891" s="4"/>
     </row>
     <row r="892" ht="15.75" customHeight="1">
       <c r="A892" s="2"/>
@@ -8382,6 +9287,7 @@
       <c r="E892" s="2"/>
       <c r="F892" s="2"/>
       <c r="G892" s="2"/>
+      <c r="H892" s="4"/>
     </row>
     <row r="893" ht="15.75" customHeight="1">
       <c r="A893" s="2"/>
@@ -8391,6 +9297,7 @@
       <c r="E893" s="2"/>
       <c r="F893" s="2"/>
       <c r="G893" s="2"/>
+      <c r="H893" s="4"/>
     </row>
     <row r="894" ht="15.75" customHeight="1">
       <c r="A894" s="2"/>
@@ -8400,6 +9307,7 @@
       <c r="E894" s="2"/>
       <c r="F894" s="2"/>
       <c r="G894" s="2"/>
+      <c r="H894" s="4"/>
     </row>
     <row r="895" ht="15.75" customHeight="1">
       <c r="A895" s="2"/>
@@ -8409,6 +9317,7 @@
       <c r="E895" s="2"/>
       <c r="F895" s="2"/>
       <c r="G895" s="2"/>
+      <c r="H895" s="4"/>
     </row>
     <row r="896" ht="15.75" customHeight="1">
       <c r="A896" s="2"/>
@@ -8418,6 +9327,7 @@
       <c r="E896" s="2"/>
       <c r="F896" s="2"/>
       <c r="G896" s="2"/>
+      <c r="H896" s="4"/>
     </row>
     <row r="897" ht="15.75" customHeight="1">
       <c r="A897" s="2"/>
@@ -8427,6 +9337,7 @@
       <c r="E897" s="2"/>
       <c r="F897" s="2"/>
       <c r="G897" s="2"/>
+      <c r="H897" s="4"/>
     </row>
     <row r="898" ht="15.75" customHeight="1">
       <c r="A898" s="2"/>
@@ -8436,6 +9347,7 @@
       <c r="E898" s="2"/>
       <c r="F898" s="2"/>
       <c r="G898" s="2"/>
+      <c r="H898" s="4"/>
     </row>
     <row r="899" ht="15.75" customHeight="1">
       <c r="A899" s="2"/>
@@ -8445,6 +9357,7 @@
       <c r="E899" s="2"/>
       <c r="F899" s="2"/>
       <c r="G899" s="2"/>
+      <c r="H899" s="4"/>
     </row>
     <row r="900" ht="15.75" customHeight="1">
       <c r="A900" s="2"/>
@@ -8454,6 +9367,7 @@
       <c r="E900" s="2"/>
       <c r="F900" s="2"/>
       <c r="G900" s="2"/>
+      <c r="H900" s="4"/>
     </row>
     <row r="901" ht="15.75" customHeight="1">
       <c r="A901" s="2"/>
@@ -8463,6 +9377,7 @@
       <c r="E901" s="2"/>
       <c r="F901" s="2"/>
       <c r="G901" s="2"/>
+      <c r="H901" s="4"/>
     </row>
     <row r="902" ht="15.75" customHeight="1">
       <c r="A902" s="2"/>
@@ -8472,6 +9387,7 @@
       <c r="E902" s="2"/>
       <c r="F902" s="2"/>
       <c r="G902" s="2"/>
+      <c r="H902" s="4"/>
     </row>
     <row r="903" ht="15.75" customHeight="1">
       <c r="A903" s="2"/>
@@ -8481,6 +9397,7 @@
       <c r="E903" s="2"/>
       <c r="F903" s="2"/>
       <c r="G903" s="2"/>
+      <c r="H903" s="4"/>
     </row>
     <row r="904" ht="15.75" customHeight="1">
       <c r="A904" s="2"/>
@@ -8490,6 +9407,7 @@
       <c r="E904" s="2"/>
       <c r="F904" s="2"/>
       <c r="G904" s="2"/>
+      <c r="H904" s="4"/>
     </row>
     <row r="905" ht="15.75" customHeight="1">
       <c r="A905" s="2"/>
@@ -8499,6 +9417,7 @@
       <c r="E905" s="2"/>
       <c r="F905" s="2"/>
       <c r="G905" s="2"/>
+      <c r="H905" s="4"/>
     </row>
     <row r="906" ht="15.75" customHeight="1">
       <c r="A906" s="2"/>
@@ -8508,6 +9427,7 @@
       <c r="E906" s="2"/>
       <c r="F906" s="2"/>
       <c r="G906" s="2"/>
+      <c r="H906" s="4"/>
     </row>
     <row r="907" ht="15.75" customHeight="1">
       <c r="A907" s="2"/>
@@ -8517,6 +9437,7 @@
       <c r="E907" s="2"/>
       <c r="F907" s="2"/>
       <c r="G907" s="2"/>
+      <c r="H907" s="4"/>
     </row>
     <row r="908" ht="15.75" customHeight="1">
       <c r="A908" s="2"/>
@@ -8526,6 +9447,7 @@
       <c r="E908" s="2"/>
       <c r="F908" s="2"/>
       <c r="G908" s="2"/>
+      <c r="H908" s="4"/>
     </row>
     <row r="909" ht="15.75" customHeight="1">
       <c r="A909" s="2"/>
@@ -8535,6 +9457,7 @@
       <c r="E909" s="2"/>
       <c r="F909" s="2"/>
       <c r="G909" s="2"/>
+      <c r="H909" s="4"/>
     </row>
     <row r="910" ht="15.75" customHeight="1">
       <c r="A910" s="2"/>
@@ -8544,6 +9467,7 @@
       <c r="E910" s="2"/>
       <c r="F910" s="2"/>
       <c r="G910" s="2"/>
+      <c r="H910" s="4"/>
     </row>
     <row r="911" ht="15.75" customHeight="1">
       <c r="A911" s="2"/>
@@ -8553,6 +9477,7 @@
       <c r="E911" s="2"/>
       <c r="F911" s="2"/>
       <c r="G911" s="2"/>
+      <c r="H911" s="4"/>
     </row>
     <row r="912" ht="15.75" customHeight="1">
       <c r="A912" s="2"/>
@@ -8562,6 +9487,7 @@
       <c r="E912" s="2"/>
       <c r="F912" s="2"/>
       <c r="G912" s="2"/>
+      <c r="H912" s="4"/>
     </row>
     <row r="913" ht="15.75" customHeight="1">
       <c r="A913" s="2"/>
@@ -8571,6 +9497,7 @@
       <c r="E913" s="2"/>
       <c r="F913" s="2"/>
       <c r="G913" s="2"/>
+      <c r="H913" s="4"/>
     </row>
     <row r="914" ht="15.75" customHeight="1">
       <c r="A914" s="2"/>
@@ -8580,6 +9507,7 @@
       <c r="E914" s="2"/>
       <c r="F914" s="2"/>
       <c r="G914" s="2"/>
+      <c r="H914" s="4"/>
     </row>
     <row r="915" ht="15.75" customHeight="1">
       <c r="A915" s="2"/>
@@ -8589,6 +9517,7 @@
       <c r="E915" s="2"/>
       <c r="F915" s="2"/>
       <c r="G915" s="2"/>
+      <c r="H915" s="4"/>
     </row>
     <row r="916" ht="15.75" customHeight="1">
       <c r="A916" s="2"/>
@@ -8598,6 +9527,7 @@
       <c r="E916" s="2"/>
       <c r="F916" s="2"/>
       <c r="G916" s="2"/>
+      <c r="H916" s="4"/>
     </row>
     <row r="917" ht="15.75" customHeight="1">
       <c r="A917" s="2"/>
@@ -8607,6 +9537,7 @@
       <c r="E917" s="2"/>
       <c r="F917" s="2"/>
       <c r="G917" s="2"/>
+      <c r="H917" s="4"/>
     </row>
     <row r="918" ht="15.75" customHeight="1">
       <c r="A918" s="2"/>
@@ -8616,6 +9547,7 @@
       <c r="E918" s="2"/>
       <c r="F918" s="2"/>
       <c r="G918" s="2"/>
+      <c r="H918" s="4"/>
     </row>
     <row r="919" ht="15.75" customHeight="1">
       <c r="A919" s="2"/>
@@ -8625,6 +9557,7 @@
       <c r="E919" s="2"/>
       <c r="F919" s="2"/>
       <c r="G919" s="2"/>
+      <c r="H919" s="4"/>
     </row>
     <row r="920" ht="15.75" customHeight="1">
       <c r="A920" s="2"/>
@@ -8634,6 +9567,7 @@
       <c r="E920" s="2"/>
       <c r="F920" s="2"/>
       <c r="G920" s="2"/>
+      <c r="H920" s="4"/>
     </row>
     <row r="921" ht="15.75" customHeight="1">
       <c r="A921" s="2"/>
@@ -8643,6 +9577,7 @@
       <c r="E921" s="2"/>
       <c r="F921" s="2"/>
       <c r="G921" s="2"/>
+      <c r="H921" s="4"/>
     </row>
     <row r="922" ht="15.75" customHeight="1">
       <c r="A922" s="2"/>
@@ -8652,6 +9587,7 @@
       <c r="E922" s="2"/>
       <c r="F922" s="2"/>
       <c r="G922" s="2"/>
+      <c r="H922" s="4"/>
     </row>
     <row r="923" ht="15.75" customHeight="1">
       <c r="A923" s="2"/>
@@ -8661,6 +9597,7 @@
       <c r="E923" s="2"/>
       <c r="F923" s="2"/>
       <c r="G923" s="2"/>
+      <c r="H923" s="4"/>
     </row>
     <row r="924" ht="15.75" customHeight="1">
       <c r="A924" s="2"/>
@@ -8670,6 +9607,7 @@
       <c r="E924" s="2"/>
       <c r="F924" s="2"/>
       <c r="G924" s="2"/>
+      <c r="H924" s="4"/>
     </row>
     <row r="925" ht="15.75" customHeight="1">
       <c r="A925" s="2"/>
@@ -8679,6 +9617,7 @@
       <c r="E925" s="2"/>
       <c r="F925" s="2"/>
       <c r="G925" s="2"/>
+      <c r="H925" s="4"/>
     </row>
     <row r="926" ht="15.75" customHeight="1">
       <c r="A926" s="2"/>
@@ -8688,6 +9627,7 @@
       <c r="E926" s="2"/>
       <c r="F926" s="2"/>
       <c r="G926" s="2"/>
+      <c r="H926" s="4"/>
     </row>
     <row r="927" ht="15.75" customHeight="1">
       <c r="A927" s="2"/>
@@ -8697,6 +9637,7 @@
       <c r="E927" s="2"/>
       <c r="F927" s="2"/>
       <c r="G927" s="2"/>
+      <c r="H927" s="4"/>
     </row>
     <row r="928" ht="15.75" customHeight="1">
       <c r="A928" s="2"/>
@@ -8706,6 +9647,7 @@
       <c r="E928" s="2"/>
       <c r="F928" s="2"/>
       <c r="G928" s="2"/>
+      <c r="H928" s="4"/>
     </row>
     <row r="929" ht="15.75" customHeight="1">
       <c r="A929" s="2"/>
@@ -8715,6 +9657,7 @@
       <c r="E929" s="2"/>
       <c r="F929" s="2"/>
       <c r="G929" s="2"/>
+      <c r="H929" s="4"/>
     </row>
     <row r="930" ht="15.75" customHeight="1">
       <c r="A930" s="2"/>
@@ -8724,6 +9667,7 @@
       <c r="E930" s="2"/>
       <c r="F930" s="2"/>
       <c r="G930" s="2"/>
+      <c r="H930" s="4"/>
     </row>
     <row r="931" ht="15.75" customHeight="1">
       <c r="A931" s="2"/>
@@ -8733,6 +9677,7 @@
       <c r="E931" s="2"/>
       <c r="F931" s="2"/>
       <c r="G931" s="2"/>
+      <c r="H931" s="4"/>
     </row>
     <row r="932" ht="15.75" customHeight="1">
       <c r="A932" s="2"/>
@@ -8742,6 +9687,7 @@
       <c r="E932" s="2"/>
       <c r="F932" s="2"/>
       <c r="G932" s="2"/>
+      <c r="H932" s="4"/>
     </row>
     <row r="933" ht="15.75" customHeight="1">
       <c r="A933" s="2"/>
@@ -8751,6 +9697,7 @@
       <c r="E933" s="2"/>
       <c r="F933" s="2"/>
       <c r="G933" s="2"/>
+      <c r="H933" s="4"/>
     </row>
     <row r="934" ht="15.75" customHeight="1">
       <c r="A934" s="2"/>
@@ -8760,6 +9707,7 @@
       <c r="E934" s="2"/>
       <c r="F934" s="2"/>
       <c r="G934" s="2"/>
+      <c r="H934" s="4"/>
     </row>
     <row r="935" ht="15.75" customHeight="1">
       <c r="A935" s="2"/>
@@ -8769,6 +9717,7 @@
       <c r="E935" s="2"/>
       <c r="F935" s="2"/>
       <c r="G935" s="2"/>
+      <c r="H935" s="4"/>
     </row>
     <row r="936" ht="15.75" customHeight="1">
       <c r="A936" s="2"/>
@@ -8778,6 +9727,7 @@
       <c r="E936" s="2"/>
       <c r="F936" s="2"/>
       <c r="G936" s="2"/>
+      <c r="H936" s="4"/>
     </row>
     <row r="937" ht="15.75" customHeight="1">
       <c r="A937" s="2"/>
@@ -8787,6 +9737,7 @@
       <c r="E937" s="2"/>
       <c r="F937" s="2"/>
       <c r="G937" s="2"/>
+      <c r="H937" s="4"/>
     </row>
     <row r="938" ht="15.75" customHeight="1">
       <c r="A938" s="2"/>
@@ -8796,6 +9747,7 @@
       <c r="E938" s="2"/>
       <c r="F938" s="2"/>
       <c r="G938" s="2"/>
+      <c r="H938" s="4"/>
     </row>
     <row r="939" ht="15.75" customHeight="1">
       <c r="A939" s="2"/>
@@ -8805,6 +9757,7 @@
       <c r="E939" s="2"/>
       <c r="F939" s="2"/>
       <c r="G939" s="2"/>
+      <c r="H939" s="4"/>
     </row>
     <row r="940" ht="15.75" customHeight="1">
       <c r="A940" s="2"/>
@@ -8814,6 +9767,7 @@
       <c r="E940" s="2"/>
       <c r="F940" s="2"/>
       <c r="G940" s="2"/>
+      <c r="H940" s="4"/>
     </row>
     <row r="941" ht="15.75" customHeight="1">
       <c r="A941" s="2"/>
@@ -8823,6 +9777,7 @@
       <c r="E941" s="2"/>
       <c r="F941" s="2"/>
       <c r="G941" s="2"/>
+      <c r="H941" s="4"/>
     </row>
     <row r="942" ht="15.75" customHeight="1">
       <c r="A942" s="2"/>
@@ -8832,6 +9787,7 @@
       <c r="E942" s="2"/>
       <c r="F942" s="2"/>
       <c r="G942" s="2"/>
+      <c r="H942" s="4"/>
     </row>
     <row r="943" ht="15.75" customHeight="1">
       <c r="A943" s="2"/>
@@ -8841,6 +9797,7 @@
       <c r="E943" s="2"/>
       <c r="F943" s="2"/>
       <c r="G943" s="2"/>
+      <c r="H943" s="4"/>
     </row>
     <row r="944" ht="15.75" customHeight="1">
       <c r="A944" s="2"/>
@@ -8850,6 +9807,7 @@
       <c r="E944" s="2"/>
       <c r="F944" s="2"/>
       <c r="G944" s="2"/>
+      <c r="H944" s="4"/>
     </row>
     <row r="945" ht="15.75" customHeight="1">
       <c r="A945" s="2"/>
@@ -8859,6 +9817,7 @@
       <c r="E945" s="2"/>
       <c r="F945" s="2"/>
       <c r="G945" s="2"/>
+      <c r="H945" s="4"/>
     </row>
     <row r="946" ht="15.75" customHeight="1">
       <c r="A946" s="2"/>
@@ -8868,6 +9827,7 @@
       <c r="E946" s="2"/>
       <c r="F946" s="2"/>
       <c r="G946" s="2"/>
+      <c r="H946" s="4"/>
     </row>
     <row r="947" ht="15.75" customHeight="1">
       <c r="A947" s="2"/>
@@ -8877,6 +9837,7 @@
       <c r="E947" s="2"/>
       <c r="F947" s="2"/>
       <c r="G947" s="2"/>
+      <c r="H947" s="4"/>
     </row>
     <row r="948" ht="15.75" customHeight="1">
       <c r="A948" s="2"/>
@@ -8886,6 +9847,7 @@
       <c r="E948" s="2"/>
       <c r="F948" s="2"/>
       <c r="G948" s="2"/>
+      <c r="H948" s="4"/>
     </row>
     <row r="949" ht="15.75" customHeight="1">
       <c r="A949" s="2"/>
@@ -8895,6 +9857,7 @@
       <c r="E949" s="2"/>
       <c r="F949" s="2"/>
       <c r="G949" s="2"/>
+      <c r="H949" s="4"/>
     </row>
     <row r="950" ht="15.75" customHeight="1">
       <c r="A950" s="2"/>
@@ -8904,6 +9867,7 @@
       <c r="E950" s="2"/>
       <c r="F950" s="2"/>
       <c r="G950" s="2"/>
+      <c r="H950" s="4"/>
     </row>
     <row r="951" ht="15.75" customHeight="1">
       <c r="A951" s="2"/>
@@ -8913,6 +9877,7 @@
       <c r="E951" s="2"/>
       <c r="F951" s="2"/>
       <c r="G951" s="2"/>
+      <c r="H951" s="4"/>
     </row>
     <row r="952" ht="15.75" customHeight="1">
       <c r="A952" s="2"/>
@@ -8922,6 +9887,7 @@
       <c r="E952" s="2"/>
       <c r="F952" s="2"/>
       <c r="G952" s="2"/>
+      <c r="H952" s="4"/>
     </row>
     <row r="953" ht="15.75" customHeight="1">
       <c r="A953" s="2"/>
@@ -8931,6 +9897,7 @@
       <c r="E953" s="2"/>
       <c r="F953" s="2"/>
       <c r="G953" s="2"/>
+      <c r="H953" s="4"/>
     </row>
   </sheetData>
   <printOptions/>

--- a/ΕΥΑΓΓΕΛΙΖΟΜΕΝΟΙ.xlsx
+++ b/ΕΥΑΓΓΕΛΙΖΟΜΕΝΟΙ.xlsx
@@ -60,7 +60,7 @@
     <t>smyrnopoulos@gmail.com</t>
   </si>
   <si>
-    <t>251219912@</t>
+    <t>25121991@</t>
   </si>
 </sst>
 </file>
